--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -436,25 +436,25 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>10 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E2" t="str">
-        <v>10 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="F2" t="str">
-        <v>4:21</v>
+        <v>2:59</v>
       </c>
       <c r="G2" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="H2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -466,30 +466,30 @@
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E3" t="str">
-        <v>1 day ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="F3" t="str">
-        <v>4:09</v>
+        <v>4:21</v>
       </c>
       <c r="G3" t="str">
-        <v>Dermot Kennedy</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="H3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -501,18 +501,18 @@
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-22</v>
@@ -521,10 +521,10 @@
         <v>1 day ago</v>
       </c>
       <c r="F4" t="str">
-        <v>2:34</v>
+        <v>4:09</v>
       </c>
       <c r="G4" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="H4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -536,30 +536,30 @@
         <v/>
       </c>
       <c r="K4" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E5" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="F5" t="str">
-        <v>3:10</v>
+        <v>2:34</v>
       </c>
       <c r="G5" t="str">
-        <v>Olivia Dean</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="H5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -571,18 +571,18 @@
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B6" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-22</v>
@@ -591,10 +591,10 @@
         <v>2 days ago</v>
       </c>
       <c r="F6" t="str">
-        <v>3:21</v>
+        <v>3:10</v>
       </c>
       <c r="G6" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="H6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -606,18 +606,18 @@
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B7" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-22</v>
@@ -626,10 +626,10 @@
         <v>2 days ago</v>
       </c>
       <c r="F7" t="str">
-        <v>3:06</v>
+        <v>3:21</v>
       </c>
       <c r="G7" t="str">
-        <v>The Avett Brothers</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="H7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -641,18 +641,18 @@
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B8" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-22</v>
@@ -661,10 +661,10 @@
         <v>2 days ago</v>
       </c>
       <c r="F8" t="str">
-        <v>3:21</v>
+        <v>3:06</v>
       </c>
       <c r="G8" t="str">
-        <v>Jordana Bryant</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="H8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -676,18 +676,18 @@
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B9" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-22</v>
@@ -696,10 +696,10 @@
         <v>2 days ago</v>
       </c>
       <c r="F9" t="str">
-        <v>7:21</v>
+        <v>3:21</v>
       </c>
       <c r="G9" t="str">
-        <v>Katy Perry</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="H9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -711,30 +711,30 @@
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B10" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E10" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="F10" t="str">
-        <v>3:17</v>
+        <v>7:21</v>
       </c>
       <c r="G10" t="str">
-        <v>Lauren Watkins</v>
+        <v>Katy Perry</v>
       </c>
       <c r="H10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -746,30 +746,30 @@
         <v/>
       </c>
       <c r="K10" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B11" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E11" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="F11" t="str">
-        <v>3:45</v>
+        <v>3:17</v>
       </c>
       <c r="G11" t="str">
-        <v>Tones And I</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="H11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -781,18 +781,18 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B12" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-22</v>
@@ -801,10 +801,10 @@
         <v>4 days ago</v>
       </c>
       <c r="F12" t="str">
-        <v>3:57</v>
+        <v>3:45</v>
       </c>
       <c r="G12" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Tones And I</v>
       </c>
       <c r="H12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -816,30 +816,30 @@
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B13" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E13" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="F13" t="str">
-        <v>3:03</v>
+        <v>3:57</v>
       </c>
       <c r="G13" t="str">
-        <v>Charlie Puth</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="H13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -851,18 +851,18 @@
         <v/>
       </c>
       <c r="K13" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B14" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-22</v>
@@ -871,10 +871,10 @@
         <v>6 days ago</v>
       </c>
       <c r="F14" t="str">
-        <v>4:27</v>
+        <v>3:03</v>
       </c>
       <c r="G14" t="str">
-        <v>Chappell Roan</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="H14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -886,18 +886,18 @@
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B15" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-22</v>
@@ -906,10 +906,10 @@
         <v>6 days ago</v>
       </c>
       <c r="F15" t="str">
-        <v>4:34</v>
+        <v>4:27</v>
       </c>
       <c r="G15" t="str">
-        <v>Armik</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="H15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -921,18 +921,18 @@
         <v/>
       </c>
       <c r="K15" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B16" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-22</v>
@@ -941,10 +941,10 @@
         <v>6 days ago</v>
       </c>
       <c r="F16" t="str">
-        <v>2:54</v>
+        <v>4:34</v>
       </c>
       <c r="G16" t="str">
-        <v>LØLØ</v>
+        <v>Armik</v>
       </c>
       <c r="H16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -956,18 +956,18 @@
         <v/>
       </c>
       <c r="K16" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B17" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-22</v>
@@ -976,10 +976,10 @@
         <v>6 days ago</v>
       </c>
       <c r="F17" t="str">
-        <v>3:25</v>
+        <v>2:54</v>
       </c>
       <c r="G17" t="str">
-        <v>Tenille Townes</v>
+        <v>LØLØ</v>
       </c>
       <c r="H17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -991,18 +991,18 @@
         <v/>
       </c>
       <c r="K17" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B18" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-22</v>
@@ -1011,10 +1011,10 @@
         <v>6 days ago</v>
       </c>
       <c r="F18" t="str">
-        <v>2:01</v>
+        <v>3:25</v>
       </c>
       <c r="G18" t="str">
-        <v>Alan Walker</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="H18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1026,18 +1026,18 @@
         <v/>
       </c>
       <c r="K18" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-22</v>
@@ -1046,10 +1046,10 @@
         <v>6 days ago</v>
       </c>
       <c r="F19" t="str">
-        <v>2:25</v>
+        <v>2:01</v>
       </c>
       <c r="G19" t="str">
-        <v>Charli xcx</v>
+        <v>Alan Walker</v>
       </c>
       <c r="H19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1061,18 +1061,18 @@
         <v/>
       </c>
       <c r="K19" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B20" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-22</v>
@@ -1081,10 +1081,10 @@
         <v>6 days ago</v>
       </c>
       <c r="F20" t="str">
-        <v>1:14</v>
+        <v>2:25</v>
       </c>
       <c r="G20" t="str">
-        <v>Labrinth</v>
+        <v>Charli xcx</v>
       </c>
       <c r="H20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1096,18 +1096,18 @@
         <v/>
       </c>
       <c r="K20" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B21" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-22</v>
@@ -1116,10 +1116,10 @@
         <v>6 days ago</v>
       </c>
       <c r="F21" t="str">
-        <v>2:59</v>
+        <v>1:14</v>
       </c>
       <c r="G21" t="str">
-        <v>Charlie Puth</v>
+        <v>Labrinth</v>
       </c>
       <c r="H21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1131,18 +1131,18 @@
         <v/>
       </c>
       <c r="K21" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B22" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-22</v>
@@ -1151,10 +1151,10 @@
         <v>6 days ago</v>
       </c>
       <c r="F22" t="str">
-        <v>2:29</v>
+        <v>2:59</v>
       </c>
       <c r="G22" t="str">
-        <v>Girl Tones</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="H22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1166,18 +1166,18 @@
         <v/>
       </c>
       <c r="K22" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B23" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-22</v>
@@ -1186,10 +1186,10 @@
         <v>6 days ago</v>
       </c>
       <c r="F23" t="str">
-        <v>2:34</v>
+        <v>2:29</v>
       </c>
       <c r="G23" t="str">
-        <v>Jagwar Twin</v>
+        <v>Girl Tones</v>
       </c>
       <c r="H23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1201,18 +1201,18 @@
         <v/>
       </c>
       <c r="K23" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B24" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-22</v>
@@ -1221,10 +1221,10 @@
         <v>6 days ago</v>
       </c>
       <c r="F24" t="str">
-        <v>3:48</v>
+        <v>2:34</v>
       </c>
       <c r="G24" t="str">
-        <v>Caroline Jones</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="H24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1236,18 +1236,18 @@
         <v/>
       </c>
       <c r="K24" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B25" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-22</v>
@@ -1256,10 +1256,10 @@
         <v>6 days ago</v>
       </c>
       <c r="F25" t="str">
-        <v>3:32</v>
+        <v>3:48</v>
       </c>
       <c r="G25" t="str">
-        <v>The Beaches</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="H25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1271,18 +1271,18 @@
         <v/>
       </c>
       <c r="K25" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B26" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-22</v>
@@ -1291,10 +1291,10 @@
         <v>6 days ago</v>
       </c>
       <c r="F26" t="str">
-        <v>3:49</v>
+        <v>3:32</v>
       </c>
       <c r="G26" t="str">
-        <v>Dolly Parton</v>
+        <v>The Beaches</v>
       </c>
       <c r="H26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1306,18 +1306,18 @@
         <v/>
       </c>
       <c r="K26" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B27" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-22</v>
@@ -1326,10 +1326,10 @@
         <v>6 days ago</v>
       </c>
       <c r="F27" t="str">
-        <v>4:28</v>
+        <v>3:49</v>
       </c>
       <c r="G27" t="str">
-        <v>Madison Beer</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="H27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1341,18 +1341,18 @@
         <v/>
       </c>
       <c r="K27" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-22</v>
@@ -1361,10 +1361,10 @@
         <v>6 days ago</v>
       </c>
       <c r="F28" t="str">
-        <v>3:37</v>
+        <v>4:28</v>
       </c>
       <c r="G28" t="str">
-        <v>Ty Myers</v>
+        <v>Madison Beer</v>
       </c>
       <c r="H28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1376,18 +1376,18 @@
         <v/>
       </c>
       <c r="K28" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B29" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-22</v>
@@ -1396,10 +1396,10 @@
         <v>6 days ago</v>
       </c>
       <c r="F29" t="str">
-        <v>3:35</v>
+        <v>3:37</v>
       </c>
       <c r="G29" t="str">
-        <v>Megan Moroney</v>
+        <v>Ty Myers</v>
       </c>
       <c r="H29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1411,18 +1411,18 @@
         <v/>
       </c>
       <c r="K29" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B30" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-22</v>
@@ -1431,10 +1431,10 @@
         <v>6 days ago</v>
       </c>
       <c r="F30" t="str">
-        <v>2:31</v>
+        <v>3:35</v>
       </c>
       <c r="G30" t="str">
-        <v>Julia Cole Music</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="H30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1446,30 +1446,30 @@
         <v/>
       </c>
       <c r="K30" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E31" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="F31" t="str">
-        <v>3:21</v>
+        <v>2:31</v>
       </c>
       <c r="G31" t="str">
-        <v>Lily Allen</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="H31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1481,18 +1481,18 @@
         <v/>
       </c>
       <c r="K31" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B32" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-22</v>
@@ -1501,10 +1501,10 @@
         <v>7 days ago</v>
       </c>
       <c r="F32" t="str">
-        <v>5:24</v>
+        <v>3:21</v>
       </c>
       <c r="G32" t="str">
-        <v>Nickless</v>
+        <v>Lily Allen</v>
       </c>
       <c r="H32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1516,18 +1516,18 @@
         <v/>
       </c>
       <c r="K32" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B33" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-22</v>
@@ -1536,10 +1536,10 @@
         <v>7 days ago</v>
       </c>
       <c r="F33" t="str">
-        <v>3:11</v>
+        <v>5:24</v>
       </c>
       <c r="G33" t="str">
-        <v>Peach PRC</v>
+        <v>Nickless</v>
       </c>
       <c r="H33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1551,18 +1551,18 @@
         <v/>
       </c>
       <c r="K33" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
+        <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B34" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
+        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-22</v>
@@ -1571,10 +1571,10 @@
         <v>7 days ago</v>
       </c>
       <c r="F34" t="str">
-        <v>4:11</v>
+        <v>3:11</v>
       </c>
       <c r="G34" t="str">
-        <v>Ocean Alley</v>
+        <v>Peach PRC</v>
       </c>
       <c r="H34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1586,18 +1586,18 @@
         <v/>
       </c>
       <c r="K34" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
+        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
       </c>
       <c r="B35" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
+        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-22</v>
@@ -1606,10 +1606,10 @@
         <v>7 days ago</v>
       </c>
       <c r="F35" t="str">
-        <v>3:31</v>
+        <v>4:11</v>
       </c>
       <c r="G35" t="str">
-        <v>OneRepublic</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="H35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1621,18 +1621,18 @@
         <v/>
       </c>
       <c r="K35" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B36" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
+        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-22</v>
@@ -1641,10 +1641,10 @@
         <v>7 days ago</v>
       </c>
       <c r="F36" t="str">
-        <v>4:16</v>
+        <v>3:31</v>
       </c>
       <c r="G36" t="str">
-        <v>Ty Myers</v>
+        <v>OneRepublic</v>
       </c>
       <c r="H36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1656,18 +1656,18 @@
         <v/>
       </c>
       <c r="K36" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
       </c>
       <c r="B37" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
+        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-22</v>
@@ -1676,10 +1676,10 @@
         <v>8 days ago</v>
       </c>
       <c r="F37" t="str">
-        <v>4:42</v>
+        <v>4:16</v>
       </c>
       <c r="G37" t="str">
-        <v>JavaJazzFest</v>
+        <v>Ty Myers</v>
       </c>
       <c r="H37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1691,30 +1691,30 @@
         <v/>
       </c>
       <c r="K37" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video)</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B38" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
+        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E38" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="F38" t="str">
-        <v>2:47</v>
+        <v>4:42</v>
       </c>
       <c r="G38" t="str">
-        <v>Teo Glacier</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="H38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1726,18 +1726,18 @@
         <v/>
       </c>
       <c r="K38" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
+        <v>Teo Glacier - Don't Mind (Music Video)</v>
       </c>
       <c r="B39" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
+        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-22</v>
@@ -1746,10 +1746,10 @@
         <v>9 days ago</v>
       </c>
       <c r="F39" t="str">
-        <v>3:59</v>
+        <v>2:47</v>
       </c>
       <c r="G39" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>Teo Glacier</v>
       </c>
       <c r="H39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,30 +1761,30 @@
         <v/>
       </c>
       <c r="K39" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
+        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E40" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="F40" t="str">
-        <v>4:09</v>
+        <v>3:59</v>
       </c>
       <c r="G40" t="str">
-        <v>Louie TheSinger</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="H40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1796,30 +1796,30 @@
         <v/>
       </c>
       <c r="K40" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ella jane - When I Was Beautiful (Live)</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
       </c>
       <c r="B41" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
+        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E41" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="F41" t="str">
-        <v>3:24</v>
+        <v>4:09</v>
       </c>
       <c r="G41" t="str">
-        <v>ella jane</v>
+        <v>Louie TheSinger</v>
       </c>
       <c r="H41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1831,18 +1831,18 @@
         <v/>
       </c>
       <c r="K41" t="str">
-        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Johnny Orlando - Emilia (Official Video)</v>
+        <v>ella jane - When I Was Beautiful (Live)</v>
       </c>
       <c r="B42" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
+        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-22</v>
@@ -1851,10 +1851,10 @@
         <v>13 days ago</v>
       </c>
       <c r="F42" t="str">
-        <v>3:14</v>
+        <v>3:24</v>
       </c>
       <c r="G42" t="str">
-        <v>Johnny Orlando</v>
+        <v>ella jane</v>
       </c>
       <c r="H42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1866,18 +1866,18 @@
         <v/>
       </c>
       <c r="K42" t="str">
-        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
+        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video)</v>
+        <v>Johnny Orlando - Emilia (Official Video)</v>
       </c>
       <c r="B43" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
+        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-22</v>
@@ -1886,10 +1886,10 @@
         <v>13 days ago</v>
       </c>
       <c r="F43" t="str">
-        <v>3:32</v>
+        <v>3:14</v>
       </c>
       <c r="G43" t="str">
-        <v>Kungs</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="H43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1901,18 +1901,18 @@
         <v/>
       </c>
       <c r="K43" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
+        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
+        <v>Kungs, Theophilus London - Galaxy (official video)</v>
       </c>
       <c r="B44" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
+        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-22</v>
@@ -1921,10 +1921,10 @@
         <v>13 days ago</v>
       </c>
       <c r="F44" t="str">
-        <v>3:15</v>
+        <v>3:32</v>
       </c>
       <c r="G44" t="str">
-        <v>Billy Raffoul</v>
+        <v>Kungs</v>
       </c>
       <c r="H44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1936,18 +1936,18 @@
         <v/>
       </c>
       <c r="K44" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
+        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
+        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-22</v>
@@ -1956,10 +1956,10 @@
         <v>13 days ago</v>
       </c>
       <c r="F45" t="str">
-        <v>3:03</v>
+        <v>3:15</v>
       </c>
       <c r="G45" t="str">
-        <v>NathanEvanss</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="H45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1971,18 +1971,18 @@
         <v/>
       </c>
       <c r="K45" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) (Official Music Video) - Billy Raffoul</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Stephen Sanchez - Sweet Love</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
       </c>
       <c r="B46" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
+        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-22</v>
@@ -1991,10 +1991,10 @@
         <v>13 days ago</v>
       </c>
       <c r="F46" t="str">
-        <v>3:04</v>
+        <v>3:03</v>
       </c>
       <c r="G46" t="str">
-        <v>Stephen Sanchez</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="H46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2006,18 +2006,18 @@
         <v/>
       </c>
       <c r="K46" t="str">
-        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video]</v>
+        <v>Stephen Sanchez - Sweet Love</v>
       </c>
       <c r="B47" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
+        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-22</v>
@@ -2026,10 +2026,10 @@
         <v>13 days ago</v>
       </c>
       <c r="F47" t="str">
-        <v>3:33</v>
+        <v>3:04</v>
       </c>
       <c r="G47" t="str">
-        <v>Bruno Mars</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="H47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2041,18 +2041,18 @@
         <v/>
       </c>
       <c r="K47" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
+        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
+        <v>Bruno Mars - I Just Might [Official Music Video]</v>
       </c>
       <c r="B48" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
+        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-22</v>
@@ -2061,10 +2061,10 @@
         <v>13 days ago</v>
       </c>
       <c r="F48" t="str">
-        <v>2:53</v>
+        <v>3:33</v>
       </c>
       <c r="G48" t="str">
-        <v>MAX</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="H48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2076,18 +2076,18 @@
         <v/>
       </c>
       <c r="K48" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
+        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
       </c>
       <c r="B49" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
+        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-22</v>
@@ -2096,10 +2096,10 @@
         <v>13 days ago</v>
       </c>
       <c r="F49" t="str">
-        <v>4:11</v>
+        <v>2:53</v>
       </c>
       <c r="G49" t="str">
-        <v>Jessie J</v>
+        <v>MAX</v>
       </c>
       <c r="H49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2111,18 +2111,18 @@
         <v/>
       </c>
       <c r="K49" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
       </c>
       <c r="B50" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
+        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-22</v>
@@ -2131,10 +2131,10 @@
         <v>13 days ago</v>
       </c>
       <c r="F50" t="str">
-        <v>2:45</v>
+        <v>4:11</v>
       </c>
       <c r="G50" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Jessie J</v>
       </c>
       <c r="H50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2146,18 +2146,18 @@
         <v/>
       </c>
       <c r="K50" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
       </c>
       <c r="B51" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
+        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-22</v>
@@ -2166,10 +2166,10 @@
         <v>13 days ago</v>
       </c>
       <c r="F51" t="str">
-        <v>4:00</v>
+        <v>2:45</v>
       </c>
       <c r="G51" t="str">
-        <v>Brandon Lake and Cody Johnson</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="H51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2181,18 +2181,18 @@
         <v/>
       </c>
       <c r="K51" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
       </c>
       <c r="B52" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
+        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-22</v>
@@ -2201,10 +2201,10 @@
         <v>13 days ago</v>
       </c>
       <c r="F52" t="str">
-        <v>3:27</v>
+        <v>4:00</v>
       </c>
       <c r="G52" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Brandon Lake and Cody Johnson</v>
       </c>
       <c r="H52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2216,30 +2216,30 @@
         <v/>
       </c>
       <c r="K52" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
       </c>
       <c r="B53" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
+        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E53" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="F53" t="str">
-        <v>3:25</v>
+        <v>3:27</v>
       </c>
       <c r="G53" t="str">
-        <v>Olivia Dean</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="H53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2251,18 +2251,18 @@
         <v/>
       </c>
       <c r="K53" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
       </c>
       <c r="B54" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
+        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-22</v>
@@ -2271,10 +2271,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="F54" t="str">
-        <v>3:34</v>
+        <v>3:25</v>
       </c>
       <c r="G54" t="str">
-        <v>Demi Lovato</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="H54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2286,18 +2286,18 @@
         <v/>
       </c>
       <c r="K54" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Train - Mittens (Live on TODAY)</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B55" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=R2k_wPsAHKQ</v>
+        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-22</v>
@@ -2306,10 +2306,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="F55" t="str">
-        <v>3:17</v>
+        <v>3:34</v>
       </c>
       <c r="G55" t="str">
-        <v>Train</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="H55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2321,18 +2321,18 @@
         <v/>
       </c>
       <c r="K55" t="str">
-        <v>Train - Mittens (Live on TODAY) - Train</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
+        <v>Train - Mittens (Live on TODAY)</v>
       </c>
       <c r="B56" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
+        <v>https://www.youtube.com/watch?v=R2k_wPsAHKQ</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-22</v>
@@ -2341,10 +2341,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="F56" t="str">
-        <v>2:25</v>
+        <v>3:17</v>
       </c>
       <c r="G56" t="str">
-        <v>Joseph</v>
+        <v>Train</v>
       </c>
       <c r="H56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2356,18 +2356,18 @@
         <v/>
       </c>
       <c r="K56" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
+        <v>Train - Mittens (Live on TODAY) - Train</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
       </c>
       <c r="B57" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
+        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-22</v>
@@ -2376,10 +2376,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="F57" t="str">
-        <v>3:26</v>
+        <v>2:25</v>
       </c>
       <c r="G57" t="str">
-        <v>Demi Lovato</v>
+        <v>Joseph</v>
       </c>
       <c r="H57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2391,18 +2391,18 @@
         <v/>
       </c>
       <c r="K57" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B58" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
+        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-22</v>
@@ -2411,10 +2411,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="F58" t="str">
-        <v>4:46</v>
+        <v>3:26</v>
       </c>
       <c r="G58" t="str">
-        <v>Keith Urban</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="H58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2426,18 +2426,18 @@
         <v/>
       </c>
       <c r="K58" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B59" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
+        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-22</v>
@@ -2446,7 +2446,7 @@
         <v>2 weeks ago</v>
       </c>
       <c r="F59" t="str">
-        <v>3:24</v>
+        <v>4:46</v>
       </c>
       <c r="G59" t="str">
         <v>Keith Urban</v>
@@ -2461,18 +2461,18 @@
         <v/>
       </c>
       <c r="K59" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B60" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
+        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-22</v>
@@ -2481,10 +2481,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="F60" t="str">
-        <v>2:52</v>
+        <v>3:24</v>
       </c>
       <c r="G60" t="str">
-        <v>Madonna</v>
+        <v>Keith Urban</v>
       </c>
       <c r="H60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2496,18 +2496,18 @@
         <v/>
       </c>
       <c r="K60" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
       </c>
       <c r="B61" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
+        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-22</v>
@@ -2516,10 +2516,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="F61" t="str">
-        <v>2:06</v>
+        <v>2:52</v>
       </c>
       <c r="G61" t="str">
-        <v>Estas Tonne</v>
+        <v>Madonna</v>
       </c>
       <c r="H61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2531,18 +2531,18 @@
         <v/>
       </c>
       <c r="K61" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estas Tonne</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Anna Graves - Burn On (Official Music Video)</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
+        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-22</v>
@@ -2551,10 +2551,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="F62" t="str">
-        <v>3:09</v>
+        <v>2:06</v>
       </c>
       <c r="G62" t="str">
-        <v>Anna Graves</v>
+        <v>Estas Tonne</v>
       </c>
       <c r="H62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2566,18 +2566,18 @@
         <v/>
       </c>
       <c r="K62" t="str">
-        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estas Tonne</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
+        <v>Anna Graves - Burn On (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
+        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-22</v>
@@ -2586,10 +2586,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="F63" t="str">
-        <v>5:11</v>
+        <v>3:09</v>
       </c>
       <c r="G63" t="str">
-        <v>Ocean Alley</v>
+        <v>Anna Graves</v>
       </c>
       <c r="H63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2601,18 +2601,18 @@
         <v/>
       </c>
       <c r="K63" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
+        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
+        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-22</v>
@@ -2621,10 +2621,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="F64" t="str">
-        <v>3:40</v>
+        <v>5:11</v>
       </c>
       <c r="G64" t="str">
-        <v>Zara Larsson</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="H64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2636,18 +2636,18 @@
         <v/>
       </c>
       <c r="K64" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
+        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-22</v>
@@ -2656,10 +2656,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="F65" t="str">
-        <v>3:49</v>
+        <v>3:40</v>
       </c>
       <c r="G65" t="str">
-        <v>Lauren Watkins</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="H65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2671,18 +2671,18 @@
         <v/>
       </c>
       <c r="K65" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
+        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-22</v>
@@ -2691,10 +2691,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="F66" t="str">
-        <v>3:42</v>
+        <v>3:49</v>
       </c>
       <c r="G66" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="H66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2706,18 +2706,18 @@
         <v/>
       </c>
       <c r="K66" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
+        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-22</v>
@@ -2726,10 +2726,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="F67" t="str">
-        <v>5:11</v>
+        <v>3:42</v>
       </c>
       <c r="G67" t="str">
-        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="H67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2741,18 +2741,18 @@
         <v/>
       </c>
       <c r="K67" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
+        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-22</v>
@@ -2761,10 +2761,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="F68" t="str">
-        <v>3:57</v>
+        <v>5:11</v>
       </c>
       <c r="G68" t="str">
-        <v>Lainey Wilson</v>
+        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="H68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2776,18 +2776,18 @@
         <v/>
       </c>
       <c r="K68" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video)</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
+        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-22</v>
@@ -2796,10 +2796,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="F69" t="str">
-        <v>3:29</v>
+        <v>3:57</v>
       </c>
       <c r="G69" t="str">
-        <v>Grace Enger</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="H69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2811,18 +2811,18 @@
         <v/>
       </c>
       <c r="K69" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video)</v>
+        <v>Grace Enger - All My Songs (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
+        <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-22</v>
@@ -2831,10 +2831,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="F70" t="str">
-        <v>3:10</v>
+        <v>3:29</v>
       </c>
       <c r="G70" t="str">
-        <v>Alan Walker and 2 more</v>
+        <v>Grace Enger</v>
       </c>
       <c r="H70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2846,18 +2846,18 @@
         <v/>
       </c>
       <c r="K70" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
+        <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Emilia Tarrant - Break Up With Myself</v>
+        <v>Alan Walker - Broken Strings (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
+        <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-22</v>
@@ -2866,10 +2866,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="F71" t="str">
-        <v>4:04</v>
+        <v>3:10</v>
       </c>
       <c r="G71" t="str">
-        <v>Emilia Tarrant</v>
+        <v>Alan Walker and 2 more</v>
       </c>
       <c r="H71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2881,30 +2881,30 @@
         <v/>
       </c>
       <c r="K71" t="str">
-        <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
+        <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026)</v>
+        <v>Emilia Tarrant - Break Up With Myself</v>
       </c>
       <c r="B72" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
+        <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E72" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="F72" t="str">
-        <v>3:09</v>
+        <v>4:04</v>
       </c>
       <c r="G72" t="str">
-        <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Emilia Tarrant</v>
       </c>
       <c r="H72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2916,18 +2916,18 @@
         <v/>
       </c>
       <c r="K72" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer)</v>
+        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026)</v>
       </c>
       <c r="B73" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
+        <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-22</v>
@@ -2936,10 +2936,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="F73" t="str">
-        <v>2:27</v>
+        <v>3:09</v>
       </c>
       <c r="G73" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="H73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2951,18 +2951,18 @@
         <v/>
       </c>
       <c r="K73" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
+        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Maggie Lindemann - fate</v>
+        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer)</v>
       </c>
       <c r="B74" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
+        <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-22</v>
@@ -2971,10 +2971,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="F74" t="str">
-        <v>2:12</v>
+        <v>2:27</v>
       </c>
       <c r="G74" t="str">
-        <v>Maggie Lindemann</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="H74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2986,18 +2986,18 @@
         <v/>
       </c>
       <c r="K74" t="str">
-        <v>Maggie Lindemann - fate - Maggie Lindemann</v>
+        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023)</v>
+        <v>Maggie Lindemann - fate</v>
       </c>
       <c r="B75" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=wo9yPPCh75Q</v>
+        <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-22</v>
@@ -3006,10 +3006,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="F75" t="str">
-        <v>4:44</v>
+        <v>2:12</v>
       </c>
       <c r="G75" t="str">
-        <v>Cliff Richard</v>
+        <v>Maggie Lindemann</v>
       </c>
       <c r="H75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3021,18 +3021,18 @@
         <v/>
       </c>
       <c r="K75" t="str">
-        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023) - Cliff Richard</v>
+        <v>Maggie Lindemann - fate - Maggie Lindemann</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025</v>
+        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023)</v>
       </c>
       <c r="B76" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=ND6maRwmzHk</v>
+        <v>https://www.youtube.com/watch?v=wo9yPPCh75Q</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-22</v>
@@ -3041,10 +3041,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="F76" t="str">
-        <v>1:00:09</v>
+        <v>4:44</v>
       </c>
       <c r="G76" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="H76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3056,18 +3056,18 @@
         <v/>
       </c>
       <c r="K76" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025 - Purple Disco Machine</v>
+        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023) - Cliff Richard</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall)</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025</v>
       </c>
       <c r="B77" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=9jMMOYr-VhE</v>
+        <v>https://www.youtube.com/watch?v=ND6maRwmzHk</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-22</v>
@@ -3076,10 +3076,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="F77" t="str">
-        <v>4:15</v>
+        <v>1:00:09</v>
       </c>
       <c r="G77" t="str">
-        <v>RAYE</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="H77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="K77" t="str">
-        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall) - RAYE</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Madison Cunningham - My Full Name (Garden Session)</v>
+        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall)</v>
       </c>
       <c r="B78" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=o2F-QmqdNtI</v>
+        <v>https://www.youtube.com/watch?v=9jMMOYr-VhE</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-22</v>
@@ -3111,10 +3111,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="F78" t="str">
-        <v>4:07</v>
+        <v>4:15</v>
       </c>
       <c r="G78" t="str">
-        <v>Madison Cunningham</v>
+        <v>RAYE</v>
       </c>
       <c r="H78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3126,18 +3126,18 @@
         <v/>
       </c>
       <c r="K78" t="str">
-        <v>Madison Cunningham - My Full Name (Garden Session) - Madison Cunningham</v>
+        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall) - RAYE</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions)</v>
+        <v>Madison Cunningham - My Full Name (Garden Session)</v>
       </c>
       <c r="B79" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=5-6cEVLqE90</v>
+        <v>https://www.youtube.com/watch?v=o2F-QmqdNtI</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-22</v>
@@ -3146,10 +3146,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="F79" t="str">
-        <v>3:10</v>
+        <v>4:07</v>
       </c>
       <c r="G79" t="str">
-        <v>Teddy Swims</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="H79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3161,18 +3161,18 @@
         <v/>
       </c>
       <c r="K79" t="str">
-        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>Madison Cunningham - My Full Name (Garden Session) - Madison Cunningham</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower)</v>
+        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions)</v>
       </c>
       <c r="B80" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=ivPSbcEMwCs</v>
+        <v>https://www.youtube.com/watch?v=5-6cEVLqE90</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-22</v>
@@ -3181,10 +3181,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="F80" t="str">
-        <v>3:47</v>
+        <v>3:10</v>
       </c>
       <c r="G80" t="str">
-        <v>Christina Aguilera</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="H80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3196,18 +3196,18 @@
         <v/>
       </c>
       <c r="K80" t="str">
-        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower) - Christina Aguilera</v>
+        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025)</v>
+        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower)</v>
       </c>
       <c r="B81" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=tYpOHbXFnm0</v>
+        <v>https://www.youtube.com/watch?v=ivPSbcEMwCs</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-22</v>
@@ -3216,10 +3216,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="F81" t="str">
-        <v>3:58</v>
+        <v>3:47</v>
       </c>
       <c r="G81" t="str">
-        <v>RAYE</v>
+        <v>Christina Aguilera</v>
       </c>
       <c r="H81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3231,18 +3231,18 @@
         <v/>
       </c>
       <c r="K81" t="str">
-        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025) - RAYE</v>
+        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower) - Christina Aguilera</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Dasha - Here For The Party (Official Audio)</v>
+        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025)</v>
       </c>
       <c r="B82" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=rSO9oYUnO2k</v>
+        <v>https://www.youtube.com/watch?v=tYpOHbXFnm0</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-22</v>
@@ -3251,10 +3251,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="F82" t="str">
-        <v>3:30</v>
+        <v>3:58</v>
       </c>
       <c r="G82" t="str">
-        <v>Dasha</v>
+        <v>RAYE</v>
       </c>
       <c r="H82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3266,30 +3266,30 @@
         <v/>
       </c>
       <c r="K82" t="str">
-        <v>Dasha - Here For The Party (Official Audio) - Dasha</v>
+        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025) - RAYE</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Lady Gaga in Harlequin Live: One Night Only</v>
+        <v>Dasha - Here For The Party (Official Audio)</v>
       </c>
       <c r="B83" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=c231tCsQalU</v>
+        <v>https://www.youtube.com/watch?v=rSO9oYUnO2k</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E83" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="F83" t="str">
-        <v>51:49</v>
+        <v>3:30</v>
       </c>
       <c r="G83" t="str">
-        <v>Lady Gaga and YouTube</v>
+        <v>Dasha</v>
       </c>
       <c r="H83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3301,18 +3301,18 @@
         <v/>
       </c>
       <c r="K83" t="str">
-        <v>Lady Gaga in Harlequin Live: One Night Only - Lady Gaga and YouTube</v>
+        <v>Dasha - Here For The Party (Official Audio) - Dasha</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Sabrina Carpenter - Such A Funny Way (Official Lyric Video)</v>
+        <v>Lady Gaga in Harlequin Live: One Night Only</v>
       </c>
       <c r="B84" t="str">
         <v>4 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=oaJKUCgSSkc</v>
+        <v>https://www.youtube.com/watch?v=c231tCsQalU</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-22</v>
@@ -3321,10 +3321,10 @@
         <v>4 weeks ago</v>
       </c>
       <c r="F84" t="str">
-        <v>3:53</v>
+        <v>51:49</v>
       </c>
       <c r="G84" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>Lady Gaga and YouTube</v>
       </c>
       <c r="H84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3336,18 +3336,18 @@
         <v/>
       </c>
       <c r="K84" t="str">
-        <v>Sabrina Carpenter - Such A Funny Way (Official Lyric Video) - Sabrina Carpenter</v>
+        <v>Lady Gaga in Harlequin Live: One Night Only - Lady Gaga and YouTube</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Megan Moroney - Beautiful Things (Official Fan Video)</v>
+        <v>Sabrina Carpenter - Such A Funny Way (Official Lyric Video)</v>
       </c>
       <c r="B85" t="str">
         <v>4 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=0Gxu80LxI0w</v>
+        <v>https://www.youtube.com/watch?v=oaJKUCgSSkc</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-22</v>
@@ -3356,10 +3356,10 @@
         <v>4 weeks ago</v>
       </c>
       <c r="F85" t="str">
-        <v>3:56</v>
+        <v>3:53</v>
       </c>
       <c r="G85" t="str">
-        <v>Megan Moroney</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="H85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3371,18 +3371,18 @@
         <v/>
       </c>
       <c r="K85" t="str">
-        <v>Megan Moroney - Beautiful Things (Official Fan Video) - Megan Moroney</v>
+        <v>Sabrina Carpenter - Such A Funny Way (Official Lyric Video) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Jason Derulo - Miracle</v>
+        <v>Megan Moroney - Beautiful Things (Official Fan Video)</v>
       </c>
       <c r="B86" t="str">
         <v>4 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=7sjshHJwkOE</v>
+        <v>https://www.youtube.com/watch?v=0Gxu80LxI0w</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-22</v>
@@ -3391,10 +3391,10 @@
         <v>4 weeks ago</v>
       </c>
       <c r="F86" t="str">
-        <v>4:16</v>
+        <v>3:56</v>
       </c>
       <c r="G86" t="str">
-        <v>Jason Derulo</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="H86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3406,18 +3406,18 @@
         <v/>
       </c>
       <c r="K86" t="str">
-        <v>Jason Derulo - Miracle - Jason Derulo</v>
+        <v>Megan Moroney - Beautiful Things (Official Fan Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Sananda Maitreya - Pretty Baby (Live)</v>
+        <v>Jason Derulo - Miracle</v>
       </c>
       <c r="B87" t="str">
         <v>4 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=yv1c5G5HZt8</v>
+        <v>https://www.youtube.com/watch?v=7sjshHJwkOE</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-22</v>
@@ -3426,10 +3426,10 @@
         <v>4 weeks ago</v>
       </c>
       <c r="F87" t="str">
-        <v>3:29</v>
+        <v>4:16</v>
       </c>
       <c r="G87" t="str">
-        <v>Sananda Maitreya</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="H87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3441,18 +3441,18 @@
         <v/>
       </c>
       <c r="K87" t="str">
-        <v>Sananda Maitreya - Pretty Baby (Live) - Sananda Maitreya</v>
+        <v>Jason Derulo - Miracle - Jason Derulo</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Faded - 10th Anniversary (Performance Video)</v>
+        <v>Sananda Maitreya - Pretty Baby (Live)</v>
       </c>
       <c r="B88" t="str">
         <v>4 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=EXVg23U3NRw</v>
+        <v>https://www.youtube.com/watch?v=yv1c5G5HZt8</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-22</v>
@@ -3461,10 +3461,10 @@
         <v>4 weeks ago</v>
       </c>
       <c r="F88" t="str">
-        <v>3:25</v>
+        <v>3:29</v>
       </c>
       <c r="G88" t="str">
-        <v>Alan Walker and 2 more</v>
+        <v>Sananda Maitreya</v>
       </c>
       <c r="H88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3476,18 +3476,18 @@
         <v/>
       </c>
       <c r="K88" t="str">
-        <v>Faded - 10th Anniversary (Performance Video) - Alan Walker and 2 more</v>
+        <v>Sananda Maitreya - Pretty Baby (Live) - Sananda Maitreya</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>What Are You Doing New Year's Eve (Live from the Eiffel Tower - Official Lyric Video)</v>
+        <v>Faded - 10th Anniversary (Performance Video)</v>
       </c>
       <c r="B89" t="str">
         <v>4 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=Bpb67fSUzEQ</v>
+        <v>https://www.youtube.com/watch?v=EXVg23U3NRw</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-22</v>
@@ -3496,10 +3496,10 @@
         <v>4 weeks ago</v>
       </c>
       <c r="F89" t="str">
-        <v>4:06</v>
+        <v>3:25</v>
       </c>
       <c r="G89" t="str">
-        <v>Christina Aguilera</v>
+        <v>Alan Walker and 2 more</v>
       </c>
       <c r="H89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3511,18 +3511,18 @@
         <v/>
       </c>
       <c r="K89" t="str">
-        <v>What Are You Doing New Year's Eve (Live from the Eiffel Tower - Official Lyric Video) - Christina Aguilera</v>
+        <v>Faded - 10th Anniversary (Performance Video) - Alan Walker and 2 more</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Have Yourself a Merry Little Christmas (Live from the Eiffel Tower - Official Lyric Video)</v>
+        <v>What Are You Doing New Year's Eve (Live from the Eiffel Tower - Official Lyric Video)</v>
       </c>
       <c r="B90" t="str">
         <v>4 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=gkwb6kZloLA</v>
+        <v>https://www.youtube.com/watch?v=Bpb67fSUzEQ</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-22</v>
@@ -3531,7 +3531,7 @@
         <v>4 weeks ago</v>
       </c>
       <c r="F90" t="str">
-        <v>4:03</v>
+        <v>4:06</v>
       </c>
       <c r="G90" t="str">
         <v>Christina Aguilera</v>
@@ -3546,30 +3546,30 @@
         <v/>
       </c>
       <c r="K90" t="str">
-        <v>Have Yourself a Merry Little Christmas (Live from the Eiffel Tower - Official Lyric Video) - Christina Aguilera</v>
+        <v>What Are You Doing New Year's Eve (Live from the Eiffel Tower - Official Lyric Video) - Christina Aguilera</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Chris Rea - Driving Home for Christmas - (Live on National Lottery Stars, 2000)</v>
+        <v>Have Yourself a Merry Little Christmas (Live from the Eiffel Tower - Official Lyric Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>1 year ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=Jckb3dnS5fw</v>
+        <v>https://www.youtube.com/watch?v=gkwb6kZloLA</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E91" t="str">
-        <v>1 year ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="F91" t="str">
-        <v>4:11</v>
+        <v>4:03</v>
       </c>
       <c r="G91" t="str">
-        <v>Chris Rea Official</v>
+        <v>Christina Aguilera</v>
       </c>
       <c r="H91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3581,30 +3581,30 @@
         <v/>
       </c>
       <c r="K91" t="str">
-        <v>Chris Rea - Driving Home for Christmas - (Live on National Lottery Stars, 2000) - Chris Rea Official</v>
+        <v>Have Yourself a Merry Little Christmas (Live from the Eiffel Tower - Official Lyric Video) - Christina Aguilera</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Jessie J - I'll Never Know Why (The Royal Variety Performance 2025)</v>
+        <v>Chris Rea - Driving Home for Christmas - (Live on National Lottery Stars, 2000)</v>
       </c>
       <c r="B92" t="str">
-        <v>1 month ago</v>
+        <v>1 year ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=DPA8v4YS8AY</v>
+        <v>https://www.youtube.com/watch?v=Jckb3dnS5fw</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E92" t="str">
-        <v>1 month ago</v>
+        <v>1 year ago</v>
       </c>
       <c r="F92" t="str">
-        <v>4:08</v>
+        <v>4:11</v>
       </c>
       <c r="G92" t="str">
-        <v>Jessie J</v>
+        <v>Chris Rea Official</v>
       </c>
       <c r="H92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3616,18 +3616,18 @@
         <v/>
       </c>
       <c r="K92" t="str">
-        <v>Jessie J - I'll Never Know Why (The Royal Variety Performance 2025) - Jessie J</v>
+        <v>Chris Rea - Driving Home for Christmas - (Live on National Lottery Stars, 2000) - Chris Rea Official</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Craig David - Walking Away (Official HD Video)</v>
+        <v>Jessie J - I'll Never Know Why (The Royal Variety Performance 2025)</v>
       </c>
       <c r="B93" t="str">
         <v>1 month ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=v8Yu21pEbqw</v>
+        <v>https://www.youtube.com/watch?v=DPA8v4YS8AY</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-22</v>
@@ -3636,10 +3636,10 @@
         <v>1 month ago</v>
       </c>
       <c r="F93" t="str">
-        <v>3:34</v>
+        <v>4:08</v>
       </c>
       <c r="G93" t="str">
-        <v>Craig David</v>
+        <v>Jessie J</v>
       </c>
       <c r="H93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3651,18 +3651,18 @@
         <v/>
       </c>
       <c r="K93" t="str">
-        <v>Craig David - Walking Away (Official HD Video) - Craig David</v>
+        <v>Jessie J - I'll Never Know Why (The Royal Variety Performance 2025) - Jessie J</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Christina Aguilera, Yseult - Ave Maria (Live from the Eiffel Tower - Official Video)</v>
+        <v>Craig David - Walking Away (Official HD Video)</v>
       </c>
       <c r="B94" t="str">
         <v>1 month ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=sq2u9Cfn2B8</v>
+        <v>https://www.youtube.com/watch?v=v8Yu21pEbqw</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-22</v>
@@ -3671,10 +3671,10 @@
         <v>1 month ago</v>
       </c>
       <c r="F94" t="str">
-        <v>4:37</v>
+        <v>3:34</v>
       </c>
       <c r="G94" t="str">
-        <v>Christina Aguilera</v>
+        <v>Craig David</v>
       </c>
       <c r="H94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3686,18 +3686,18 @@
         <v/>
       </c>
       <c r="K94" t="str">
-        <v>Christina Aguilera, Yseult - Ave Maria (Live from the Eiffel Tower - Official Video) - Christina Aguilera</v>
+        <v>Craig David - Walking Away (Official HD Video) - Craig David</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Shawn Mendes &amp; Niall Horan - This Town (Live from London)</v>
+        <v>Christina Aguilera, Yseult - Ave Maria (Live from the Eiffel Tower - Official Video)</v>
       </c>
       <c r="B95" t="str">
         <v>1 month ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=Ea2DSMNIK5w</v>
+        <v>https://www.youtube.com/watch?v=sq2u9Cfn2B8</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-22</v>
@@ -3706,10 +3706,10 @@
         <v>1 month ago</v>
       </c>
       <c r="F95" t="str">
-        <v>6:27</v>
+        <v>4:37</v>
       </c>
       <c r="G95" t="str">
-        <v>Shawn Mendes and Niall Horan</v>
+        <v>Christina Aguilera</v>
       </c>
       <c r="H95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3721,18 +3721,18 @@
         <v/>
       </c>
       <c r="K95" t="str">
-        <v>Shawn Mendes &amp; Niall Horan - This Town (Live from London) - Shawn Mendes and Niall Horan</v>
+        <v>Christina Aguilera, Yseult - Ave Maria (Live from the Eiffel Tower - Official Video) - Christina Aguilera</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Shakira - Zoo (From "Zootopia 2")</v>
+        <v>Shawn Mendes &amp; Niall Horan - This Town (Live from London)</v>
       </c>
       <c r="B96" t="str">
         <v>1 month ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=kCIf6yaJisQ</v>
+        <v>https://www.youtube.com/watch?v=Ea2DSMNIK5w</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-22</v>
@@ -3741,10 +3741,10 @@
         <v>1 month ago</v>
       </c>
       <c r="F96" t="str">
-        <v>2:07</v>
+        <v>6:27</v>
       </c>
       <c r="G96" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Shawn Mendes and Niall Horan</v>
       </c>
       <c r="H96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3756,18 +3756,18 @@
         <v/>
       </c>
       <c r="K96" t="str">
-        <v>Shakira - Zoo (From "Zootopia 2") - DisneyMusicVEVO</v>
+        <v>Shawn Mendes &amp; Niall Horan - This Town (Live from London) - Shawn Mendes and Niall Horan</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Within Temptation - Ice Queen (Acoustic) | 2025 Reimagined Edition</v>
+        <v>Shakira - Zoo (From "Zootopia 2")</v>
       </c>
       <c r="B97" t="str">
         <v>1 month ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=f1Iqm16vWDQ</v>
+        <v>https://www.youtube.com/watch?v=kCIf6yaJisQ</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-22</v>
@@ -3776,10 +3776,10 @@
         <v>1 month ago</v>
       </c>
       <c r="F97" t="str">
-        <v>3:40</v>
+        <v>2:07</v>
       </c>
       <c r="G97" t="str">
-        <v>Within Temptation</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="H97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3791,18 +3791,18 @@
         <v/>
       </c>
       <c r="K97" t="str">
-        <v>Within Temptation - Ice Queen (Acoustic) | 2025 Reimagined Edition - Within Temptation</v>
+        <v>Shakira - Zoo (From "Zootopia 2") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>OneRepublic - Give Me Something (for Arknights Endfield) (Official Audio)</v>
+        <v>Within Temptation - Ice Queen (Acoustic) | 2025 Reimagined Edition</v>
       </c>
       <c r="B98" t="str">
         <v>1 month ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=4eqzUNO-ONs</v>
+        <v>https://www.youtube.com/watch?v=f1Iqm16vWDQ</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-22</v>
@@ -3811,10 +3811,10 @@
         <v>1 month ago</v>
       </c>
       <c r="F98" t="str">
-        <v>2:43</v>
+        <v>3:40</v>
       </c>
       <c r="G98" t="str">
-        <v>OneRepublic</v>
+        <v>Within Temptation</v>
       </c>
       <c r="H98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3826,18 +3826,18 @@
         <v/>
       </c>
       <c r="K98" t="str">
-        <v>OneRepublic - Give Me Something (for Arknights Endfield) (Official Audio) - OneRepublic</v>
+        <v>Within Temptation - Ice Queen (Acoustic) | 2025 Reimagined Edition - Within Temptation</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Passenger | The Road Is Long</v>
+        <v>OneRepublic - Give Me Something (for Arknights Endfield) (Official Audio)</v>
       </c>
       <c r="B99" t="str">
         <v>1 month ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=oi4aTOc-IX4</v>
+        <v>https://www.youtube.com/watch?v=4eqzUNO-ONs</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-22</v>
@@ -3846,10 +3846,10 @@
         <v>1 month ago</v>
       </c>
       <c r="F99" t="str">
-        <v>4:01</v>
+        <v>2:43</v>
       </c>
       <c r="G99" t="str">
-        <v>Passenger</v>
+        <v>OneRepublic</v>
       </c>
       <c r="H99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3861,18 +3861,18 @@
         <v/>
       </c>
       <c r="K99" t="str">
-        <v>Passenger | The Road Is Long - Passenger</v>
+        <v>OneRepublic - Give Me Something (for Arknights Endfield) (Official Audio) - OneRepublic</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Black Honey - Carroll Avenue (Live at RAK)</v>
+        <v>Passenger | The Road Is Long</v>
       </c>
       <c r="B100" t="str">
         <v>1 month ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=LPXTE3a6QrM</v>
+        <v>https://www.youtube.com/watch?v=oi4aTOc-IX4</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-22</v>
@@ -3881,10 +3881,10 @@
         <v>1 month ago</v>
       </c>
       <c r="F100" t="str">
-        <v>3:19</v>
+        <v>4:01</v>
       </c>
       <c r="G100" t="str">
-        <v>Black Honey</v>
+        <v>Passenger</v>
       </c>
       <c r="H100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3896,18 +3896,18 @@
         <v/>
       </c>
       <c r="K100" t="str">
-        <v>Black Honey - Carroll Avenue (Live at RAK) - Black Honey</v>
+        <v>Passenger | The Road Is Long - Passenger</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Bastille - SAVE MY SOUL (Piano Version)</v>
+        <v>Black Honey - Carroll Avenue (Live at RAK)</v>
       </c>
       <c r="B101" t="str">
         <v>1 month ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=paLJCQy5j-I</v>
+        <v>https://www.youtube.com/watch?v=LPXTE3a6QrM</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-22</v>
@@ -3916,10 +3916,10 @@
         <v>1 month ago</v>
       </c>
       <c r="F101" t="str">
-        <v>2:41</v>
+        <v>3:19</v>
       </c>
       <c r="G101" t="str">
-        <v>BASTILLEvideos</v>
+        <v>Black Honey</v>
       </c>
       <c r="H101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3931,7 +3931,7 @@
         <v/>
       </c>
       <c r="K101" t="str">
-        <v>Bastille - SAVE MY SOUL (Piano Version) - BASTILLEvideos</v>
+        <v>Black Honey - Carroll Avenue (Live at RAK) - Black Honey</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:L101"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -413,7 +413,7 @@
         <v>תאריך סריקה</v>
       </c>
       <c r="E1" t="str">
-        <v>תיאור</v>
+        <v>שעה</v>
       </c>
       <c r="F1" t="str">
         <v>משך</v>
@@ -448,24 +448,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
         <v>5 hours ago</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>2:59</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <v>Lana Lubany</v>
       </c>
-      <c r="H2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I2" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
       </c>
       <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
         <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
@@ -483,24 +486,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
         <v>11 hours ago</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
         <v>4:21</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v>DEF LEPPARD</v>
       </c>
-      <c r="H3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I3" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
         <v/>
       </c>
       <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
         <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
@@ -518,24 +524,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
         <v>1 day ago</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
         <v>4:09</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>Dermot Kennedy</v>
       </c>
-      <c r="H4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I4" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
         <v/>
       </c>
       <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
         <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
@@ -553,24 +562,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
         <v>1 day ago</v>
       </c>
-      <c r="F5" t="str">
+      <c r="G5" t="str">
         <v>2:34</v>
       </c>
-      <c r="G5" t="str">
+      <c r="H5" t="str">
         <v>Lauren Sanderson</v>
       </c>
-      <c r="H5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I5" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
         <v/>
       </c>
       <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
         <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
@@ -588,24 +600,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
         <v>2 days ago</v>
       </c>
-      <c r="F6" t="str">
+      <c r="G6" t="str">
         <v>3:10</v>
       </c>
-      <c r="G6" t="str">
+      <c r="H6" t="str">
         <v>Olivia Dean</v>
       </c>
-      <c r="H6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I6" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
         <v/>
       </c>
       <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
         <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
@@ -623,24 +638,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
         <v>2 days ago</v>
       </c>
-      <c r="F7" t="str">
+      <c r="G7" t="str">
         <v>3:21</v>
       </c>
-      <c r="G7" t="str">
+      <c r="H7" t="str">
         <v>David Guetta and Tones And I</v>
       </c>
-      <c r="H7" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I7" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
         <v/>
       </c>
       <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
@@ -658,24 +676,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
         <v>2 days ago</v>
       </c>
-      <c r="F8" t="str">
+      <c r="G8" t="str">
         <v>3:06</v>
       </c>
-      <c r="G8" t="str">
+      <c r="H8" t="str">
         <v>The Avett Brothers</v>
       </c>
-      <c r="H8" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I8" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
         <v/>
       </c>
       <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
         <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
@@ -693,24 +714,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
         <v>2 days ago</v>
       </c>
-      <c r="F9" t="str">
+      <c r="G9" t="str">
         <v>3:21</v>
       </c>
-      <c r="G9" t="str">
+      <c r="H9" t="str">
         <v>Jordana Bryant</v>
       </c>
-      <c r="H9" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I9" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
         <v/>
       </c>
       <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
         <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
@@ -728,24 +752,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
         <v>2 days ago</v>
       </c>
-      <c r="F10" t="str">
+      <c r="G10" t="str">
         <v>7:21</v>
       </c>
-      <c r="G10" t="str">
+      <c r="H10" t="str">
         <v>Katy Perry</v>
       </c>
-      <c r="H10" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I10" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
         <v/>
       </c>
       <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
         <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
@@ -763,24 +790,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
         <v>3 days ago</v>
       </c>
-      <c r="F11" t="str">
+      <c r="G11" t="str">
         <v>3:17</v>
       </c>
-      <c r="G11" t="str">
+      <c r="H11" t="str">
         <v>Lauren Watkins</v>
       </c>
-      <c r="H11" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I11" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
         <v/>
       </c>
       <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
         <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
@@ -798,24 +828,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
         <v>4 days ago</v>
       </c>
-      <c r="F12" t="str">
+      <c r="G12" t="str">
         <v>3:45</v>
       </c>
-      <c r="G12" t="str">
+      <c r="H12" t="str">
         <v>Tones And I</v>
       </c>
-      <c r="H12" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I12" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
         <v/>
       </c>
       <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
         <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
@@ -833,24 +866,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
         <v>4 days ago</v>
       </c>
-      <c r="F13" t="str">
+      <c r="G13" t="str">
         <v>3:57</v>
       </c>
-      <c r="G13" t="str">
+      <c r="H13" t="str">
         <v>Ashleigh Dallas</v>
       </c>
-      <c r="H13" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I13" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
         <v/>
       </c>
       <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
         <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
@@ -868,24 +904,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
         <v>6 days ago</v>
       </c>
-      <c r="F14" t="str">
+      <c r="G14" t="str">
         <v>3:03</v>
       </c>
-      <c r="G14" t="str">
+      <c r="H14" t="str">
         <v>Charlie Puth</v>
       </c>
-      <c r="H14" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I14" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
         <v/>
       </c>
       <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
         <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
@@ -903,24 +942,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
         <v>6 days ago</v>
       </c>
-      <c r="F15" t="str">
+      <c r="G15" t="str">
         <v>4:27</v>
       </c>
-      <c r="G15" t="str">
+      <c r="H15" t="str">
         <v>Chappell Roan</v>
       </c>
-      <c r="H15" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I15" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
         <v/>
       </c>
       <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
         <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
@@ -938,24 +980,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
         <v>6 days ago</v>
       </c>
-      <c r="F16" t="str">
+      <c r="G16" t="str">
         <v>4:34</v>
       </c>
-      <c r="G16" t="str">
+      <c r="H16" t="str">
         <v>Armik</v>
       </c>
-      <c r="H16" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I16" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
         <v/>
       </c>
       <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
         <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
@@ -973,24 +1018,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
         <v>6 days ago</v>
       </c>
-      <c r="F17" t="str">
+      <c r="G17" t="str">
         <v>2:54</v>
       </c>
-      <c r="G17" t="str">
+      <c r="H17" t="str">
         <v>LØLØ</v>
       </c>
-      <c r="H17" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I17" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
         <v/>
       </c>
       <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
         <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
@@ -1008,24 +1056,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
         <v>6 days ago</v>
       </c>
-      <c r="F18" t="str">
+      <c r="G18" t="str">
         <v>3:25</v>
       </c>
-      <c r="G18" t="str">
+      <c r="H18" t="str">
         <v>Tenille Townes</v>
       </c>
-      <c r="H18" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I18" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
         <v/>
       </c>
       <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
         <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
@@ -1043,24 +1094,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
         <v>6 days ago</v>
       </c>
-      <c r="F19" t="str">
+      <c r="G19" t="str">
         <v>2:01</v>
       </c>
-      <c r="G19" t="str">
+      <c r="H19" t="str">
         <v>Alan Walker</v>
       </c>
-      <c r="H19" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I19" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
         <v/>
       </c>
       <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
         <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
@@ -1078,24 +1132,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
         <v>6 days ago</v>
       </c>
-      <c r="F20" t="str">
+      <c r="G20" t="str">
         <v>2:25</v>
       </c>
-      <c r="G20" t="str">
+      <c r="H20" t="str">
         <v>Charli xcx</v>
       </c>
-      <c r="H20" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I20" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
         <v/>
       </c>
       <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
         <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
@@ -1113,24 +1170,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
         <v>6 days ago</v>
       </c>
-      <c r="F21" t="str">
+      <c r="G21" t="str">
         <v>1:14</v>
       </c>
-      <c r="G21" t="str">
+      <c r="H21" t="str">
         <v>Labrinth</v>
       </c>
-      <c r="H21" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I21" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
         <v/>
       </c>
       <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
         <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
@@ -1148,24 +1208,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
         <v>6 days ago</v>
       </c>
-      <c r="F22" t="str">
+      <c r="G22" t="str">
         <v>2:59</v>
       </c>
-      <c r="G22" t="str">
+      <c r="H22" t="str">
         <v>Charlie Puth</v>
       </c>
-      <c r="H22" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I22" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
         <v/>
       </c>
       <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
         <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
@@ -1183,24 +1246,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
         <v>6 days ago</v>
       </c>
-      <c r="F23" t="str">
+      <c r="G23" t="str">
         <v>2:29</v>
       </c>
-      <c r="G23" t="str">
+      <c r="H23" t="str">
         <v>Girl Tones</v>
       </c>
-      <c r="H23" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I23" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
         <v/>
       </c>
       <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
         <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
@@ -1218,24 +1284,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
         <v>6 days ago</v>
       </c>
-      <c r="F24" t="str">
+      <c r="G24" t="str">
         <v>2:34</v>
       </c>
-      <c r="G24" t="str">
+      <c r="H24" t="str">
         <v>Jagwar Twin</v>
       </c>
-      <c r="H24" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I24" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
         <v/>
       </c>
       <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
         <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
@@ -1253,24 +1322,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
         <v>6 days ago</v>
       </c>
-      <c r="F25" t="str">
+      <c r="G25" t="str">
         <v>3:48</v>
       </c>
-      <c r="G25" t="str">
+      <c r="H25" t="str">
         <v>Caroline Jones</v>
       </c>
-      <c r="H25" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I25" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
         <v/>
       </c>
       <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
         <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
@@ -1288,24 +1360,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
         <v>6 days ago</v>
       </c>
-      <c r="F26" t="str">
+      <c r="G26" t="str">
         <v>3:32</v>
       </c>
-      <c r="G26" t="str">
+      <c r="H26" t="str">
         <v>The Beaches</v>
       </c>
-      <c r="H26" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I26" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
         <v/>
       </c>
       <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
         <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
@@ -1323,24 +1398,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
         <v>6 days ago</v>
       </c>
-      <c r="F27" t="str">
+      <c r="G27" t="str">
         <v>3:49</v>
       </c>
-      <c r="G27" t="str">
+      <c r="H27" t="str">
         <v>Dolly Parton</v>
       </c>
-      <c r="H27" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I27" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
         <v/>
       </c>
       <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
         <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
@@ -1358,24 +1436,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
         <v>6 days ago</v>
       </c>
-      <c r="F28" t="str">
+      <c r="G28" t="str">
         <v>4:28</v>
       </c>
-      <c r="G28" t="str">
+      <c r="H28" t="str">
         <v>Madison Beer</v>
       </c>
-      <c r="H28" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I28" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
         <v/>
       </c>
       <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
         <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
@@ -1393,24 +1474,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
         <v>6 days ago</v>
       </c>
-      <c r="F29" t="str">
+      <c r="G29" t="str">
         <v>3:37</v>
       </c>
-      <c r="G29" t="str">
+      <c r="H29" t="str">
         <v>Ty Myers</v>
       </c>
-      <c r="H29" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I29" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
         <v/>
       </c>
       <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
         <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
@@ -1428,24 +1512,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
         <v>6 days ago</v>
       </c>
-      <c r="F30" t="str">
+      <c r="G30" t="str">
         <v>3:35</v>
       </c>
-      <c r="G30" t="str">
+      <c r="H30" t="str">
         <v>Megan Moroney</v>
       </c>
-      <c r="H30" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I30" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
         <v/>
       </c>
       <c r="K30" t="str">
+        <v/>
+      </c>
+      <c r="L30" t="str">
         <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
@@ -1463,24 +1550,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
         <v>6 days ago</v>
       </c>
-      <c r="F31" t="str">
+      <c r="G31" t="str">
         <v>2:31</v>
       </c>
-      <c r="G31" t="str">
+      <c r="H31" t="str">
         <v>Julia Cole Music</v>
       </c>
-      <c r="H31" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I31" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
         <v/>
       </c>
       <c r="K31" t="str">
+        <v/>
+      </c>
+      <c r="L31" t="str">
         <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
@@ -1498,24 +1588,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
         <v>7 days ago</v>
       </c>
-      <c r="F32" t="str">
+      <c r="G32" t="str">
         <v>3:21</v>
       </c>
-      <c r="G32" t="str">
+      <c r="H32" t="str">
         <v>Lily Allen</v>
       </c>
-      <c r="H32" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I32" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
         <v/>
       </c>
       <c r="K32" t="str">
+        <v/>
+      </c>
+      <c r="L32" t="str">
         <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
@@ -1533,24 +1626,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
         <v>7 days ago</v>
       </c>
-      <c r="F33" t="str">
+      <c r="G33" t="str">
         <v>5:24</v>
       </c>
-      <c r="G33" t="str">
+      <c r="H33" t="str">
         <v>Nickless</v>
       </c>
-      <c r="H33" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I33" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
         <v/>
       </c>
       <c r="K33" t="str">
+        <v/>
+      </c>
+      <c r="L33" t="str">
         <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
@@ -1568,24 +1664,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
         <v>7 days ago</v>
       </c>
-      <c r="F34" t="str">
+      <c r="G34" t="str">
         <v>3:11</v>
       </c>
-      <c r="G34" t="str">
+      <c r="H34" t="str">
         <v>Peach PRC</v>
       </c>
-      <c r="H34" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I34" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
         <v/>
       </c>
       <c r="K34" t="str">
+        <v/>
+      </c>
+      <c r="L34" t="str">
         <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
@@ -1603,24 +1702,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
         <v>7 days ago</v>
       </c>
-      <c r="F35" t="str">
+      <c r="G35" t="str">
         <v>4:11</v>
       </c>
-      <c r="G35" t="str">
+      <c r="H35" t="str">
         <v>Ocean Alley</v>
       </c>
-      <c r="H35" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I35" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
         <v/>
       </c>
       <c r="K35" t="str">
+        <v/>
+      </c>
+      <c r="L35" t="str">
         <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
       </c>
     </row>
@@ -1638,24 +1740,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
         <v>7 days ago</v>
       </c>
-      <c r="F36" t="str">
+      <c r="G36" t="str">
         <v>3:31</v>
       </c>
-      <c r="G36" t="str">
+      <c r="H36" t="str">
         <v>OneRepublic</v>
       </c>
-      <c r="H36" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I36" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
         <v/>
       </c>
       <c r="K36" t="str">
+        <v/>
+      </c>
+      <c r="L36" t="str">
         <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
       </c>
     </row>
@@ -1673,24 +1778,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
         <v>8 days ago</v>
       </c>
-      <c r="F37" t="str">
+      <c r="G37" t="str">
         <v>4:16</v>
       </c>
-      <c r="G37" t="str">
+      <c r="H37" t="str">
         <v>Ty Myers</v>
       </c>
-      <c r="H37" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I37" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
         <v/>
       </c>
       <c r="K37" t="str">
+        <v/>
+      </c>
+      <c r="L37" t="str">
         <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
       </c>
     </row>
@@ -1708,24 +1816,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
         <v>8 days ago</v>
       </c>
-      <c r="F38" t="str">
+      <c r="G38" t="str">
         <v>4:42</v>
       </c>
-      <c r="G38" t="str">
+      <c r="H38" t="str">
         <v>JavaJazzFest</v>
       </c>
-      <c r="H38" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I38" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
         <v/>
       </c>
       <c r="K38" t="str">
+        <v/>
+      </c>
+      <c r="L38" t="str">
         <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
@@ -1743,24 +1854,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
         <v>9 days ago</v>
       </c>
-      <c r="F39" t="str">
+      <c r="G39" t="str">
         <v>2:47</v>
       </c>
-      <c r="G39" t="str">
+      <c r="H39" t="str">
         <v>Teo Glacier</v>
       </c>
-      <c r="H39" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I39" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
         <v/>
       </c>
       <c r="K39" t="str">
+        <v/>
+      </c>
+      <c r="L39" t="str">
         <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
       </c>
     </row>
@@ -1778,24 +1892,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
         <v>9 days ago</v>
       </c>
-      <c r="F40" t="str">
+      <c r="G40" t="str">
         <v>3:59</v>
       </c>
-      <c r="G40" t="str">
+      <c r="H40" t="str">
         <v>Brigitte Calls Me Baby</v>
       </c>
-      <c r="H40" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I40" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
         <v/>
       </c>
       <c r="K40" t="str">
+        <v/>
+      </c>
+      <c r="L40" t="str">
         <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
@@ -1813,24 +1930,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
         <v>10 days ago</v>
       </c>
-      <c r="F41" t="str">
+      <c r="G41" t="str">
         <v>4:09</v>
       </c>
-      <c r="G41" t="str">
+      <c r="H41" t="str">
         <v>Louie TheSinger</v>
       </c>
-      <c r="H41" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I41" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
         <v/>
       </c>
       <c r="K41" t="str">
+        <v/>
+      </c>
+      <c r="L41" t="str">
         <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
       </c>
     </row>
@@ -1848,24 +1968,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
         <v>13 days ago</v>
       </c>
-      <c r="F42" t="str">
+      <c r="G42" t="str">
         <v>3:24</v>
       </c>
-      <c r="G42" t="str">
+      <c r="H42" t="str">
         <v>ella jane</v>
       </c>
-      <c r="H42" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I42" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
         <v/>
       </c>
       <c r="K42" t="str">
+        <v/>
+      </c>
+      <c r="L42" t="str">
         <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
       </c>
     </row>
@@ -1883,24 +2006,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
         <v>13 days ago</v>
       </c>
-      <c r="F43" t="str">
+      <c r="G43" t="str">
         <v>3:14</v>
       </c>
-      <c r="G43" t="str">
+      <c r="H43" t="str">
         <v>Johnny Orlando</v>
       </c>
-      <c r="H43" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I43" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
         <v/>
       </c>
       <c r="K43" t="str">
+        <v/>
+      </c>
+      <c r="L43" t="str">
         <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
       </c>
     </row>
@@ -1918,30 +2044,33 @@
         <v>2026-01-22</v>
       </c>
       <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
         <v>13 days ago</v>
       </c>
-      <c r="F44" t="str">
+      <c r="G44" t="str">
         <v>3:32</v>
       </c>
-      <c r="G44" t="str">
+      <c r="H44" t="str">
         <v>Kungs</v>
       </c>
-      <c r="H44" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I44" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
         <v/>
       </c>
       <c r="K44" t="str">
+        <v/>
+      </c>
+      <c r="L44" t="str">
         <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) (Official Music Video)</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
       </c>
       <c r="B45" t="str">
         <v>13 days ago</v>
@@ -1953,25 +2082,28 @@
         <v>2026-01-22</v>
       </c>
       <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
         <v>13 days ago</v>
       </c>
-      <c r="F45" t="str">
+      <c r="G45" t="str">
         <v>3:15</v>
       </c>
-      <c r="G45" t="str">
+      <c r="H45" t="str">
         <v>Billy Raffoul</v>
       </c>
-      <c r="H45" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I45" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
         <v/>
       </c>
       <c r="K45" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) (Official Music Video) - Billy Raffoul</v>
+        <v/>
+      </c>
+      <c r="L45" t="str">
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
       </c>
     </row>
     <row r="46">
@@ -1988,24 +2120,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
         <v>13 days ago</v>
       </c>
-      <c r="F46" t="str">
+      <c r="G46" t="str">
         <v>3:03</v>
       </c>
-      <c r="G46" t="str">
+      <c r="H46" t="str">
         <v>NathanEvanss</v>
       </c>
-      <c r="H46" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I46" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
         <v/>
       </c>
       <c r="K46" t="str">
+        <v/>
+      </c>
+      <c r="L46" t="str">
         <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
       </c>
     </row>
@@ -2023,24 +2158,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
         <v>13 days ago</v>
       </c>
-      <c r="F47" t="str">
+      <c r="G47" t="str">
         <v>3:04</v>
       </c>
-      <c r="G47" t="str">
+      <c r="H47" t="str">
         <v>Stephen Sanchez</v>
       </c>
-      <c r="H47" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I47" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
         <v/>
       </c>
       <c r="K47" t="str">
+        <v/>
+      </c>
+      <c r="L47" t="str">
         <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
       </c>
     </row>
@@ -2058,24 +2196,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
         <v>13 days ago</v>
       </c>
-      <c r="F48" t="str">
+      <c r="G48" t="str">
         <v>3:33</v>
       </c>
-      <c r="G48" t="str">
+      <c r="H48" t="str">
         <v>Bruno Mars</v>
       </c>
-      <c r="H48" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I48" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
         <v/>
       </c>
       <c r="K48" t="str">
+        <v/>
+      </c>
+      <c r="L48" t="str">
         <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
@@ -2093,24 +2234,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
         <v>13 days ago</v>
       </c>
-      <c r="F49" t="str">
+      <c r="G49" t="str">
         <v>2:53</v>
       </c>
-      <c r="G49" t="str">
+      <c r="H49" t="str">
         <v>MAX</v>
       </c>
-      <c r="H49" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I49" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
         <v/>
       </c>
       <c r="K49" t="str">
+        <v/>
+      </c>
+      <c r="L49" t="str">
         <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
       </c>
     </row>
@@ -2128,24 +2272,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
         <v>13 days ago</v>
       </c>
-      <c r="F50" t="str">
+      <c r="G50" t="str">
         <v>4:11</v>
       </c>
-      <c r="G50" t="str">
+      <c r="H50" t="str">
         <v>Jessie J</v>
       </c>
-      <c r="H50" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I50" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
         <v/>
       </c>
       <c r="K50" t="str">
+        <v/>
+      </c>
+      <c r="L50" t="str">
         <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
       </c>
     </row>
@@ -2163,24 +2310,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
         <v>13 days ago</v>
       </c>
-      <c r="F51" t="str">
+      <c r="G51" t="str">
         <v>2:45</v>
       </c>
-      <c r="G51" t="str">
+      <c r="H51" t="str">
         <v>Claire Rosinkranz</v>
       </c>
-      <c r="H51" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I51" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
         <v/>
       </c>
       <c r="K51" t="str">
+        <v/>
+      </c>
+      <c r="L51" t="str">
         <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
       </c>
     </row>
@@ -2198,24 +2348,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
         <v>13 days ago</v>
       </c>
-      <c r="F52" t="str">
+      <c r="G52" t="str">
         <v>4:00</v>
       </c>
-      <c r="G52" t="str">
+      <c r="H52" t="str">
         <v>Brandon Lake and Cody Johnson</v>
       </c>
-      <c r="H52" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I52" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
         <v/>
       </c>
       <c r="K52" t="str">
+        <v/>
+      </c>
+      <c r="L52" t="str">
         <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
       </c>
     </row>
@@ -2233,24 +2386,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
         <v>13 days ago</v>
       </c>
-      <c r="F53" t="str">
+      <c r="G53" t="str">
         <v>3:27</v>
       </c>
-      <c r="G53" t="str">
+      <c r="H53" t="str">
         <v>The Kid LAROI.</v>
       </c>
-      <c r="H53" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I53" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
         <v/>
       </c>
       <c r="K53" t="str">
+        <v/>
+      </c>
+      <c r="L53" t="str">
         <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
       </c>
     </row>
@@ -2268,24 +2424,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
         <v>2 weeks ago</v>
       </c>
-      <c r="F54" t="str">
+      <c r="G54" t="str">
         <v>3:25</v>
       </c>
-      <c r="G54" t="str">
+      <c r="H54" t="str">
         <v>Olivia Dean</v>
       </c>
-      <c r="H54" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I54" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
         <v/>
       </c>
       <c r="K54" t="str">
+        <v/>
+      </c>
+      <c r="L54" t="str">
         <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
       </c>
     </row>
@@ -2303,24 +2462,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
         <v>2 weeks ago</v>
       </c>
-      <c r="F55" t="str">
+      <c r="G55" t="str">
         <v>3:34</v>
       </c>
-      <c r="G55" t="str">
+      <c r="H55" t="str">
         <v>Demi Lovato</v>
       </c>
-      <c r="H55" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I55" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
         <v/>
       </c>
       <c r="K55" t="str">
+        <v/>
+      </c>
+      <c r="L55" t="str">
         <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
@@ -2338,24 +2500,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
         <v>2 weeks ago</v>
       </c>
-      <c r="F56" t="str">
+      <c r="G56" t="str">
         <v>3:17</v>
       </c>
-      <c r="G56" t="str">
+      <c r="H56" t="str">
         <v>Train</v>
       </c>
-      <c r="H56" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I56" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
         <v/>
       </c>
       <c r="K56" t="str">
+        <v/>
+      </c>
+      <c r="L56" t="str">
         <v>Train - Mittens (Live on TODAY) - Train</v>
       </c>
     </row>
@@ -2373,24 +2538,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
         <v>2 weeks ago</v>
       </c>
-      <c r="F57" t="str">
+      <c r="G57" t="str">
         <v>2:25</v>
       </c>
-      <c r="G57" t="str">
+      <c r="H57" t="str">
         <v>Joseph</v>
       </c>
-      <c r="H57" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I57" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
         <v/>
       </c>
       <c r="K57" t="str">
+        <v/>
+      </c>
+      <c r="L57" t="str">
         <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
       </c>
     </row>
@@ -2408,24 +2576,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
         <v>2 weeks ago</v>
       </c>
-      <c r="F58" t="str">
+      <c r="G58" t="str">
         <v>3:26</v>
       </c>
-      <c r="G58" t="str">
+      <c r="H58" t="str">
         <v>Demi Lovato</v>
       </c>
-      <c r="H58" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I58" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
         <v/>
       </c>
       <c r="K58" t="str">
+        <v/>
+      </c>
+      <c r="L58" t="str">
         <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
@@ -2443,24 +2614,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
         <v>2 weeks ago</v>
       </c>
-      <c r="F59" t="str">
+      <c r="G59" t="str">
         <v>4:46</v>
       </c>
-      <c r="G59" t="str">
+      <c r="H59" t="str">
         <v>Keith Urban</v>
       </c>
-      <c r="H59" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I59" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
         <v/>
       </c>
       <c r="K59" t="str">
+        <v/>
+      </c>
+      <c r="L59" t="str">
         <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
@@ -2478,24 +2652,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
         <v>2 weeks ago</v>
       </c>
-      <c r="F60" t="str">
+      <c r="G60" t="str">
         <v>3:24</v>
       </c>
-      <c r="G60" t="str">
+      <c r="H60" t="str">
         <v>Keith Urban</v>
       </c>
-      <c r="H60" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I60" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
         <v/>
       </c>
       <c r="K60" t="str">
+        <v/>
+      </c>
+      <c r="L60" t="str">
         <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
@@ -2513,24 +2690,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
         <v>2 weeks ago</v>
       </c>
-      <c r="F61" t="str">
+      <c r="G61" t="str">
         <v>2:52</v>
       </c>
-      <c r="G61" t="str">
+      <c r="H61" t="str">
         <v>Madonna</v>
       </c>
-      <c r="H61" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I61" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
         <v/>
       </c>
       <c r="K61" t="str">
+        <v/>
+      </c>
+      <c r="L61" t="str">
         <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
       </c>
     </row>
@@ -2548,24 +2728,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
         <v>2 weeks ago</v>
       </c>
-      <c r="F62" t="str">
+      <c r="G62" t="str">
         <v>2:06</v>
       </c>
-      <c r="G62" t="str">
+      <c r="H62" t="str">
         <v>Estas Tonne</v>
       </c>
-      <c r="H62" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I62" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
         <v/>
       </c>
       <c r="K62" t="str">
+        <v/>
+      </c>
+      <c r="L62" t="str">
         <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estas Tonne</v>
       </c>
     </row>
@@ -2583,24 +2766,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
         <v>2 weeks ago</v>
       </c>
-      <c r="F63" t="str">
+      <c r="G63" t="str">
         <v>3:09</v>
       </c>
-      <c r="G63" t="str">
+      <c r="H63" t="str">
         <v>Anna Graves</v>
       </c>
-      <c r="H63" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I63" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
         <v/>
       </c>
       <c r="K63" t="str">
+        <v/>
+      </c>
+      <c r="L63" t="str">
         <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
       </c>
     </row>
@@ -2618,24 +2804,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
         <v>2 weeks ago</v>
       </c>
-      <c r="F64" t="str">
+      <c r="G64" t="str">
         <v>5:11</v>
       </c>
-      <c r="G64" t="str">
+      <c r="H64" t="str">
         <v>Ocean Alley</v>
       </c>
-      <c r="H64" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I64" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
         <v/>
       </c>
       <c r="K64" t="str">
+        <v/>
+      </c>
+      <c r="L64" t="str">
         <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
       </c>
     </row>
@@ -2653,24 +2842,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
         <v>2 weeks ago</v>
       </c>
-      <c r="F65" t="str">
+      <c r="G65" t="str">
         <v>3:40</v>
       </c>
-      <c r="G65" t="str">
+      <c r="H65" t="str">
         <v>Zara Larsson</v>
       </c>
-      <c r="H65" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I65" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
         <v/>
       </c>
       <c r="K65" t="str">
+        <v/>
+      </c>
+      <c r="L65" t="str">
         <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
       </c>
     </row>
@@ -2688,24 +2880,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
         <v>2 weeks ago</v>
       </c>
-      <c r="F66" t="str">
+      <c r="G66" t="str">
         <v>3:49</v>
       </c>
-      <c r="G66" t="str">
+      <c r="H66" t="str">
         <v>Lauren Watkins</v>
       </c>
-      <c r="H66" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I66" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
         <v/>
       </c>
       <c r="K66" t="str">
+        <v/>
+      </c>
+      <c r="L66" t="str">
         <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
@@ -2723,24 +2918,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
         <v>2 weeks ago</v>
       </c>
-      <c r="F67" t="str">
+      <c r="G67" t="str">
         <v>3:42</v>
       </c>
-      <c r="G67" t="str">
+      <c r="H67" t="str">
         <v>Goo Goo Dolls</v>
       </c>
-      <c r="H67" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I67" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
         <v/>
       </c>
       <c r="K67" t="str">
+        <v/>
+      </c>
+      <c r="L67" t="str">
         <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
       </c>
     </row>
@@ -2758,24 +2956,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
         <v>2 weeks ago</v>
       </c>
-      <c r="F68" t="str">
+      <c r="G68" t="str">
         <v>5:11</v>
       </c>
-      <c r="G68" t="str">
+      <c r="H68" t="str">
         <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
-      <c r="H68" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I68" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
         <v/>
       </c>
       <c r="K68" t="str">
+        <v/>
+      </c>
+      <c r="L68" t="str">
         <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
@@ -2793,24 +2994,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
         <v>2 weeks ago</v>
       </c>
-      <c r="F69" t="str">
+      <c r="G69" t="str">
         <v>3:57</v>
       </c>
-      <c r="G69" t="str">
+      <c r="H69" t="str">
         <v>Lainey Wilson</v>
       </c>
-      <c r="H69" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I69" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
         <v/>
       </c>
       <c r="K69" t="str">
+        <v/>
+      </c>
+      <c r="L69" t="str">
         <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
       </c>
     </row>
@@ -2828,24 +3032,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
         <v>2 weeks ago</v>
       </c>
-      <c r="F70" t="str">
+      <c r="G70" t="str">
         <v>3:29</v>
       </c>
-      <c r="G70" t="str">
+      <c r="H70" t="str">
         <v>Grace Enger</v>
       </c>
-      <c r="H70" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I70" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
         <v/>
       </c>
       <c r="K70" t="str">
+        <v/>
+      </c>
+      <c r="L70" t="str">
         <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
       </c>
     </row>
@@ -2863,24 +3070,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E71" t="str">
+        <v/>
+      </c>
+      <c r="F71" t="str">
         <v>2 weeks ago</v>
       </c>
-      <c r="F71" t="str">
+      <c r="G71" t="str">
         <v>3:10</v>
       </c>
-      <c r="G71" t="str">
+      <c r="H71" t="str">
         <v>Alan Walker and 2 more</v>
       </c>
-      <c r="H71" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I71" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
         <v/>
       </c>
       <c r="K71" t="str">
+        <v/>
+      </c>
+      <c r="L71" t="str">
         <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
       </c>
     </row>
@@ -2898,24 +3108,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E72" t="str">
+        <v/>
+      </c>
+      <c r="F72" t="str">
         <v>2 weeks ago</v>
       </c>
-      <c r="F72" t="str">
+      <c r="G72" t="str">
         <v>4:04</v>
       </c>
-      <c r="G72" t="str">
+      <c r="H72" t="str">
         <v>Emilia Tarrant</v>
       </c>
-      <c r="H72" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I72" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
         <v/>
       </c>
       <c r="K72" t="str">
+        <v/>
+      </c>
+      <c r="L72" t="str">
         <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
       </c>
     </row>
@@ -2933,24 +3146,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E73" t="str">
+        <v/>
+      </c>
+      <c r="F73" t="str">
         <v>3 weeks ago</v>
       </c>
-      <c r="F73" t="str">
+      <c r="G73" t="str">
         <v>3:09</v>
       </c>
-      <c r="G73" t="str">
+      <c r="H73" t="str">
         <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
-      <c r="H73" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I73" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
         <v/>
       </c>
       <c r="K73" t="str">
+        <v/>
+      </c>
+      <c r="L73" t="str">
         <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
@@ -2968,24 +3184,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E74" t="str">
+        <v/>
+      </c>
+      <c r="F74" t="str">
         <v>3 weeks ago</v>
       </c>
-      <c r="F74" t="str">
+      <c r="G74" t="str">
         <v>2:27</v>
       </c>
-      <c r="G74" t="str">
+      <c r="H74" t="str">
         <v>Lauren Spencer Smith</v>
       </c>
-      <c r="H74" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I74" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
         <v/>
       </c>
       <c r="K74" t="str">
+        <v/>
+      </c>
+      <c r="L74" t="str">
         <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
@@ -3003,24 +3222,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E75" t="str">
+        <v/>
+      </c>
+      <c r="F75" t="str">
         <v>3 weeks ago</v>
       </c>
-      <c r="F75" t="str">
+      <c r="G75" t="str">
         <v>2:12</v>
       </c>
-      <c r="G75" t="str">
+      <c r="H75" t="str">
         <v>Maggie Lindemann</v>
       </c>
-      <c r="H75" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I75" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
         <v/>
       </c>
       <c r="K75" t="str">
+        <v/>
+      </c>
+      <c r="L75" t="str">
         <v>Maggie Lindemann - fate - Maggie Lindemann</v>
       </c>
     </row>
@@ -3038,24 +3260,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E76" t="str">
+        <v/>
+      </c>
+      <c r="F76" t="str">
         <v>3 weeks ago</v>
       </c>
-      <c r="F76" t="str">
+      <c r="G76" t="str">
         <v>4:44</v>
       </c>
-      <c r="G76" t="str">
+      <c r="H76" t="str">
         <v>Cliff Richard</v>
       </c>
-      <c r="H76" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I76" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
         <v/>
       </c>
       <c r="K76" t="str">
+        <v/>
+      </c>
+      <c r="L76" t="str">
         <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023) - Cliff Richard</v>
       </c>
     </row>
@@ -3073,24 +3298,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E77" t="str">
+        <v/>
+      </c>
+      <c r="F77" t="str">
         <v>3 weeks ago</v>
       </c>
-      <c r="F77" t="str">
+      <c r="G77" t="str">
         <v>1:00:09</v>
       </c>
-      <c r="G77" t="str">
+      <c r="H77" t="str">
         <v>Purple Disco Machine</v>
       </c>
-      <c r="H77" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I77" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
         <v/>
       </c>
       <c r="K77" t="str">
+        <v/>
+      </c>
+      <c r="L77" t="str">
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025 - Purple Disco Machine</v>
       </c>
     </row>
@@ -3108,24 +3336,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E78" t="str">
+        <v/>
+      </c>
+      <c r="F78" t="str">
         <v>3 weeks ago</v>
       </c>
-      <c r="F78" t="str">
+      <c r="G78" t="str">
         <v>4:15</v>
       </c>
-      <c r="G78" t="str">
+      <c r="H78" t="str">
         <v>RAYE</v>
       </c>
-      <c r="H78" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I78" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
         <v/>
       </c>
       <c r="K78" t="str">
+        <v/>
+      </c>
+      <c r="L78" t="str">
         <v>RAYE - Black Mascara. (Live at The Royal Albert Hall) - RAYE</v>
       </c>
     </row>
@@ -3143,24 +3374,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E79" t="str">
+        <v/>
+      </c>
+      <c r="F79" t="str">
         <v>3 weeks ago</v>
       </c>
-      <c r="F79" t="str">
+      <c r="G79" t="str">
         <v>4:07</v>
       </c>
-      <c r="G79" t="str">
+      <c r="H79" t="str">
         <v>Madison Cunningham</v>
       </c>
-      <c r="H79" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I79" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
         <v/>
       </c>
       <c r="K79" t="str">
+        <v/>
+      </c>
+      <c r="L79" t="str">
         <v>Madison Cunningham - My Full Name (Garden Session) - Madison Cunningham</v>
       </c>
     </row>
@@ -3178,24 +3412,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E80" t="str">
+        <v/>
+      </c>
+      <c r="F80" t="str">
         <v>3 weeks ago</v>
       </c>
-      <c r="F80" t="str">
+      <c r="G80" t="str">
         <v>3:10</v>
       </c>
-      <c r="G80" t="str">
+      <c r="H80" t="str">
         <v>Teddy Swims</v>
       </c>
-      <c r="H80" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I80" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
         <v/>
       </c>
       <c r="K80" t="str">
+        <v/>
+      </c>
+      <c r="L80" t="str">
         <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
@@ -3213,24 +3450,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E81" t="str">
+        <v/>
+      </c>
+      <c r="F81" t="str">
         <v>3 weeks ago</v>
       </c>
-      <c r="F81" t="str">
+      <c r="G81" t="str">
         <v>3:47</v>
       </c>
-      <c r="G81" t="str">
+      <c r="H81" t="str">
         <v>Christina Aguilera</v>
       </c>
-      <c r="H81" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I81" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
         <v/>
       </c>
       <c r="K81" t="str">
+        <v/>
+      </c>
+      <c r="L81" t="str">
         <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower) - Christina Aguilera</v>
       </c>
     </row>
@@ -3248,24 +3488,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E82" t="str">
+        <v/>
+      </c>
+      <c r="F82" t="str">
         <v>3 weeks ago</v>
       </c>
-      <c r="F82" t="str">
+      <c r="G82" t="str">
         <v>3:58</v>
       </c>
-      <c r="G82" t="str">
+      <c r="H82" t="str">
         <v>RAYE</v>
       </c>
-      <c r="H82" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I82" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
         <v/>
       </c>
       <c r="K82" t="str">
+        <v/>
+      </c>
+      <c r="L82" t="str">
         <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025) - RAYE</v>
       </c>
     </row>
@@ -3283,24 +3526,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E83" t="str">
+        <v/>
+      </c>
+      <c r="F83" t="str">
         <v>3 weeks ago</v>
       </c>
-      <c r="F83" t="str">
+      <c r="G83" t="str">
         <v>3:30</v>
       </c>
-      <c r="G83" t="str">
+      <c r="H83" t="str">
         <v>Dasha</v>
       </c>
-      <c r="H83" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I83" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
         <v/>
       </c>
       <c r="K83" t="str">
+        <v/>
+      </c>
+      <c r="L83" t="str">
         <v>Dasha - Here For The Party (Official Audio) - Dasha</v>
       </c>
     </row>
@@ -3318,24 +3564,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E84" t="str">
+        <v/>
+      </c>
+      <c r="F84" t="str">
         <v>4 weeks ago</v>
       </c>
-      <c r="F84" t="str">
+      <c r="G84" t="str">
         <v>51:49</v>
       </c>
-      <c r="G84" t="str">
+      <c r="H84" t="str">
         <v>Lady Gaga and YouTube</v>
       </c>
-      <c r="H84" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I84" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
         <v/>
       </c>
       <c r="K84" t="str">
+        <v/>
+      </c>
+      <c r="L84" t="str">
         <v>Lady Gaga in Harlequin Live: One Night Only - Lady Gaga and YouTube</v>
       </c>
     </row>
@@ -3353,24 +3602,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E85" t="str">
+        <v/>
+      </c>
+      <c r="F85" t="str">
         <v>4 weeks ago</v>
       </c>
-      <c r="F85" t="str">
+      <c r="G85" t="str">
         <v>3:53</v>
       </c>
-      <c r="G85" t="str">
+      <c r="H85" t="str">
         <v>Sabrina Carpenter</v>
       </c>
-      <c r="H85" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I85" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
         <v/>
       </c>
       <c r="K85" t="str">
+        <v/>
+      </c>
+      <c r="L85" t="str">
         <v>Sabrina Carpenter - Such A Funny Way (Official Lyric Video) - Sabrina Carpenter</v>
       </c>
     </row>
@@ -3388,24 +3640,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E86" t="str">
+        <v/>
+      </c>
+      <c r="F86" t="str">
         <v>4 weeks ago</v>
       </c>
-      <c r="F86" t="str">
+      <c r="G86" t="str">
         <v>3:56</v>
       </c>
-      <c r="G86" t="str">
+      <c r="H86" t="str">
         <v>Megan Moroney</v>
       </c>
-      <c r="H86" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I86" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
         <v/>
       </c>
       <c r="K86" t="str">
+        <v/>
+      </c>
+      <c r="L86" t="str">
         <v>Megan Moroney - Beautiful Things (Official Fan Video) - Megan Moroney</v>
       </c>
     </row>
@@ -3423,24 +3678,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E87" t="str">
+        <v/>
+      </c>
+      <c r="F87" t="str">
         <v>4 weeks ago</v>
       </c>
-      <c r="F87" t="str">
+      <c r="G87" t="str">
         <v>4:16</v>
       </c>
-      <c r="G87" t="str">
+      <c r="H87" t="str">
         <v>Jason Derulo</v>
       </c>
-      <c r="H87" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I87" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
         <v/>
       </c>
       <c r="K87" t="str">
+        <v/>
+      </c>
+      <c r="L87" t="str">
         <v>Jason Derulo - Miracle - Jason Derulo</v>
       </c>
     </row>
@@ -3458,24 +3716,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E88" t="str">
+        <v/>
+      </c>
+      <c r="F88" t="str">
         <v>4 weeks ago</v>
       </c>
-      <c r="F88" t="str">
+      <c r="G88" t="str">
         <v>3:29</v>
       </c>
-      <c r="G88" t="str">
+      <c r="H88" t="str">
         <v>Sananda Maitreya</v>
       </c>
-      <c r="H88" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I88" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
         <v/>
       </c>
       <c r="K88" t="str">
+        <v/>
+      </c>
+      <c r="L88" t="str">
         <v>Sananda Maitreya - Pretty Baby (Live) - Sananda Maitreya</v>
       </c>
     </row>
@@ -3493,24 +3754,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E89" t="str">
+        <v/>
+      </c>
+      <c r="F89" t="str">
         <v>4 weeks ago</v>
       </c>
-      <c r="F89" t="str">
+      <c r="G89" t="str">
         <v>3:25</v>
       </c>
-      <c r="G89" t="str">
+      <c r="H89" t="str">
         <v>Alan Walker and 2 more</v>
       </c>
-      <c r="H89" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I89" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
         <v/>
       </c>
       <c r="K89" t="str">
+        <v/>
+      </c>
+      <c r="L89" t="str">
         <v>Faded - 10th Anniversary (Performance Video) - Alan Walker and 2 more</v>
       </c>
     </row>
@@ -3528,24 +3792,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E90" t="str">
+        <v/>
+      </c>
+      <c r="F90" t="str">
         <v>4 weeks ago</v>
       </c>
-      <c r="F90" t="str">
+      <c r="G90" t="str">
         <v>4:06</v>
       </c>
-      <c r="G90" t="str">
+      <c r="H90" t="str">
         <v>Christina Aguilera</v>
       </c>
-      <c r="H90" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I90" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
         <v/>
       </c>
       <c r="K90" t="str">
+        <v/>
+      </c>
+      <c r="L90" t="str">
         <v>What Are You Doing New Year's Eve (Live from the Eiffel Tower - Official Lyric Video) - Christina Aguilera</v>
       </c>
     </row>
@@ -3563,24 +3830,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E91" t="str">
+        <v/>
+      </c>
+      <c r="F91" t="str">
         <v>4 weeks ago</v>
       </c>
-      <c r="F91" t="str">
+      <c r="G91" t="str">
         <v>4:03</v>
       </c>
-      <c r="G91" t="str">
+      <c r="H91" t="str">
         <v>Christina Aguilera</v>
       </c>
-      <c r="H91" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I91" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
         <v/>
       </c>
       <c r="K91" t="str">
+        <v/>
+      </c>
+      <c r="L91" t="str">
         <v>Have Yourself a Merry Little Christmas (Live from the Eiffel Tower - Official Lyric Video) - Christina Aguilera</v>
       </c>
     </row>
@@ -3598,24 +3868,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E92" t="str">
+        <v/>
+      </c>
+      <c r="F92" t="str">
         <v>1 year ago</v>
       </c>
-      <c r="F92" t="str">
+      <c r="G92" t="str">
         <v>4:11</v>
       </c>
-      <c r="G92" t="str">
+      <c r="H92" t="str">
         <v>Chris Rea Official</v>
       </c>
-      <c r="H92" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I92" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
         <v/>
       </c>
       <c r="K92" t="str">
+        <v/>
+      </c>
+      <c r="L92" t="str">
         <v>Chris Rea - Driving Home for Christmas - (Live on National Lottery Stars, 2000) - Chris Rea Official</v>
       </c>
     </row>
@@ -3633,24 +3906,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E93" t="str">
+        <v/>
+      </c>
+      <c r="F93" t="str">
         <v>1 month ago</v>
       </c>
-      <c r="F93" t="str">
+      <c r="G93" t="str">
         <v>4:08</v>
       </c>
-      <c r="G93" t="str">
+      <c r="H93" t="str">
         <v>Jessie J</v>
       </c>
-      <c r="H93" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I93" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
         <v/>
       </c>
       <c r="K93" t="str">
+        <v/>
+      </c>
+      <c r="L93" t="str">
         <v>Jessie J - I'll Never Know Why (The Royal Variety Performance 2025) - Jessie J</v>
       </c>
     </row>
@@ -3668,24 +3944,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
         <v>1 month ago</v>
       </c>
-      <c r="F94" t="str">
+      <c r="G94" t="str">
         <v>3:34</v>
       </c>
-      <c r="G94" t="str">
+      <c r="H94" t="str">
         <v>Craig David</v>
       </c>
-      <c r="H94" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I94" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
         <v/>
       </c>
       <c r="K94" t="str">
+        <v/>
+      </c>
+      <c r="L94" t="str">
         <v>Craig David - Walking Away (Official HD Video) - Craig David</v>
       </c>
     </row>
@@ -3703,24 +3982,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
         <v>1 month ago</v>
       </c>
-      <c r="F95" t="str">
+      <c r="G95" t="str">
         <v>4:37</v>
       </c>
-      <c r="G95" t="str">
+      <c r="H95" t="str">
         <v>Christina Aguilera</v>
       </c>
-      <c r="H95" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I95" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
         <v/>
       </c>
       <c r="K95" t="str">
+        <v/>
+      </c>
+      <c r="L95" t="str">
         <v>Christina Aguilera, Yseult - Ave Maria (Live from the Eiffel Tower - Official Video) - Christina Aguilera</v>
       </c>
     </row>
@@ -3738,24 +4020,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
         <v>1 month ago</v>
       </c>
-      <c r="F96" t="str">
+      <c r="G96" t="str">
         <v>6:27</v>
       </c>
-      <c r="G96" t="str">
+      <c r="H96" t="str">
         <v>Shawn Mendes and Niall Horan</v>
       </c>
-      <c r="H96" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I96" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
         <v/>
       </c>
       <c r="K96" t="str">
+        <v/>
+      </c>
+      <c r="L96" t="str">
         <v>Shawn Mendes &amp; Niall Horan - This Town (Live from London) - Shawn Mendes and Niall Horan</v>
       </c>
     </row>
@@ -3773,24 +4058,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
         <v>1 month ago</v>
       </c>
-      <c r="F97" t="str">
+      <c r="G97" t="str">
         <v>2:07</v>
       </c>
-      <c r="G97" t="str">
+      <c r="H97" t="str">
         <v>DisneyMusicVEVO</v>
       </c>
-      <c r="H97" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I97" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
         <v/>
       </c>
       <c r="K97" t="str">
+        <v/>
+      </c>
+      <c r="L97" t="str">
         <v>Shakira - Zoo (From "Zootopia 2") - DisneyMusicVEVO</v>
       </c>
     </row>
@@ -3808,24 +4096,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
         <v>1 month ago</v>
       </c>
-      <c r="F98" t="str">
+      <c r="G98" t="str">
         <v>3:40</v>
       </c>
-      <c r="G98" t="str">
+      <c r="H98" t="str">
         <v>Within Temptation</v>
       </c>
-      <c r="H98" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I98" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J98" t="str">
         <v/>
       </c>
       <c r="K98" t="str">
+        <v/>
+      </c>
+      <c r="L98" t="str">
         <v>Within Temptation - Ice Queen (Acoustic) | 2025 Reimagined Edition - Within Temptation</v>
       </c>
     </row>
@@ -3843,24 +4134,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E99" t="str">
+        <v/>
+      </c>
+      <c r="F99" t="str">
         <v>1 month ago</v>
       </c>
-      <c r="F99" t="str">
+      <c r="G99" t="str">
         <v>2:43</v>
       </c>
-      <c r="G99" t="str">
+      <c r="H99" t="str">
         <v>OneRepublic</v>
       </c>
-      <c r="H99" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I99" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J99" t="str">
         <v/>
       </c>
       <c r="K99" t="str">
+        <v/>
+      </c>
+      <c r="L99" t="str">
         <v>OneRepublic - Give Me Something (for Arknights Endfield) (Official Audio) - OneRepublic</v>
       </c>
     </row>
@@ -3878,24 +4172,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
         <v>1 month ago</v>
       </c>
-      <c r="F100" t="str">
+      <c r="G100" t="str">
         <v>4:01</v>
       </c>
-      <c r="G100" t="str">
+      <c r="H100" t="str">
         <v>Passenger</v>
       </c>
-      <c r="H100" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I100" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J100" t="str">
         <v/>
       </c>
       <c r="K100" t="str">
+        <v/>
+      </c>
+      <c r="L100" t="str">
         <v>Passenger | The Road Is Long - Passenger</v>
       </c>
     </row>
@@ -3913,30 +4210,33 @@
         <v>2026-01-22</v>
       </c>
       <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
         <v>1 month ago</v>
       </c>
-      <c r="F101" t="str">
+      <c r="G101" t="str">
         <v>3:19</v>
       </c>
-      <c r="G101" t="str">
+      <c r="H101" t="str">
         <v>Black Honey</v>
       </c>
-      <c r="H101" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
       <c r="I101" t="str">
-        <v/>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J101" t="str">
         <v/>
       </c>
       <c r="K101" t="str">
+        <v/>
+      </c>
+      <c r="L101" t="str">
         <v>Black Honey - Carroll Avenue (Live at RAK) - Black Honey</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K101"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L101"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>2:59</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -477,7 +477,7 @@
         <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:21</v>
@@ -743,7 +743,7 @@
         <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>7:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,19 +439,19 @@
         <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>6 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>6 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>2:59</v>
@@ -477,19 +477,19 @@
         <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>12 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>12 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:21</v>
@@ -521,7 +521,7 @@
         <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -857,19 +857,19 @@
         <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B13" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>3:57</v>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1541,19 +1541,19 @@
         <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>2:31</v>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1731,19 +1731,19 @@
         <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B36" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>3:31</v>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=R2k_wPsAHKQ</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=wo9yPPCh75Q</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=ND6maRwmzHk</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=9jMMOYr-VhE</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=o2F-QmqdNtI</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=5-6cEVLqE90</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=ivPSbcEMwCs</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=tYpOHbXFnm0</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=rSO9oYUnO2k</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=c231tCsQalU</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=oaJKUCgSSkc</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=0Gxu80LxI0w</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=7sjshHJwkOE</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=yv1c5G5HZt8</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=EXVg23U3NRw</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=Bpb67fSUzEQ</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=gkwb6kZloLA</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=Jckb3dnS5fw</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=DPA8v4YS8AY</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=v8Yu21pEbqw</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=sq2u9Cfn2B8</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=Ea2DSMNIK5w</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=kCIf6yaJisQ</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=f1Iqm16vWDQ</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=4eqzUNO-ONs</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=oi4aTOc-IX4</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=LPXTE3a6QrM</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>2:59</v>
@@ -477,7 +477,7 @@
         <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:21</v>
@@ -553,7 +553,7 @@
         <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:34</v>
@@ -1921,7 +1921,7 @@
         <v>Louie TheSinger "Texas Gold" Official Music Video</v>
       </c>
       <c r="B41" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>4:09</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>2:59</v>
@@ -477,7 +477,7 @@
         <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:21</v>
@@ -667,7 +667,7 @@
         <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:06</v>
@@ -705,7 +705,7 @@
         <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>3:21</v>
@@ -1123,7 +1123,7 @@
         <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>2:25</v>
@@ -1161,7 +1161,7 @@
         <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B21" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>1:14</v>
@@ -1199,7 +1199,7 @@
         <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B22" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>2:59</v>
@@ -1237,7 +1237,7 @@
         <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B23" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>2:29</v>
@@ -1275,7 +1275,7 @@
         <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B24" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>2:34</v>
@@ -1313,7 +1313,7 @@
         <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>3:48</v>
@@ -1351,7 +1351,7 @@
         <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B26" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>3:32</v>
@@ -1389,7 +1389,7 @@
         <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B27" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>3:49</v>
@@ -1427,7 +1427,7 @@
         <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>4:28</v>
@@ -1465,7 +1465,7 @@
         <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>3:37</v>
@@ -1503,7 +1503,7 @@
         <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>3:35</v>
@@ -1693,7 +1693,7 @@
         <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
       </c>
       <c r="B35" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>4:11</v>
@@ -1883,7 +1883,7 @@
         <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>3:59</v>
@@ -2187,7 +2187,7 @@
         <v>Bruno Mars - I Just Might [Official Music Video]</v>
       </c>
       <c r="B48" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G48" t="str">
         <v>3:33</v>
@@ -2225,7 +2225,7 @@
         <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
       </c>
       <c r="B49" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G49" t="str">
         <v>2:53</v>
@@ -2263,7 +2263,7 @@
         <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G50" t="str">
         <v>4:11</v>
@@ -2301,7 +2301,7 @@
         <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G51" t="str">
         <v>2:45</v>
@@ -2339,7 +2339,7 @@
         <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G52" t="str">
         <v>4:00</v>
@@ -2377,7 +2377,7 @@
         <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
       </c>
       <c r="B53" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G53" t="str">
         <v>3:27</v>
@@ -3099,7 +3099,7 @@
         <v>Emilia Tarrant - Break Up With Myself</v>
       </c>
       <c r="B72" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G72" t="str">
         <v>4:04</v>
@@ -3517,7 +3517,7 @@
         <v>Dasha - Here For The Party (Official Audio)</v>
       </c>
       <c r="B83" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=rSO9oYUnO2k</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G83" t="str">
         <v>3:30</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>2:59</v>
@@ -477,7 +477,7 @@
         <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:21</v>
@@ -1655,7 +1655,7 @@
         <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B34" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>3:11</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>2:59</v>
@@ -477,7 +477,7 @@
         <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>2:59</v>
@@ -477,7 +477,7 @@
         <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:21</v>
@@ -1845,7 +1845,7 @@
         <v>Teo Glacier - Don't Mind (Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>2:47</v>
@@ -2070,7 +2070,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
         <v>13 days ago</v>
@@ -2103,7 +2103,7 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) (Official Music Video) - Billy Raffoul</v>
       </c>
     </row>
     <row r="46">

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>2:59</v>
@@ -477,7 +477,7 @@
         <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:21</v>
@@ -1085,7 +1085,7 @@
         <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>2:01</v>
@@ -1807,7 +1807,7 @@
         <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B38" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>4:42</v>
@@ -2070,7 +2070,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) (Official Music Video)</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
       </c>
       <c r="B45" t="str">
         <v>13 days ago</v>
@@ -2103,7 +2103,7 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) (Official Music Video) - Billy Raffoul</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
       </c>
     </row>
     <row r="46">

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>17 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-23</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>17 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v>2:59</v>
+        <v>4:10</v>
       </c>
       <c r="H2" t="str">
-        <v>Lana Lubany</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>23 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-23</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>23 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>4:21</v>
+        <v>3:26</v>
       </c>
       <c r="H3" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B4" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-23</v>
@@ -530,10 +530,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
-        <v>4:09</v>
+        <v>2:56</v>
       </c>
       <c r="H4" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>2 days ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-23</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 days ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G5" t="str">
-        <v>2:34</v>
+        <v>2:56</v>
       </c>
       <c r="H5" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-23</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:10</v>
+        <v>4:01</v>
       </c>
       <c r="H6" t="str">
-        <v>Olivia Dean</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-23</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:21</v>
+        <v>3:05</v>
       </c>
       <c r="H7" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>3 days ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-23</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>3 days ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:06</v>
+        <v>2:27</v>
       </c>
       <c r="H8" t="str">
-        <v>The Avett Brothers</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>3 days ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-23</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>3 days ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:21</v>
+        <v>2:34</v>
       </c>
       <c r="H9" t="str">
-        <v>Jordana Bryant</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>3 days ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-23</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>3 days ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G10" t="str">
-        <v>7:21</v>
+        <v>3:13</v>
       </c>
       <c r="H10" t="str">
-        <v>Katy Perry</v>
+        <v>Ashley Kutcher</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B11" t="str">
-        <v>3 days ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-23</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>3 days ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:17</v>
+        <v>3:13</v>
       </c>
       <c r="H11" t="str">
-        <v>Lauren Watkins</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>4 days ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-23</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>4 days ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:45</v>
+        <v>3:08</v>
       </c>
       <c r="H12" t="str">
-        <v>Tones And I</v>
+        <v>CAIN</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B13" t="str">
-        <v>5 days ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-23</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>5 days ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:57</v>
+        <v>5:14</v>
       </c>
       <c r="H13" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>6 days ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-23</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>6 days ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:03</v>
+        <v>2:59</v>
       </c>
       <c r="H14" t="str">
-        <v>Charlie Puth</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-23</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
-        <v>4:27</v>
+        <v>4:21</v>
       </c>
       <c r="H15" t="str">
-        <v>Chappell Roan</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-23</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:34</v>
+        <v>4:09</v>
       </c>
       <c r="H16" t="str">
-        <v>Armik</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-23</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>2:54</v>
+        <v>2:34</v>
       </c>
       <c r="H17" t="str">
-        <v>LØLØ</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B18" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-23</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:25</v>
+        <v>3:10</v>
       </c>
       <c r="H18" t="str">
-        <v>Tenille Townes</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B19" t="str">
-        <v>7 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-23</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>7 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:01</v>
+        <v>3:21</v>
       </c>
       <c r="H19" t="str">
-        <v>Alan Walker</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-23</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>2:25</v>
+        <v>3:06</v>
       </c>
       <c r="H20" t="str">
-        <v>Charli xcx</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-23</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>1:14</v>
+        <v>3:21</v>
       </c>
       <c r="H21" t="str">
-        <v>Labrinth</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B22" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-23</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>2:59</v>
+        <v>7:21</v>
       </c>
       <c r="H22" t="str">
-        <v>Charlie Puth</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B23" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-23</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>2:29</v>
+        <v>3:17</v>
       </c>
       <c r="H23" t="str">
-        <v>Girl Tones</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B24" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-23</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>2:34</v>
+        <v>3:45</v>
       </c>
       <c r="H24" t="str">
-        <v>Jagwar Twin</v>
+        <v>Tones And I</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B25" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-23</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:48</v>
+        <v>3:57</v>
       </c>
       <c r="H25" t="str">
-        <v>Caroline Jones</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-23</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:32</v>
+        <v>3:03</v>
       </c>
       <c r="H26" t="str">
-        <v>The Beaches</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B27" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-23</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:49</v>
+        <v>4:27</v>
       </c>
       <c r="H27" t="str">
-        <v>Dolly Parton</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B28" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-23</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:28</v>
+        <v>4:34</v>
       </c>
       <c r="H28" t="str">
-        <v>Madison Beer</v>
+        <v>Armik</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-23</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:37</v>
+        <v>2:54</v>
       </c>
       <c r="H29" t="str">
-        <v>Ty Myers</v>
+        <v>LØLØ</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B30" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-23</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:35</v>
+        <v>3:25</v>
       </c>
       <c r="H30" t="str">
-        <v>Megan Moroney</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-23</v>
@@ -1556,10 +1556,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:31</v>
+        <v>2:01</v>
       </c>
       <c r="H31" t="str">
-        <v>Julia Cole Music</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B32" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-23</v>
@@ -1594,10 +1594,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:21</v>
+        <v>2:25</v>
       </c>
       <c r="H32" t="str">
-        <v>Lily Allen</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B33" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-23</v>
@@ -1632,10 +1632,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>5:24</v>
+        <v>1:14</v>
       </c>
       <c r="H33" t="str">
-        <v>Nickless</v>
+        <v>Labrinth</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B34" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-23</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:11</v>
+        <v>2:59</v>
       </c>
       <c r="H34" t="str">
-        <v>Peach PRC</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B35" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-23</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>4:11</v>
+        <v>2:29</v>
       </c>
       <c r="H35" t="str">
-        <v>Ocean Alley</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B36" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-23</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:31</v>
+        <v>2:34</v>
       </c>
       <c r="H36" t="str">
-        <v>OneRepublic</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-23</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>4:16</v>
+        <v>3:48</v>
       </c>
       <c r="H37" t="str">
-        <v>Ty Myers</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B38" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-23</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>4:42</v>
+        <v>3:32</v>
       </c>
       <c r="H38" t="str">
-        <v>JavaJazzFest</v>
+        <v>The Beaches</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video)</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B39" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-23</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>2:47</v>
+        <v>3:49</v>
       </c>
       <c r="H39" t="str">
-        <v>Teo Glacier</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-23</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:59</v>
+        <v>4:28</v>
       </c>
       <c r="H40" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-23</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>4:09</v>
+        <v>3:37</v>
       </c>
       <c r="H41" t="str">
-        <v>Louie TheSinger</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ella jane - When I Was Beautiful (Live)</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-23</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:24</v>
+        <v>3:35</v>
       </c>
       <c r="H42" t="str">
-        <v>ella jane</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Johnny Orlando - Emilia (Official Video)</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-23</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:14</v>
+        <v>2:31</v>
       </c>
       <c r="H43" t="str">
-        <v>Johnny Orlando</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video)</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B44" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-23</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:32</v>
+        <v>3:21</v>
       </c>
       <c r="H44" t="str">
-        <v>Kungs</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B45" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-23</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:15</v>
+        <v>5:24</v>
       </c>
       <c r="H45" t="str">
-        <v>Billy Raffoul</v>
+        <v>Nickless</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
+        <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B46" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
+        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-23</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:03</v>
+        <v>3:11</v>
       </c>
       <c r="H46" t="str">
-        <v>NathanEvanss</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
+        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Stephen Sanchez - Sweet Love</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
       </c>
       <c r="B47" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
+        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-23</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:04</v>
+        <v>4:11</v>
       </c>
       <c r="H47" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video]</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B48" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
+        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-23</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:33</v>
+        <v>3:31</v>
       </c>
       <c r="H48" t="str">
-        <v>Bruno Mars</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
       </c>
       <c r="B49" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
+        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-23</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>2:53</v>
+        <v>4:16</v>
       </c>
       <c r="H49" t="str">
-        <v>MAX</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B50" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
+        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-23</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:11</v>
+        <v>4:42</v>
       </c>
       <c r="H50" t="str">
-        <v>Jessie J</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
+        <v>Teo Glacier - Don't Mind (Music Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
+        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-23</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:45</v>
+        <v>2:47</v>
       </c>
       <c r="H51" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Teo Glacier</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
+        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
+        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-23</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>4:00</v>
+        <v>3:59</v>
       </c>
       <c r="H52" t="str">
-        <v>Brandon Lake and Cody Johnson</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
       </c>
       <c r="B53" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
+        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-23</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:27</v>
+        <v>4:09</v>
       </c>
       <c r="H53" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Louie TheSinger</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
+        <v>ella jane - When I Was Beautiful (Live)</v>
       </c>
       <c r="B54" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
+        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-23</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:25</v>
+        <v>3:24</v>
       </c>
       <c r="H54" t="str">
-        <v>Olivia Dean</v>
+        <v>ella jane</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
+        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Johnny Orlando - Emilia (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
+        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-23</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:34</v>
+        <v>3:14</v>
       </c>
       <c r="H55" t="str">
-        <v>Demi Lovato</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Train - Mittens (Live on TODAY)</v>
+        <v>Kungs, Theophilus London - Galaxy (official video)</v>
       </c>
       <c r="B56" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=R2k_wPsAHKQ</v>
+        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-23</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:17</v>
+        <v>3:32</v>
       </c>
       <c r="H56" t="str">
-        <v>Train</v>
+        <v>Kungs</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Train - Mittens (Live on TODAY) - Train</v>
+        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
       </c>
       <c r="B57" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
+        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-23</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>2:25</v>
+        <v>3:15</v>
       </c>
       <c r="H57" t="str">
-        <v>Joseph</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
+        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-23</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:26</v>
+        <v>3:03</v>
       </c>
       <c r="H58" t="str">
-        <v>Demi Lovato</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Stephen Sanchez - Sweet Love</v>
       </c>
       <c r="B59" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
+        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-23</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>4:46</v>
+        <v>3:04</v>
       </c>
       <c r="H59" t="str">
-        <v>Keith Urban</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Bruno Mars - I Just Might [Official Music Video]</v>
       </c>
       <c r="B60" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
+        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-23</v>
@@ -2658,10 +2658,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:24</v>
+        <v>3:33</v>
       </c>
       <c r="H60" t="str">
-        <v>Keith Urban</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
       </c>
       <c r="B61" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
+        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-23</v>
@@ -2696,10 +2696,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:52</v>
+        <v>2:53</v>
       </c>
       <c r="H61" t="str">
-        <v>Madonna</v>
+        <v>MAX</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
+        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-23</v>
@@ -2734,10 +2734,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
-        <v>2:06</v>
+        <v>4:11</v>
       </c>
       <c r="H62" t="str">
-        <v>Estas Tonne</v>
+        <v>Jessie J</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estas Tonne</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Anna Graves - Burn On (Official Music Video)</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
+        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-23</v>
@@ -2772,10 +2772,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:09</v>
+        <v>2:45</v>
       </c>
       <c r="H63" t="str">
-        <v>Anna Graves</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
+        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-23</v>
@@ -2810,10 +2810,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
-        <v>5:11</v>
+        <v>4:00</v>
       </c>
       <c r="H64" t="str">
-        <v>Ocean Alley</v>
+        <v>Brandon Lake and Cody Johnson</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
+        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-23</v>
@@ -2848,10 +2848,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:40</v>
+        <v>3:27</v>
       </c>
       <c r="H65" t="str">
-        <v>Zara Larsson</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
+        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-23</v>
@@ -2886,10 +2886,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:49</v>
+        <v>3:25</v>
       </c>
       <c r="H66" t="str">
-        <v>Lauren Watkins</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
+        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-23</v>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:42</v>
+        <v>3:34</v>
       </c>
       <c r="H67" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Train - Mittens (Live on TODAY)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
+        <v>https://www.youtube.com/watch?v=R2k_wPsAHKQ</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-23</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>5:11</v>
+        <v>3:17</v>
       </c>
       <c r="H68" t="str">
-        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Train</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Train - Mittens (Live on TODAY) - Train</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
+        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-23</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:57</v>
+        <v>2:25</v>
       </c>
       <c r="H69" t="str">
-        <v>Lainey Wilson</v>
+        <v>Joseph</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video)</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
+        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-23</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:29</v>
+        <v>3:26</v>
       </c>
       <c r="H70" t="str">
-        <v>Grace Enger</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video)</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
+        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-23</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:10</v>
+        <v>4:46</v>
       </c>
       <c r="H71" t="str">
-        <v>Alan Walker and 2 more</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Emilia Tarrant - Break Up With Myself</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B72" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
+        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-23</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>4:04</v>
+        <v>3:24</v>
       </c>
       <c r="H72" t="str">
-        <v>Emilia Tarrant</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026)</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
       </c>
       <c r="B73" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
+        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-23</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:09</v>
+        <v>2:52</v>
       </c>
       <c r="H73" t="str">
-        <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Madonna</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer)</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
       </c>
       <c r="B74" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
+        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-23</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:27</v>
+        <v>2:06</v>
       </c>
       <c r="H74" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Estas Tonne</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estas Tonne</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Maggie Lindemann - fate</v>
+        <v>Anna Graves - Burn On (Official Music Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
+        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-23</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:12</v>
+        <v>3:09</v>
       </c>
       <c r="H75" t="str">
-        <v>Maggie Lindemann</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Maggie Lindemann - fate - Maggie Lindemann</v>
+        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023)</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=wo9yPPCh75Q</v>
+        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-23</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>4:44</v>
+        <v>5:11</v>
       </c>
       <c r="H76" t="str">
-        <v>Cliff Richard</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023) - Cliff Richard</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
       </c>
       <c r="B77" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=ND6maRwmzHk</v>
+        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-23</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>1:00:09</v>
+        <v>3:40</v>
       </c>
       <c r="H77" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025 - Purple Disco Machine</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall)</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B78" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=9jMMOYr-VhE</v>
+        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-23</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>4:15</v>
+        <v>3:49</v>
       </c>
       <c r="H78" t="str">
-        <v>RAYE</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall) - RAYE</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Madison Cunningham - My Full Name (Garden Session)</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B79" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=o2F-QmqdNtI</v>
+        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-23</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>4:07</v>
+        <v>3:42</v>
       </c>
       <c r="H79" t="str">
-        <v>Madison Cunningham</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Madison Cunningham - My Full Name (Garden Session) - Madison Cunningham</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions)</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B80" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=5-6cEVLqE90</v>
+        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-23</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:10</v>
+        <v>5:11</v>
       </c>
       <c r="H80" t="str">
-        <v>Teddy Swims</v>
+        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower)</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
       </c>
       <c r="B81" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=ivPSbcEMwCs</v>
+        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-23</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:47</v>
+        <v>3:57</v>
       </c>
       <c r="H81" t="str">
-        <v>Christina Aguilera</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower) - Christina Aguilera</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025)</v>
+        <v>Grace Enger - All My Songs (Official Lyric Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=tYpOHbXFnm0</v>
+        <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-23</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:58</v>
+        <v>3:29</v>
       </c>
       <c r="H82" t="str">
-        <v>RAYE</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025) - RAYE</v>
+        <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Dasha - Here For The Party (Official Audio)</v>
+        <v>Alan Walker - Broken Strings (Official Music Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=rSO9oYUnO2k</v>
+        <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-23</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:30</v>
+        <v>3:10</v>
       </c>
       <c r="H83" t="str">
-        <v>Dasha</v>
+        <v>Alan Walker and 2 more</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Dasha - Here For The Party (Official Audio) - Dasha</v>
+        <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Lady Gaga in Harlequin Live: One Night Only</v>
+        <v>Emilia Tarrant - Break Up With Myself</v>
       </c>
       <c r="B84" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=c231tCsQalU</v>
+        <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-23</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>51:49</v>
+        <v>4:04</v>
       </c>
       <c r="H84" t="str">
-        <v>Lady Gaga and YouTube</v>
+        <v>Emilia Tarrant</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Lady Gaga in Harlequin Live: One Night Only - Lady Gaga and YouTube</v>
+        <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Sabrina Carpenter - Such A Funny Way (Official Lyric Video)</v>
+        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026)</v>
       </c>
       <c r="B85" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=oaJKUCgSSkc</v>
+        <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-23</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:53</v>
+        <v>3:09</v>
       </c>
       <c r="H85" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Sabrina Carpenter - Such A Funny Way (Official Lyric Video) - Sabrina Carpenter</v>
+        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Megan Moroney - Beautiful Things (Official Fan Video)</v>
+        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer)</v>
       </c>
       <c r="B86" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=0Gxu80LxI0w</v>
+        <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-23</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:56</v>
+        <v>2:27</v>
       </c>
       <c r="H86" t="str">
-        <v>Megan Moroney</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Megan Moroney - Beautiful Things (Official Fan Video) - Megan Moroney</v>
+        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Jason Derulo - Miracle</v>
+        <v>Maggie Lindemann - fate</v>
       </c>
       <c r="B87" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=7sjshHJwkOE</v>
+        <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-23</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>4:16</v>
+        <v>2:12</v>
       </c>
       <c r="H87" t="str">
-        <v>Jason Derulo</v>
+        <v>Maggie Lindemann</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Jason Derulo - Miracle - Jason Derulo</v>
+        <v>Maggie Lindemann - fate - Maggie Lindemann</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Sananda Maitreya - Pretty Baby (Live)</v>
+        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023)</v>
       </c>
       <c r="B88" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=yv1c5G5HZt8</v>
+        <v>https://www.youtube.com/watch?v=wo9yPPCh75Q</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-23</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:29</v>
+        <v>4:44</v>
       </c>
       <c r="H88" t="str">
-        <v>Sananda Maitreya</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Sananda Maitreya - Pretty Baby (Live) - Sananda Maitreya</v>
+        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023) - Cliff Richard</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Faded - 10th Anniversary (Performance Video)</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025</v>
       </c>
       <c r="B89" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=EXVg23U3NRw</v>
+        <v>https://www.youtube.com/watch?v=ND6maRwmzHk</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-23</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:25</v>
+        <v>1:00:09</v>
       </c>
       <c r="H89" t="str">
-        <v>Alan Walker and 2 more</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Faded - 10th Anniversary (Performance Video) - Alan Walker and 2 more</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>What Are You Doing New Year's Eve (Live from the Eiffel Tower - Official Lyric Video)</v>
+        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall)</v>
       </c>
       <c r="B90" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=Bpb67fSUzEQ</v>
+        <v>https://www.youtube.com/watch?v=9jMMOYr-VhE</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-23</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>4:06</v>
+        <v>4:15</v>
       </c>
       <c r="H90" t="str">
-        <v>Christina Aguilera</v>
+        <v>RAYE</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>What Are You Doing New Year's Eve (Live from the Eiffel Tower - Official Lyric Video) - Christina Aguilera</v>
+        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall) - RAYE</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Have Yourself a Merry Little Christmas (Live from the Eiffel Tower - Official Lyric Video)</v>
+        <v>Madison Cunningham - My Full Name (Garden Session)</v>
       </c>
       <c r="B91" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=gkwb6kZloLA</v>
+        <v>https://www.youtube.com/watch?v=o2F-QmqdNtI</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-23</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>4:03</v>
+        <v>4:07</v>
       </c>
       <c r="H91" t="str">
-        <v>Christina Aguilera</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Have Yourself a Merry Little Christmas (Live from the Eiffel Tower - Official Lyric Video) - Christina Aguilera</v>
+        <v>Madison Cunningham - My Full Name (Garden Session) - Madison Cunningham</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Chris Rea - Driving Home for Christmas - (Live on National Lottery Stars, 2000)</v>
+        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions)</v>
       </c>
       <c r="B92" t="str">
-        <v>1 year ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=Jckb3dnS5fw</v>
+        <v>https://www.youtube.com/watch?v=5-6cEVLqE90</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-23</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>1 year ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>4:11</v>
+        <v>3:10</v>
       </c>
       <c r="H92" t="str">
-        <v>Chris Rea Official</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Chris Rea - Driving Home for Christmas - (Live on National Lottery Stars, 2000) - Chris Rea Official</v>
+        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Jessie J - I'll Never Know Why (The Royal Variety Performance 2025)</v>
+        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower)</v>
       </c>
       <c r="B93" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=DPA8v4YS8AY</v>
+        <v>https://www.youtube.com/watch?v=ivPSbcEMwCs</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-23</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>4:08</v>
+        <v>3:47</v>
       </c>
       <c r="H93" t="str">
-        <v>Jessie J</v>
+        <v>Christina Aguilera</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Jessie J - I'll Never Know Why (The Royal Variety Performance 2025) - Jessie J</v>
+        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower) - Christina Aguilera</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Craig David - Walking Away (Official HD Video)</v>
+        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025)</v>
       </c>
       <c r="B94" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=v8Yu21pEbqw</v>
+        <v>https://www.youtube.com/watch?v=tYpOHbXFnm0</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-23</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:34</v>
+        <v>3:58</v>
       </c>
       <c r="H94" t="str">
-        <v>Craig David</v>
+        <v>RAYE</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Craig David - Walking Away (Official HD Video) - Craig David</v>
+        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025) - RAYE</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Christina Aguilera, Yseult - Ave Maria (Live from the Eiffel Tower - Official Video)</v>
+        <v>Dasha - Here For The Party (Official Audio)</v>
       </c>
       <c r="B95" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=sq2u9Cfn2B8</v>
+        <v>https://www.youtube.com/watch?v=rSO9oYUnO2k</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-23</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:37</v>
+        <v>3:30</v>
       </c>
       <c r="H95" t="str">
-        <v>Christina Aguilera</v>
+        <v>Dasha</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Christina Aguilera, Yseult - Ave Maria (Live from the Eiffel Tower - Official Video) - Christina Aguilera</v>
+        <v>Dasha - Here For The Party (Official Audio) - Dasha</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Shawn Mendes &amp; Niall Horan - This Town (Live from London)</v>
+        <v>Lady Gaga in Harlequin Live: One Night Only</v>
       </c>
       <c r="B96" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=Ea2DSMNIK5w</v>
+        <v>https://www.youtube.com/watch?v=c231tCsQalU</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-23</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>6:27</v>
+        <v>51:49</v>
       </c>
       <c r="H96" t="str">
-        <v>Shawn Mendes and Niall Horan</v>
+        <v>Lady Gaga and YouTube</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Shawn Mendes &amp; Niall Horan - This Town (Live from London) - Shawn Mendes and Niall Horan</v>
+        <v>Lady Gaga in Harlequin Live: One Night Only - Lady Gaga and YouTube</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Shakira - Zoo (From "Zootopia 2")</v>
+        <v>Sabrina Carpenter - Such A Funny Way (Official Lyric Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=kCIf6yaJisQ</v>
+        <v>https://www.youtube.com/watch?v=oaJKUCgSSkc</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-23</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>2:07</v>
+        <v>3:53</v>
       </c>
       <c r="H97" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Shakira - Zoo (From "Zootopia 2") - DisneyMusicVEVO</v>
+        <v>Sabrina Carpenter - Such A Funny Way (Official Lyric Video) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Within Temptation - Ice Queen (Acoustic) | 2025 Reimagined Edition</v>
+        <v>Megan Moroney - Beautiful Things (Official Fan Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=f1Iqm16vWDQ</v>
+        <v>https://www.youtube.com/watch?v=0Gxu80LxI0w</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-23</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:40</v>
+        <v>3:56</v>
       </c>
       <c r="H98" t="str">
-        <v>Within Temptation</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Within Temptation - Ice Queen (Acoustic) | 2025 Reimagined Edition - Within Temptation</v>
+        <v>Megan Moroney - Beautiful Things (Official Fan Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>OneRepublic - Give Me Something (for Arknights Endfield) (Official Audio)</v>
+        <v>Jason Derulo - Miracle</v>
       </c>
       <c r="B99" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=4eqzUNO-ONs</v>
+        <v>https://www.youtube.com/watch?v=7sjshHJwkOE</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-23</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>2:43</v>
+        <v>4:16</v>
       </c>
       <c r="H99" t="str">
-        <v>OneRepublic</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>OneRepublic - Give Me Something (for Arknights Endfield) (Official Audio) - OneRepublic</v>
+        <v>Jason Derulo - Miracle - Jason Derulo</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Passenger | The Road Is Long</v>
+        <v>Sananda Maitreya - Pretty Baby (Live)</v>
       </c>
       <c r="B100" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=oi4aTOc-IX4</v>
+        <v>https://www.youtube.com/watch?v=yv1c5G5HZt8</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-23</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>4:01</v>
+        <v>3:29</v>
       </c>
       <c r="H100" t="str">
-        <v>Passenger</v>
+        <v>Sananda Maitreya</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Passenger | The Road Is Long - Passenger</v>
+        <v>Sananda Maitreya - Pretty Baby (Live) - Sananda Maitreya</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Black Honey - Carroll Avenue (Live at RAK)</v>
+        <v>Faded - 10th Anniversary (Performance Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=LPXTE3a6QrM</v>
+        <v>https://www.youtube.com/watch?v=EXVg23U3NRw</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-23</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:19</v>
+        <v>3:25</v>
       </c>
       <c r="H101" t="str">
-        <v>Black Honey</v>
+        <v>Alan Walker and 2 more</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Black Honey - Carroll Avenue (Live at RAK) - Black Honey</v>
+        <v>Faded - 10th Anniversary (Performance Video) - Alan Walker and 2 more</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>6 hours ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-23</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>6 hours ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v>4:10</v>
+        <v>3:59</v>
       </c>
       <c r="H2" t="str">
-        <v>Parker McCollum</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Lyric Video)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B3" t="str">
-        <v>6 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-23</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>6 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>3:26</v>
+        <v>2:56</v>
       </c>
       <c r="H3" t="str">
-        <v>Matt Hansen</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Lyric Video) - Matt Hansen</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-23</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>2:56</v>
+        <v>3:46</v>
       </c>
       <c r="H4" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
+        <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B5" t="str">
-        <v>6 hours ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
+        <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-23</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>6 hours ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G5" t="str">
-        <v>2:56</v>
+        <v>2:47</v>
       </c>
       <c r="H5" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
+        <v>Dean Lewis - I Am Getting Well - Dean Lewis</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B6" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-23</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G6" t="str">
-        <v>4:01</v>
+        <v>4:37</v>
       </c>
       <c r="H6" t="str">
-        <v>Tauren Wells</v>
+        <v>Bella White</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-23</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:05</v>
+        <v>4:06</v>
       </c>
       <c r="H7" t="str">
-        <v>Maiah Manser</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B8" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-23</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G8" t="str">
-        <v>2:27</v>
+        <v>3:54</v>
       </c>
       <c r="H8" t="str">
-        <v>Taylor Austin Dye</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Chelsea Cutler - BAD (Official Video)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-23</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G9" t="str">
-        <v>2:34</v>
+        <v>4:10</v>
       </c>
       <c r="H9" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-23</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:13</v>
+        <v>3:26</v>
       </c>
       <c r="H10" t="str">
-        <v>Ashley Kutcher</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>6 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-23</v>
@@ -793,10 +793,10 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>6 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:13</v>
+        <v>2:56</v>
       </c>
       <c r="H11" t="str">
         <v>Louis Tomlinson</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-23</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:08</v>
+        <v>2:56</v>
       </c>
       <c r="H12" t="str">
-        <v>CAIN</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Harry Styles - Aperture (Official Audio)</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>11 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-23</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>11 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G13" t="str">
-        <v>5:14</v>
+        <v>4:01</v>
       </c>
       <c r="H13" t="str">
-        <v>Harry Styles</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>18 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-23</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>18 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:59</v>
+        <v>3:05</v>
       </c>
       <c r="H14" t="str">
-        <v>Lana Lubany</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>1 day ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-23</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1 day ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G15" t="str">
-        <v>4:21</v>
+        <v>2:27</v>
       </c>
       <c r="H15" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>1 day ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-23</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1 day ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:09</v>
+        <v>2:34</v>
       </c>
       <c r="H16" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>2 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-23</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G17" t="str">
-        <v>2:34</v>
+        <v>3:13</v>
       </c>
       <c r="H17" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Ashley Kutcher</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>2 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-23</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:10</v>
+        <v>3:13</v>
       </c>
       <c r="H18" t="str">
-        <v>Olivia Dean</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>2 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-23</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:21</v>
+        <v>3:08</v>
       </c>
       <c r="H19" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>CAIN</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>3 days ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-23</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>3 days ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:06</v>
+        <v>5:14</v>
       </c>
       <c r="H20" t="str">
-        <v>The Avett Brothers</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>3 days ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-23</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>3 days ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:21</v>
+        <v>2:59</v>
       </c>
       <c r="H21" t="str">
-        <v>Jordana Bryant</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-23</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G22" t="str">
-        <v>7:21</v>
+        <v>4:21</v>
       </c>
       <c r="H22" t="str">
-        <v>Katy Perry</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-23</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:17</v>
+        <v>4:09</v>
       </c>
       <c r="H23" t="str">
-        <v>Lauren Watkins</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-23</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:45</v>
+        <v>2:34</v>
       </c>
       <c r="H24" t="str">
-        <v>Tones And I</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B25" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-23</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:57</v>
+        <v>3:10</v>
       </c>
       <c r="H25" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B26" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-23</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:03</v>
+        <v>3:21</v>
       </c>
       <c r="H26" t="str">
-        <v>Charlie Puth</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-23</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:27</v>
+        <v>3:06</v>
       </c>
       <c r="H27" t="str">
-        <v>Chappell Roan</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-23</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:34</v>
+        <v>3:21</v>
       </c>
       <c r="H28" t="str">
-        <v>Armik</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B29" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-23</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:54</v>
+        <v>7:21</v>
       </c>
       <c r="H29" t="str">
-        <v>LØLØ</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B30" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-23</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:25</v>
+        <v>3:17</v>
       </c>
       <c r="H30" t="str">
-        <v>Tenille Townes</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B31" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-23</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:01</v>
+        <v>3:45</v>
       </c>
       <c r="H31" t="str">
-        <v>Alan Walker</v>
+        <v>Tones And I</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B32" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-23</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:25</v>
+        <v>3:57</v>
       </c>
       <c r="H32" t="str">
-        <v>Charli xcx</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-23</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>1:14</v>
+        <v>3:03</v>
       </c>
       <c r="H33" t="str">
-        <v>Labrinth</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B34" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-23</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>2:59</v>
+        <v>4:27</v>
       </c>
       <c r="H34" t="str">
-        <v>Charlie Puth</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B35" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-23</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>2:29</v>
+        <v>4:34</v>
       </c>
       <c r="H35" t="str">
-        <v>Girl Tones</v>
+        <v>Armik</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-23</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>2:34</v>
+        <v>2:54</v>
       </c>
       <c r="H36" t="str">
-        <v>Jagwar Twin</v>
+        <v>LØLØ</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B37" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-23</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:48</v>
+        <v>3:25</v>
       </c>
       <c r="H37" t="str">
-        <v>Caroline Jones</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B38" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-23</v>
@@ -1822,10 +1822,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:32</v>
+        <v>2:01</v>
       </c>
       <c r="H38" t="str">
-        <v>The Beaches</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B39" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-23</v>
@@ -1860,10 +1860,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:49</v>
+        <v>2:25</v>
       </c>
       <c r="H39" t="str">
-        <v>Dolly Parton</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B40" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-23</v>
@@ -1898,10 +1898,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>4:28</v>
+        <v>1:14</v>
       </c>
       <c r="H40" t="str">
-        <v>Madison Beer</v>
+        <v>Labrinth</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B41" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-23</v>
@@ -1936,10 +1936,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:37</v>
+        <v>2:59</v>
       </c>
       <c r="H41" t="str">
-        <v>Ty Myers</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B42" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-23</v>
@@ -1974,10 +1974,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:35</v>
+        <v>2:29</v>
       </c>
       <c r="H42" t="str">
-        <v>Megan Moroney</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B43" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-23</v>
@@ -2012,10 +2012,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:31</v>
+        <v>2:34</v>
       </c>
       <c r="H43" t="str">
-        <v>Julia Cole Music</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B44" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-23</v>
@@ -2050,10 +2050,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:21</v>
+        <v>3:48</v>
       </c>
       <c r="H44" t="str">
-        <v>Lily Allen</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B45" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-23</v>
@@ -2088,10 +2088,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>5:24</v>
+        <v>3:32</v>
       </c>
       <c r="H45" t="str">
-        <v>Nickless</v>
+        <v>The Beaches</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B46" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-23</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:11</v>
+        <v>3:49</v>
       </c>
       <c r="H46" t="str">
-        <v>Peach PRC</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-23</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>4:11</v>
+        <v>4:28</v>
       </c>
       <c r="H47" t="str">
-        <v>Ocean Alley</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-23</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:31</v>
+        <v>3:37</v>
       </c>
       <c r="H48" t="str">
-        <v>OneRepublic</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-23</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>4:16</v>
+        <v>3:35</v>
       </c>
       <c r="H49" t="str">
-        <v>Ty Myers</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-23</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:42</v>
+        <v>2:31</v>
       </c>
       <c r="H50" t="str">
-        <v>JavaJazzFest</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video)</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B51" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-23</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:47</v>
+        <v>3:21</v>
       </c>
       <c r="H51" t="str">
-        <v>Teo Glacier</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B52" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-23</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:59</v>
+        <v>5:24</v>
       </c>
       <c r="H52" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>Nickless</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
+        <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B53" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
+        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-23</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>4:09</v>
+        <v>3:11</v>
       </c>
       <c r="H53" t="str">
-        <v>Louie TheSinger</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
+        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ella jane - When I Was Beautiful (Live)</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
       </c>
       <c r="B54" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
+        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-23</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:24</v>
+        <v>4:11</v>
       </c>
       <c r="H54" t="str">
-        <v>ella jane</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Johnny Orlando - Emilia (Official Video)</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B55" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
+        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-23</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:14</v>
+        <v>3:31</v>
       </c>
       <c r="H55" t="str">
-        <v>Johnny Orlando</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video)</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
       </c>
       <c r="B56" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
+        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-23</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:32</v>
+        <v>4:16</v>
       </c>
       <c r="H56" t="str">
-        <v>Kungs</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B57" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
+        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-23</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:15</v>
+        <v>4:42</v>
       </c>
       <c r="H57" t="str">
-        <v>Billy Raffoul</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
+        <v>Teo Glacier - Don't Mind (Music Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
+        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-23</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:03</v>
+        <v>2:47</v>
       </c>
       <c r="H58" t="str">
-        <v>NathanEvanss</v>
+        <v>Teo Glacier</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
+        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Stephen Sanchez - Sweet Love</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
+        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-23</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:04</v>
+        <v>3:59</v>
       </c>
       <c r="H59" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video]</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
       </c>
       <c r="B60" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
+        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-23</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:33</v>
+        <v>4:09</v>
       </c>
       <c r="H60" t="str">
-        <v>Bruno Mars</v>
+        <v>Louie TheSinger</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
+        <v>ella jane - When I Was Beautiful (Live)</v>
       </c>
       <c r="B61" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
+        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-23</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:53</v>
+        <v>3:24</v>
       </c>
       <c r="H61" t="str">
-        <v>MAX</v>
+        <v>ella jane</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
+        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
+        <v>Johnny Orlando - Emilia (Official Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
+        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-23</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>4:11</v>
+        <v>3:14</v>
       </c>
       <c r="H62" t="str">
-        <v>Jessie J</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
+        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
+        <v>Kungs, Theophilus London - Galaxy (official video)</v>
       </c>
       <c r="B63" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
+        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-23</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>2:45</v>
+        <v>3:32</v>
       </c>
       <c r="H63" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Kungs</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
+        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
       </c>
       <c r="B64" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
+        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-23</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>4:00</v>
+        <v>3:15</v>
       </c>
       <c r="H64" t="str">
-        <v>Brandon Lake and Cody Johnson</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
+        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-23</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:27</v>
+        <v>3:03</v>
       </c>
       <c r="H65" t="str">
-        <v>The Kid LAROI.</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
+        <v>Stephen Sanchez - Sweet Love</v>
       </c>
       <c r="B66" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
+        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-23</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:25</v>
+        <v>3:04</v>
       </c>
       <c r="H66" t="str">
-        <v>Olivia Dean</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
+        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Bruno Mars - I Just Might [Official Music Video]</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
+        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-23</v>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:34</v>
+        <v>3:33</v>
       </c>
       <c r="H67" t="str">
-        <v>Demi Lovato</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Train - Mittens (Live on TODAY)</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=R2k_wPsAHKQ</v>
+        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-23</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:17</v>
+        <v>2:53</v>
       </c>
       <c r="H68" t="str">
-        <v>Train</v>
+        <v>MAX</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Train - Mittens (Live on TODAY) - Train</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
+        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-23</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:25</v>
+        <v>4:11</v>
       </c>
       <c r="H69" t="str">
-        <v>Joseph</v>
+        <v>Jessie J</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
+        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-23</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:26</v>
+        <v>2:45</v>
       </c>
       <c r="H70" t="str">
-        <v>Demi Lovato</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
+        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-23</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>4:46</v>
+        <v>4:00</v>
       </c>
       <c r="H71" t="str">
-        <v>Keith Urban</v>
+        <v>Brandon Lake and Cody Johnson</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
+        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-23</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:24</v>
+        <v>3:27</v>
       </c>
       <c r="H72" t="str">
-        <v>Keith Urban</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
+        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-23</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:52</v>
+        <v>3:25</v>
       </c>
       <c r="H73" t="str">
-        <v>Madonna</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
+        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-23</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:06</v>
+        <v>3:34</v>
       </c>
       <c r="H74" t="str">
-        <v>Estas Tonne</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estas Tonne</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Anna Graves - Burn On (Official Music Video)</v>
+        <v>Train - Mittens (Live on TODAY)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
+        <v>https://www.youtube.com/watch?v=R2k_wPsAHKQ</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-23</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:09</v>
+        <v>3:17</v>
       </c>
       <c r="H75" t="str">
-        <v>Anna Graves</v>
+        <v>Train</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
+        <v>Train - Mittens (Live on TODAY) - Train</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
+        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-23</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>5:11</v>
+        <v>2:25</v>
       </c>
       <c r="H76" t="str">
-        <v>Ocean Alley</v>
+        <v>Joseph</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
+        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-23</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:40</v>
+        <v>3:26</v>
       </c>
       <c r="H77" t="str">
-        <v>Zara Larsson</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
+        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-23</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:49</v>
+        <v>4:46</v>
       </c>
       <c r="H78" t="str">
-        <v>Lauren Watkins</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
+        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-23</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:42</v>
+        <v>3:24</v>
       </c>
       <c r="H79" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
+        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-23</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>5:11</v>
+        <v>2:52</v>
       </c>
       <c r="H80" t="str">
-        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Madonna</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
+        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-23</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:57</v>
+        <v>2:06</v>
       </c>
       <c r="H81" t="str">
-        <v>Lainey Wilson</v>
+        <v>Estas Tonne</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estas Tonne</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video)</v>
+        <v>Anna Graves - Burn On (Official Music Video)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
+        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-23</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:29</v>
+        <v>3:09</v>
       </c>
       <c r="H82" t="str">
-        <v>Grace Enger</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
+        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video)</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
+        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-23</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:10</v>
+        <v>5:11</v>
       </c>
       <c r="H83" t="str">
-        <v>Alan Walker and 2 more</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Emilia Tarrant - Break Up With Myself</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
       </c>
       <c r="B84" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
+        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-23</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>4:04</v>
+        <v>3:40</v>
       </c>
       <c r="H84" t="str">
-        <v>Emilia Tarrant</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026)</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B85" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
+        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-23</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:09</v>
+        <v>3:49</v>
       </c>
       <c r="H85" t="str">
-        <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer)</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B86" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
+        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-23</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:27</v>
+        <v>3:42</v>
       </c>
       <c r="H86" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Maggie Lindemann - fate</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B87" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
+        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-23</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:12</v>
+        <v>5:11</v>
       </c>
       <c r="H87" t="str">
-        <v>Maggie Lindemann</v>
+        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Maggie Lindemann - fate - Maggie Lindemann</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023)</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
       </c>
       <c r="B88" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=wo9yPPCh75Q</v>
+        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-23</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>4:44</v>
+        <v>3:57</v>
       </c>
       <c r="H88" t="str">
-        <v>Cliff Richard</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023) - Cliff Richard</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025</v>
+        <v>Grace Enger - All My Songs (Official Lyric Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=ND6maRwmzHk</v>
+        <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-23</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>1:00:09</v>
+        <v>3:29</v>
       </c>
       <c r="H89" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025 - Purple Disco Machine</v>
+        <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall)</v>
+        <v>Alan Walker - Broken Strings (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=9jMMOYr-VhE</v>
+        <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-23</v>
@@ -3798,10 +3798,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>4:15</v>
+        <v>3:10</v>
       </c>
       <c r="H90" t="str">
-        <v>RAYE</v>
+        <v>Alan Walker and 2 more</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall) - RAYE</v>
+        <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Madison Cunningham - My Full Name (Garden Session)</v>
+        <v>Emilia Tarrant - Break Up With Myself</v>
       </c>
       <c r="B91" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=o2F-QmqdNtI</v>
+        <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-23</v>
@@ -3836,10 +3836,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>4:07</v>
+        <v>4:04</v>
       </c>
       <c r="H91" t="str">
-        <v>Madison Cunningham</v>
+        <v>Emilia Tarrant</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Madison Cunningham - My Full Name (Garden Session) - Madison Cunningham</v>
+        <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions)</v>
+        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026)</v>
       </c>
       <c r="B92" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=5-6cEVLqE90</v>
+        <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-23</v>
@@ -3874,10 +3874,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:10</v>
+        <v>3:09</v>
       </c>
       <c r="H92" t="str">
-        <v>Teddy Swims</v>
+        <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower)</v>
+        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer)</v>
       </c>
       <c r="B93" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=ivPSbcEMwCs</v>
+        <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-23</v>
@@ -3912,10 +3912,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:47</v>
+        <v>2:27</v>
       </c>
       <c r="H93" t="str">
-        <v>Christina Aguilera</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower) - Christina Aguilera</v>
+        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025)</v>
+        <v>Maggie Lindemann - fate</v>
       </c>
       <c r="B94" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=tYpOHbXFnm0</v>
+        <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-23</v>
@@ -3950,10 +3950,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:58</v>
+        <v>2:12</v>
       </c>
       <c r="H94" t="str">
-        <v>RAYE</v>
+        <v>Maggie Lindemann</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025) - RAYE</v>
+        <v>Maggie Lindemann - fate - Maggie Lindemann</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Dasha - Here For The Party (Official Audio)</v>
+        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023)</v>
       </c>
       <c r="B95" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=rSO9oYUnO2k</v>
+        <v>https://www.youtube.com/watch?v=wo9yPPCh75Q</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-23</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:30</v>
+        <v>4:44</v>
       </c>
       <c r="H95" t="str">
-        <v>Dasha</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Dasha - Here For The Party (Official Audio) - Dasha</v>
+        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023) - Cliff Richard</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Lady Gaga in Harlequin Live: One Night Only</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025</v>
       </c>
       <c r="B96" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=c231tCsQalU</v>
+        <v>https://www.youtube.com/watch?v=ND6maRwmzHk</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-23</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>51:49</v>
+        <v>1:00:09</v>
       </c>
       <c r="H96" t="str">
-        <v>Lady Gaga and YouTube</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Lady Gaga in Harlequin Live: One Night Only - Lady Gaga and YouTube</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Sabrina Carpenter - Such A Funny Way (Official Lyric Video)</v>
+        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall)</v>
       </c>
       <c r="B97" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=oaJKUCgSSkc</v>
+        <v>https://www.youtube.com/watch?v=9jMMOYr-VhE</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-23</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:53</v>
+        <v>4:15</v>
       </c>
       <c r="H97" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>RAYE</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Sabrina Carpenter - Such A Funny Way (Official Lyric Video) - Sabrina Carpenter</v>
+        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall) - RAYE</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Megan Moroney - Beautiful Things (Official Fan Video)</v>
+        <v>Madison Cunningham - My Full Name (Garden Session)</v>
       </c>
       <c r="B98" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=0Gxu80LxI0w</v>
+        <v>https://www.youtube.com/watch?v=o2F-QmqdNtI</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-23</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:56</v>
+        <v>4:07</v>
       </c>
       <c r="H98" t="str">
-        <v>Megan Moroney</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Megan Moroney - Beautiful Things (Official Fan Video) - Megan Moroney</v>
+        <v>Madison Cunningham - My Full Name (Garden Session) - Madison Cunningham</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Jason Derulo - Miracle</v>
+        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions)</v>
       </c>
       <c r="B99" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=7sjshHJwkOE</v>
+        <v>https://www.youtube.com/watch?v=5-6cEVLqE90</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-23</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:16</v>
+        <v>3:10</v>
       </c>
       <c r="H99" t="str">
-        <v>Jason Derulo</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Jason Derulo - Miracle - Jason Derulo</v>
+        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Sananda Maitreya - Pretty Baby (Live)</v>
+        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower)</v>
       </c>
       <c r="B100" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=yv1c5G5HZt8</v>
+        <v>https://www.youtube.com/watch?v=ivPSbcEMwCs</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-23</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:29</v>
+        <v>3:47</v>
       </c>
       <c r="H100" t="str">
-        <v>Sananda Maitreya</v>
+        <v>Christina Aguilera</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Sananda Maitreya - Pretty Baby (Live) - Sananda Maitreya</v>
+        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower) - Christina Aguilera</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Faded - 10th Anniversary (Performance Video)</v>
+        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025)</v>
       </c>
       <c r="B101" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=EXVg23U3NRw</v>
+        <v>https://www.youtube.com/watch?v=tYpOHbXFnm0</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-23</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:25</v>
+        <v>3:58</v>
       </c>
       <c r="H101" t="str">
-        <v>Alan Walker and 2 more</v>
+        <v>RAYE</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Faded - 10th Anniversary (Performance Video) - Alan Walker and 2 more</v>
+        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025) - RAYE</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>2 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>2 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:59</v>
@@ -477,7 +477,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B3" t="str">
-        <v>3 hours ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>3 hours ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:56</v>
@@ -515,7 +515,7 @@
         <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>4 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>4 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:46</v>
@@ -553,7 +553,7 @@
         <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B5" t="str">
-        <v>4 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>4 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:47</v>
@@ -591,7 +591,7 @@
         <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B6" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:37</v>
@@ -629,7 +629,7 @@
         <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:06</v>
@@ -667,7 +667,7 @@
         <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B8" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:54</v>
@@ -705,7 +705,7 @@
         <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>4:10</v>
@@ -743,7 +743,7 @@
         <v>Matt Hansen - SOMEWHERE IN BETWEEN (Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:26</v>
@@ -819,7 +819,7 @@
         <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v>2:56</v>
@@ -857,7 +857,7 @@
         <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:01</v>
@@ -895,7 +895,7 @@
         <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:05</v>
@@ -933,7 +933,7 @@
         <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G15" t="str">
         <v>2:27</v>
@@ -971,7 +971,7 @@
         <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G16" t="str">
         <v>2:34</v>
@@ -1009,7 +1009,7 @@
         <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:13</v>
@@ -1047,7 +1047,7 @@
         <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:13</v>
@@ -1085,7 +1085,7 @@
         <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:08</v>
@@ -1123,7 +1123,7 @@
         <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G20" t="str">
         <v>5:14</v>
@@ -1161,7 +1161,7 @@
         <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G21" t="str">
         <v>2:59</v>
@@ -1313,7 +1313,7 @@
         <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B25" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>3:10</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>3 hours ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>3 hours ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:59</v>
@@ -477,7 +477,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B3" t="str">
-        <v>4 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>4 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:56</v>
@@ -515,7 +515,7 @@
         <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:46</v>
@@ -553,7 +553,7 @@
         <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B5" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:47</v>
@@ -591,7 +591,7 @@
         <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B6" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:37</v>
@@ -629,7 +629,7 @@
         <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:06</v>
@@ -667,7 +667,7 @@
         <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B8" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:54</v>
@@ -705,7 +705,7 @@
         <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>4:10</v>
@@ -743,7 +743,7 @@
         <v>Matt Hansen - SOMEWHERE IN BETWEEN (Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:26</v>
@@ -819,7 +819,7 @@
         <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v>2:56</v>
@@ -857,7 +857,7 @@
         <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:01</v>
@@ -895,7 +895,7 @@
         <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:05</v>
@@ -933,7 +933,7 @@
         <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G15" t="str">
         <v>2:27</v>
@@ -971,7 +971,7 @@
         <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G16" t="str">
         <v>2:34</v>
@@ -1009,7 +1009,7 @@
         <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:13</v>
@@ -1047,7 +1047,7 @@
         <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:13</v>
@@ -1085,7 +1085,7 @@
         <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:08</v>
@@ -1123,7 +1123,7 @@
         <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G20" t="str">
         <v>5:14</v>
@@ -1769,7 +1769,7 @@
         <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B37" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>3:25</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>4 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>4 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:59</v>
@@ -477,7 +477,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B3" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:56</v>
@@ -515,7 +515,7 @@
         <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:46</v>
@@ -553,7 +553,7 @@
         <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B5" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:47</v>
@@ -591,7 +591,7 @@
         <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B6" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:37</v>
@@ -629,7 +629,7 @@
         <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:06</v>
@@ -667,7 +667,7 @@
         <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B8" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:54</v>
@@ -705,7 +705,7 @@
         <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>4:10</v>
@@ -740,10 +740,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Lyric Video)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:26</v>
@@ -773,7 +773,7 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Lyric Video) - Matt Hansen</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="11">
@@ -819,7 +819,7 @@
         <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v>2:56</v>
@@ -857,7 +857,7 @@
         <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:01</v>
@@ -895,7 +895,7 @@
         <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:05</v>
@@ -933,7 +933,7 @@
         <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G15" t="str">
         <v>2:27</v>
@@ -971,7 +971,7 @@
         <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G16" t="str">
         <v>2:34</v>
@@ -1009,7 +1009,7 @@
         <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:13</v>
@@ -1047,7 +1047,7 @@
         <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:13</v>
@@ -1085,7 +1085,7 @@
         <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:08</v>
@@ -1123,7 +1123,7 @@
         <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G20" t="str">
         <v>5:14</v>
@@ -1161,7 +1161,7 @@
         <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G21" t="str">
         <v>2:59</v>
@@ -1731,7 +1731,7 @@
         <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>2:54</v>
@@ -2871,7 +2871,7 @@
         <v>Stephen Sanchez - Sweet Love</v>
       </c>
       <c r="B66" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
         <v>3:04</v>
@@ -4201,7 +4201,7 @@
         <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025)</v>
       </c>
       <c r="B101" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=tYpOHbXFnm0</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v>3:58</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:59</v>
@@ -477,7 +477,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B3" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:56</v>
@@ -515,7 +515,7 @@
         <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:46</v>
@@ -553,7 +553,7 @@
         <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B5" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:47</v>
@@ -591,7 +591,7 @@
         <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B6" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:37</v>
@@ -629,7 +629,7 @@
         <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:06</v>
@@ -667,7 +667,7 @@
         <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B8" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:54</v>
@@ -705,7 +705,7 @@
         <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>4:10</v>
@@ -743,7 +743,7 @@
         <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:26</v>
@@ -819,7 +819,7 @@
         <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v>2:56</v>
@@ -857,7 +857,7 @@
         <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:01</v>
@@ -895,7 +895,7 @@
         <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:05</v>
@@ -933,7 +933,7 @@
         <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G15" t="str">
         <v>2:27</v>
@@ -971,7 +971,7 @@
         <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G16" t="str">
         <v>2:34</v>
@@ -1009,7 +1009,7 @@
         <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:13</v>
@@ -1047,7 +1047,7 @@
         <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:13</v>
@@ -1085,7 +1085,7 @@
         <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:08</v>
@@ -1123,7 +1123,7 @@
         <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G20" t="str">
         <v>5:14</v>
@@ -1161,7 +1161,7 @@
         <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G21" t="str">
         <v>2:59</v>
@@ -1541,7 +1541,7 @@
         <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B31" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>3:45</v>
@@ -2339,7 +2339,7 @@
         <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B52" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>5:24</v>
@@ -2795,7 +2795,7 @@
         <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
       </c>
       <c r="B64" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
         <v>3:15</v>
@@ -2833,7 +2833,7 @@
         <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
         <v>3:03</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:59</v>
@@ -477,7 +477,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B3" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:56</v>
@@ -515,7 +515,7 @@
         <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:46</v>
@@ -553,7 +553,7 @@
         <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B5" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:47</v>
@@ -591,7 +591,7 @@
         <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B6" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:37</v>
@@ -629,7 +629,7 @@
         <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:06</v>
@@ -667,7 +667,7 @@
         <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B8" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:54</v>
@@ -705,7 +705,7 @@
         <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>4:10</v>
@@ -743,7 +743,7 @@
         <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:26</v>
@@ -781,7 +781,7 @@
         <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>2:56</v>
@@ -819,7 +819,7 @@
         <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v>2:56</v>
@@ -857,7 +857,7 @@
         <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:01</v>
@@ -895,7 +895,7 @@
         <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:05</v>
@@ -933,7 +933,7 @@
         <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G15" t="str">
         <v>2:27</v>
@@ -971,7 +971,7 @@
         <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G16" t="str">
         <v>2:34</v>
@@ -1009,7 +1009,7 @@
         <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:13</v>
@@ -1047,7 +1047,7 @@
         <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:13</v>
@@ -1085,7 +1085,7 @@
         <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:08</v>
@@ -1123,7 +1123,7 @@
         <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G20" t="str">
         <v>5:14</v>
@@ -1161,7 +1161,7 @@
         <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G21" t="str">
         <v>2:59</v>
@@ -1655,7 +1655,7 @@
         <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B34" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>4:27</v>
@@ -2719,7 +2719,7 @@
         <v>Johnny Orlando - Emilia (Official Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
         <v>3:14</v>
@@ -2757,7 +2757,7 @@
         <v>Kungs, Theophilus London - Galaxy (official video)</v>
       </c>
       <c r="B63" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
         <v>3:32</v>
@@ -3745,7 +3745,7 @@
         <v>Grace Enger - All My Songs (Official Lyric Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G89" t="str">
         <v>3:29</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:59</v>
@@ -477,7 +477,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B3" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:56</v>
@@ -515,7 +515,7 @@
         <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:46</v>
@@ -553,7 +553,7 @@
         <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B5" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:47</v>
@@ -591,7 +591,7 @@
         <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B6" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:37</v>
@@ -629,7 +629,7 @@
         <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:06</v>
@@ -667,7 +667,7 @@
         <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B8" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:54</v>
@@ -705,7 +705,7 @@
         <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>4:10</v>
@@ -743,7 +743,7 @@
         <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:26</v>
@@ -819,7 +819,7 @@
         <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v>2:56</v>
@@ -857,7 +857,7 @@
         <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:01</v>
@@ -895,7 +895,7 @@
         <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:05</v>
@@ -933,7 +933,7 @@
         <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G15" t="str">
         <v>2:27</v>
@@ -971,7 +971,7 @@
         <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G16" t="str">
         <v>2:34</v>
@@ -1009,7 +1009,7 @@
         <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:13</v>
@@ -1047,7 +1047,7 @@
         <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:13</v>
@@ -1085,7 +1085,7 @@
         <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:08</v>
@@ -1123,7 +1123,7 @@
         <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G20" t="str">
         <v>5:14</v>
@@ -1693,7 +1693,7 @@
         <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B35" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>4:34</v>
@@ -2301,7 +2301,7 @@
         <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B51" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>3:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:59</v>
@@ -477,7 +477,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B3" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:56</v>
@@ -515,7 +515,7 @@
         <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:46</v>
@@ -553,7 +553,7 @@
         <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B5" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:47</v>
@@ -591,7 +591,7 @@
         <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B6" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:37</v>
@@ -629,7 +629,7 @@
         <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:06</v>
@@ -667,7 +667,7 @@
         <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B8" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:54</v>
@@ -705,7 +705,7 @@
         <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>4:10</v>
@@ -743,7 +743,7 @@
         <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:26</v>
@@ -819,7 +819,7 @@
         <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v>2:56</v>
@@ -857,7 +857,7 @@
         <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:01</v>
@@ -895,7 +895,7 @@
         <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:05</v>
@@ -933,7 +933,7 @@
         <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G15" t="str">
         <v>2:27</v>
@@ -971,7 +971,7 @@
         <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G16" t="str">
         <v>2:34</v>
@@ -1009,7 +1009,7 @@
         <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:13</v>
@@ -1047,7 +1047,7 @@
         <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:13</v>
@@ -1085,7 +1085,7 @@
         <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:08</v>
@@ -1123,7 +1123,7 @@
         <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G20" t="str">
         <v>5:14</v>
@@ -1237,7 +1237,7 @@
         <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>4:09</v>
@@ -1503,7 +1503,7 @@
         <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B30" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>3:17</v>
@@ -2681,7 +2681,7 @@
         <v>ella jane - When I Was Beautiful (Live)</v>
       </c>
       <c r="B61" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
         <v>3:24</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:59</v>
@@ -477,7 +477,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B3" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:56</v>
@@ -515,7 +515,7 @@
         <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:46</v>
@@ -553,7 +553,7 @@
         <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B5" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:47</v>
@@ -591,7 +591,7 @@
         <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B6" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:37</v>
@@ -629,7 +629,7 @@
         <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:06</v>
@@ -667,7 +667,7 @@
         <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B8" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:54</v>
@@ -705,7 +705,7 @@
         <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>4:10</v>
@@ -743,7 +743,7 @@
         <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:26</v>
@@ -819,7 +819,7 @@
         <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v>2:56</v>
@@ -857,7 +857,7 @@
         <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:01</v>
@@ -895,7 +895,7 @@
         <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:05</v>
@@ -933,7 +933,7 @@
         <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G15" t="str">
         <v>2:27</v>
@@ -971,7 +971,7 @@
         <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G16" t="str">
         <v>2:34</v>
@@ -1009,7 +1009,7 @@
         <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:13</v>
@@ -1047,7 +1047,7 @@
         <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:13</v>
@@ -1085,7 +1085,7 @@
         <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:08</v>
@@ -1123,7 +1123,7 @@
         <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G20" t="str">
         <v>5:14</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:59</v>
@@ -477,7 +477,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B3" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:56</v>
@@ -515,7 +515,7 @@
         <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:46</v>
@@ -553,7 +553,7 @@
         <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B5" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:47</v>
@@ -591,7 +591,7 @@
         <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B6" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:37</v>
@@ -629,7 +629,7 @@
         <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:06</v>
@@ -667,7 +667,7 @@
         <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B8" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:54</v>
@@ -705,7 +705,7 @@
         <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>4:10</v>
@@ -743,7 +743,7 @@
         <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:26</v>
@@ -819,7 +819,7 @@
         <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v>2:56</v>
@@ -857,7 +857,7 @@
         <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:01</v>
@@ -895,7 +895,7 @@
         <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:05</v>
@@ -933,7 +933,7 @@
         <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G15" t="str">
         <v>2:27</v>
@@ -971,7 +971,7 @@
         <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G16" t="str">
         <v>2:34</v>
@@ -1009,7 +1009,7 @@
         <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:13</v>
@@ -1047,7 +1047,7 @@
         <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:13</v>
@@ -1085,7 +1085,7 @@
         <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:08</v>
@@ -1123,7 +1123,7 @@
         <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G20" t="str">
         <v>5:14</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:59</v>
@@ -477,7 +477,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B3" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:56</v>
@@ -515,7 +515,7 @@
         <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:46</v>
@@ -553,7 +553,7 @@
         <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B5" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:47</v>
@@ -591,7 +591,7 @@
         <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B6" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:37</v>
@@ -629,7 +629,7 @@
         <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:06</v>
@@ -667,7 +667,7 @@
         <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B8" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:54</v>
@@ -705,7 +705,7 @@
         <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>4:10</v>
@@ -743,7 +743,7 @@
         <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:26</v>
@@ -819,7 +819,7 @@
         <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v>2:56</v>
@@ -857,7 +857,7 @@
         <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:01</v>
@@ -895,7 +895,7 @@
         <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:05</v>
@@ -933,7 +933,7 @@
         <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G15" t="str">
         <v>2:27</v>
@@ -971,7 +971,7 @@
         <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G16" t="str">
         <v>2:34</v>
@@ -1009,7 +1009,7 @@
         <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:13</v>
@@ -1047,7 +1047,7 @@
         <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:13</v>
@@ -1085,7 +1085,7 @@
         <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:08</v>
@@ -1123,7 +1123,7 @@
         <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G20" t="str">
         <v>5:14</v>
@@ -1617,7 +1617,7 @@
         <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>3:03</v>
@@ -2491,7 +2491,7 @@
         <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
       </c>
       <c r="B56" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
         <v>4:16</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:59</v>
@@ -477,7 +477,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B3" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:56</v>
@@ -515,7 +515,7 @@
         <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:46</v>
@@ -553,7 +553,7 @@
         <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B5" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:47</v>
@@ -591,7 +591,7 @@
         <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B6" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:37</v>
@@ -629,7 +629,7 @@
         <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:06</v>
@@ -667,7 +667,7 @@
         <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B8" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:54</v>
@@ -705,7 +705,7 @@
         <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>4:10</v>
@@ -743,7 +743,7 @@
         <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:26</v>
@@ -819,7 +819,7 @@
         <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v>2:56</v>
@@ -857,7 +857,7 @@
         <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:01</v>
@@ -895,7 +895,7 @@
         <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:05</v>
@@ -933,7 +933,7 @@
         <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G15" t="str">
         <v>2:27</v>
@@ -971,7 +971,7 @@
         <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G16" t="str">
         <v>2:34</v>
@@ -1009,7 +1009,7 @@
         <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:13</v>
@@ -1047,7 +1047,7 @@
         <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:13</v>
@@ -1085,7 +1085,7 @@
         <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:08</v>
@@ -1123,7 +1123,7 @@
         <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G20" t="str">
         <v>5:14</v>
@@ -1465,7 +1465,7 @@
         <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B29" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>7:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,19 +439,19 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>13 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>13 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:59</v>
@@ -477,19 +477,19 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B3" t="str">
-        <v>14 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>14 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:56</v>
@@ -515,19 +515,19 @@
         <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:46</v>
@@ -553,19 +553,19 @@
         <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B5" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:47</v>
@@ -591,19 +591,19 @@
         <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B6" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:37</v>
@@ -629,19 +629,19 @@
         <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:06</v>
@@ -667,19 +667,19 @@
         <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B8" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:54</v>
@@ -705,19 +705,19 @@
         <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>4:10</v>
@@ -743,19 +743,19 @@
         <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:26</v>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -819,19 +819,19 @@
         <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v>2:56</v>
@@ -857,19 +857,19 @@
         <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:01</v>
@@ -895,19 +895,19 @@
         <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:05</v>
@@ -933,19 +933,19 @@
         <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G15" t="str">
         <v>2:27</v>
@@ -971,19 +971,19 @@
         <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G16" t="str">
         <v>2:34</v>
@@ -1009,19 +1009,19 @@
         <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:13</v>
@@ -1047,19 +1047,19 @@
         <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:13</v>
@@ -1085,19 +1085,19 @@
         <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:08</v>
@@ -1123,19 +1123,19 @@
         <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G20" t="str">
         <v>5:14</v>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2263,19 +2263,19 @@
         <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>2:31</v>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2453,19 +2453,19 @@
         <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B55" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>3:31</v>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=R2k_wPsAHKQ</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=wo9yPPCh75Q</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=ND6maRwmzHk</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=9jMMOYr-VhE</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=o2F-QmqdNtI</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=5-6cEVLqE90</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4163,19 +4163,19 @@
         <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower)</v>
       </c>
       <c r="B100" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=ivPSbcEMwCs</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v>3:47</v>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=tYpOHbXFnm0</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>15 hours ago</v>
+        <v>1 hour ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-24</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>15 hours ago</v>
+        <v>1 hour ago</v>
       </c>
       <c r="G2" t="str">
-        <v>3:59</v>
+        <v>3:34</v>
       </c>
       <c r="H2" t="str">
-        <v>Holly Humberstone</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>16 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-24</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>16 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>2:56</v>
+        <v>4:01</v>
       </c>
       <c r="H3" t="str">
-        <v>Cliff Richard</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B4" t="str">
-        <v>17 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-24</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>17 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>3:46</v>
+        <v>3:24</v>
       </c>
       <c r="H4" t="str">
-        <v>Jessie Ware</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Dean Lewis - I Am Getting Well</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>17 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-24</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>17 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G5" t="str">
-        <v>2:47</v>
+        <v>5:52</v>
       </c>
       <c r="H5" t="str">
-        <v>Dean Lewis</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Dean Lewis - I Am Getting Well - Dean Lewis</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B6" t="str">
-        <v>19 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-24</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>19 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G6" t="str">
-        <v>4:37</v>
+        <v>5:01</v>
       </c>
       <c r="H6" t="str">
-        <v>Bella White</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B7" t="str">
-        <v>20 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-24</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>20 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G7" t="str">
-        <v>4:06</v>
+        <v>4:12</v>
       </c>
       <c r="H7" t="str">
-        <v>Ryan Wright</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>20 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-24</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>20 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:54</v>
+        <v>3:59</v>
       </c>
       <c r="H8" t="str">
-        <v>Dove Cameron</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B9" t="str">
-        <v>20 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-24</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>20 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G9" t="str">
-        <v>4:10</v>
+        <v>2:56</v>
       </c>
       <c r="H9" t="str">
-        <v>Parker McCollum</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>20 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-24</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>20 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:26</v>
+        <v>3:46</v>
       </c>
       <c r="H10" t="str">
-        <v>Matt Hansen</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video)</v>
+        <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
+        <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-24</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G11" t="str">
-        <v>2:56</v>
+        <v>2:47</v>
       </c>
       <c r="H11" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
+        <v>Dean Lewis - I Am Getting Well - Dean Lewis</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B12" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-24</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G12" t="str">
-        <v>2:56</v>
+        <v>4:37</v>
       </c>
       <c r="H12" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Bella White</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-24</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G13" t="str">
-        <v>4:01</v>
+        <v>4:06</v>
       </c>
       <c r="H13" t="str">
-        <v>Tauren Wells</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B14" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-24</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:05</v>
+        <v>3:54</v>
       </c>
       <c r="H14" t="str">
-        <v>Maiah Manser</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-24</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G15" t="str">
-        <v>2:27</v>
+        <v>4:10</v>
       </c>
       <c r="H15" t="str">
-        <v>Taylor Austin Dye</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Chelsea Cutler - BAD (Official Video)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-24</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G16" t="str">
-        <v>2:34</v>
+        <v>3:26</v>
       </c>
       <c r="H16" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>20 hours ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-24</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>20 hours ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:13</v>
+        <v>2:56</v>
       </c>
       <c r="H17" t="str">
-        <v>Ashley Kutcher</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-24</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:13</v>
+        <v>2:56</v>
       </c>
       <c r="H18" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-24</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:08</v>
+        <v>4:01</v>
       </c>
       <c r="H19" t="str">
-        <v>CAIN</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Harry Styles - Aperture (Official Audio)</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>1 day ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-24</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>1 day ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G20" t="str">
-        <v>5:14</v>
+        <v>3:05</v>
       </c>
       <c r="H20" t="str">
-        <v>Harry Styles</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>1 day ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-24</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>1 day ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G21" t="str">
-        <v>2:59</v>
+        <v>2:27</v>
       </c>
       <c r="H21" t="str">
-        <v>Lana Lubany</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>1 day ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-24</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>1 day ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G22" t="str">
-        <v>4:21</v>
+        <v>2:34</v>
       </c>
       <c r="H22" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>2 days ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-24</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2 days ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G23" t="str">
-        <v>4:09</v>
+        <v>3:13</v>
       </c>
       <c r="H23" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Ashley Kutcher</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B24" t="str">
-        <v>2 days ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-24</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2 days ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G24" t="str">
-        <v>2:34</v>
+        <v>3:13</v>
       </c>
       <c r="H24" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>3 days ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-24</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>3 days ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:10</v>
+        <v>3:08</v>
       </c>
       <c r="H25" t="str">
-        <v>Olivia Dean</v>
+        <v>CAIN</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B26" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-24</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:21</v>
+        <v>5:14</v>
       </c>
       <c r="H26" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-24</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:06</v>
+        <v>2:59</v>
       </c>
       <c r="H27" t="str">
-        <v>The Avett Brothers</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-24</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:21</v>
+        <v>4:21</v>
       </c>
       <c r="H28" t="str">
-        <v>Jordana Bryant</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-24</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>7:21</v>
+        <v>4:09</v>
       </c>
       <c r="H29" t="str">
-        <v>Katy Perry</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-24</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:17</v>
+        <v>2:34</v>
       </c>
       <c r="H30" t="str">
-        <v>Lauren Watkins</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B31" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-24</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:45</v>
+        <v>3:10</v>
       </c>
       <c r="H31" t="str">
-        <v>Tones And I</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B32" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-24</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:57</v>
+        <v>3:21</v>
       </c>
       <c r="H32" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-24</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:03</v>
+        <v>3:06</v>
       </c>
       <c r="H33" t="str">
-        <v>Charlie Puth</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-24</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:27</v>
+        <v>3:21</v>
       </c>
       <c r="H34" t="str">
-        <v>Chappell Roan</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B35" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-24</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>4:34</v>
+        <v>7:21</v>
       </c>
       <c r="H35" t="str">
-        <v>Armik</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B36" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-24</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>2:54</v>
+        <v>3:17</v>
       </c>
       <c r="H36" t="str">
-        <v>LØLØ</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B37" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-24</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:25</v>
+        <v>3:45</v>
       </c>
       <c r="H37" t="str">
-        <v>Tenille Townes</v>
+        <v>Tones And I</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B38" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-24</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:01</v>
+        <v>3:57</v>
       </c>
       <c r="H38" t="str">
-        <v>Alan Walker</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B39" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-24</v>
@@ -1860,10 +1860,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>2:25</v>
+        <v>3:03</v>
       </c>
       <c r="H39" t="str">
-        <v>Charli xcx</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B40" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-24</v>
@@ -1898,10 +1898,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>1:14</v>
+        <v>4:27</v>
       </c>
       <c r="H40" t="str">
-        <v>Labrinth</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B41" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-24</v>
@@ -1936,10 +1936,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>2:59</v>
+        <v>4:34</v>
       </c>
       <c r="H41" t="str">
-        <v>Charlie Puth</v>
+        <v>Armik</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B42" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-24</v>
@@ -1974,10 +1974,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:29</v>
+        <v>2:54</v>
       </c>
       <c r="H42" t="str">
-        <v>Girl Tones</v>
+        <v>LØLØ</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B43" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-24</v>
@@ -2012,10 +2012,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:34</v>
+        <v>3:25</v>
       </c>
       <c r="H43" t="str">
-        <v>Jagwar Twin</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B44" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-24</v>
@@ -2050,10 +2050,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:48</v>
+        <v>2:01</v>
       </c>
       <c r="H44" t="str">
-        <v>Caroline Jones</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B45" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-24</v>
@@ -2088,10 +2088,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:32</v>
+        <v>2:25</v>
       </c>
       <c r="H45" t="str">
-        <v>The Beaches</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B46" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-24</v>
@@ -2126,10 +2126,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:49</v>
+        <v>1:14</v>
       </c>
       <c r="H46" t="str">
-        <v>Dolly Parton</v>
+        <v>Labrinth</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B47" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-24</v>
@@ -2164,10 +2164,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>4:28</v>
+        <v>2:59</v>
       </c>
       <c r="H47" t="str">
-        <v>Madison Beer</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B48" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-24</v>
@@ -2202,10 +2202,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:37</v>
+        <v>2:29</v>
       </c>
       <c r="H48" t="str">
-        <v>Ty Myers</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B49" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-24</v>
@@ -2240,10 +2240,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:35</v>
+        <v>2:34</v>
       </c>
       <c r="H49" t="str">
-        <v>Megan Moroney</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-24</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>2:31</v>
+        <v>3:48</v>
       </c>
       <c r="H50" t="str">
-        <v>Julia Cole Music</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B51" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-24</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:21</v>
+        <v>3:32</v>
       </c>
       <c r="H51" t="str">
-        <v>Lily Allen</v>
+        <v>The Beaches</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B52" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-24</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>5:24</v>
+        <v>3:49</v>
       </c>
       <c r="H52" t="str">
-        <v>Nickless</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-24</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:11</v>
+        <v>4:28</v>
       </c>
       <c r="H53" t="str">
-        <v>Peach PRC</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-24</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>4:11</v>
+        <v>3:37</v>
       </c>
       <c r="H54" t="str">
-        <v>Ocean Alley</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-24</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:31</v>
+        <v>3:35</v>
       </c>
       <c r="H55" t="str">
-        <v>OneRepublic</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-24</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>4:16</v>
+        <v>2:31</v>
       </c>
       <c r="H56" t="str">
-        <v>Ty Myers</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B57" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-24</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>4:42</v>
+        <v>3:21</v>
       </c>
       <c r="H57" t="str">
-        <v>JavaJazzFest</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video)</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B58" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-24</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>2:47</v>
+        <v>5:24</v>
       </c>
       <c r="H58" t="str">
-        <v>Teo Glacier</v>
+        <v>Nickless</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
+        <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B59" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
+        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-24</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:59</v>
+        <v>3:11</v>
       </c>
       <c r="H59" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
       </c>
       <c r="B60" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
+        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-24</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>4:09</v>
+        <v>4:11</v>
       </c>
       <c r="H60" t="str">
-        <v>Louie TheSinger</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ella jane - When I Was Beautiful (Live)</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B61" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
+        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-24</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:24</v>
+        <v>3:31</v>
       </c>
       <c r="H61" t="str">
-        <v>ella jane</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Johnny Orlando - Emilia (Official Video)</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
       </c>
       <c r="B62" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
+        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-24</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:14</v>
+        <v>4:16</v>
       </c>
       <c r="H62" t="str">
-        <v>Johnny Orlando</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video)</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B63" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
+        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-24</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:32</v>
+        <v>4:42</v>
       </c>
       <c r="H63" t="str">
-        <v>Kungs</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
+        <v>Teo Glacier - Don't Mind (Music Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
+        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-24</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:15</v>
+        <v>2:47</v>
       </c>
       <c r="H64" t="str">
-        <v>Billy Raffoul</v>
+        <v>Teo Glacier</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
+        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
+        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-24</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:03</v>
+        <v>3:59</v>
       </c>
       <c r="H65" t="str">
-        <v>NathanEvanss</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Stephen Sanchez - Sweet Love</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
       </c>
       <c r="B66" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
+        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-24</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:04</v>
+        <v>4:09</v>
       </c>
       <c r="H66" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Louie TheSinger</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video]</v>
+        <v>ella jane - When I Was Beautiful (Live)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
+        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-24</v>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:33</v>
+        <v>3:24</v>
       </c>
       <c r="H67" t="str">
-        <v>Bruno Mars</v>
+        <v>ella jane</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
+        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
+        <v>Johnny Orlando - Emilia (Official Video)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
+        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-24</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>2:53</v>
+        <v>3:14</v>
       </c>
       <c r="H68" t="str">
-        <v>MAX</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
+        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
+        <v>Kungs, Theophilus London - Galaxy (official video)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
+        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-24</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>4:11</v>
+        <v>3:32</v>
       </c>
       <c r="H69" t="str">
-        <v>Jessie J</v>
+        <v>Kungs</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
+        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
+        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-24</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:45</v>
+        <v>3:15</v>
       </c>
       <c r="H70" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
+        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-24</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>4:00</v>
+        <v>3:03</v>
       </c>
       <c r="H71" t="str">
-        <v>Brandon Lake and Cody Johnson</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
+        <v>Stephen Sanchez - Sweet Love</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
+        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-24</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:27</v>
+        <v>3:04</v>
       </c>
       <c r="H72" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
+        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
+        <v>Bruno Mars - I Just Might [Official Music Video]</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
+        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-24</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:25</v>
+        <v>3:33</v>
       </c>
       <c r="H73" t="str">
-        <v>Olivia Dean</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
+        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
+        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-24</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:34</v>
+        <v>2:53</v>
       </c>
       <c r="H74" t="str">
-        <v>Demi Lovato</v>
+        <v>MAX</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Train - Mittens (Live on TODAY)</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=R2k_wPsAHKQ</v>
+        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-24</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:17</v>
+        <v>4:11</v>
       </c>
       <c r="H75" t="str">
-        <v>Train</v>
+        <v>Jessie J</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Train - Mittens (Live on TODAY) - Train</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
+        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-24</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:25</v>
+        <v>2:45</v>
       </c>
       <c r="H76" t="str">
-        <v>Joseph</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
+        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-24</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:26</v>
+        <v>4:00</v>
       </c>
       <c r="H77" t="str">
-        <v>Demi Lovato</v>
+        <v>Brandon Lake and Cody Johnson</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
+        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-24</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>4:46</v>
+        <v>3:27</v>
       </c>
       <c r="H78" t="str">
-        <v>Keith Urban</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
+        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-24</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:24</v>
+        <v>3:25</v>
       </c>
       <c r="H79" t="str">
-        <v>Keith Urban</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
+        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-24</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>2:52</v>
+        <v>3:34</v>
       </c>
       <c r="H80" t="str">
-        <v>Madonna</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
+        <v>Train - Mittens (Live on TODAY)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
+        <v>https://www.youtube.com/watch?v=R2k_wPsAHKQ</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-24</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>2:06</v>
+        <v>3:17</v>
       </c>
       <c r="H81" t="str">
-        <v>Estas Tonne</v>
+        <v>Train</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estas Tonne</v>
+        <v>Train - Mittens (Live on TODAY) - Train</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Anna Graves - Burn On (Official Music Video)</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
+        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-24</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:09</v>
+        <v>2:25</v>
       </c>
       <c r="H82" t="str">
-        <v>Anna Graves</v>
+        <v>Joseph</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
+        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-24</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>5:11</v>
+        <v>3:26</v>
       </c>
       <c r="H83" t="str">
-        <v>Ocean Alley</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
+        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-24</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:40</v>
+        <v>4:46</v>
       </c>
       <c r="H84" t="str">
-        <v>Zara Larsson</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
+        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-24</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:49</v>
+        <v>3:24</v>
       </c>
       <c r="H85" t="str">
-        <v>Lauren Watkins</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
+        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-24</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:42</v>
+        <v>2:52</v>
       </c>
       <c r="H86" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Madonna</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
+        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-24</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>5:11</v>
+        <v>2:06</v>
       </c>
       <c r="H87" t="str">
-        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Estas Tonne</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estas Tonne</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
+        <v>Anna Graves - Burn On (Official Music Video)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
+        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-24</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:57</v>
+        <v>3:09</v>
       </c>
       <c r="H88" t="str">
-        <v>Lainey Wilson</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
+        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video)</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
+        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-24</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:29</v>
+        <v>5:11</v>
       </c>
       <c r="H89" t="str">
-        <v>Grace Enger</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video)</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
       </c>
       <c r="B90" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
+        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-24</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:10</v>
+        <v>3:40</v>
       </c>
       <c r="H90" t="str">
-        <v>Alan Walker and 2 more</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Emilia Tarrant - Break Up With Myself</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B91" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
+        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-24</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>4:04</v>
+        <v>3:49</v>
       </c>
       <c r="H91" t="str">
-        <v>Emilia Tarrant</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026)</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B92" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
+        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-24</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:09</v>
+        <v>3:42</v>
       </c>
       <c r="H92" t="str">
-        <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer)</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B93" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
+        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-24</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:27</v>
+        <v>5:11</v>
       </c>
       <c r="H93" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Maggie Lindemann - fate</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
       </c>
       <c r="B94" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
+        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-24</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>2:12</v>
+        <v>3:57</v>
       </c>
       <c r="H94" t="str">
-        <v>Maggie Lindemann</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Maggie Lindemann - fate - Maggie Lindemann</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023)</v>
+        <v>Grace Enger - All My Songs (Official Lyric Video)</v>
       </c>
       <c r="B95" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=wo9yPPCh75Q</v>
+        <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-24</v>
@@ -3988,10 +3988,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:44</v>
+        <v>3:29</v>
       </c>
       <c r="H95" t="str">
-        <v>Cliff Richard</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023) - Cliff Richard</v>
+        <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025</v>
+        <v>Alan Walker - Broken Strings (Official Music Video)</v>
       </c>
       <c r="B96" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=ND6maRwmzHk</v>
+        <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-24</v>
@@ -4026,10 +4026,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>1:00:09</v>
+        <v>3:10</v>
       </c>
       <c r="H96" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Alan Walker and 2 more</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025 - Purple Disco Machine</v>
+        <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall)</v>
+        <v>Emilia Tarrant - Break Up With Myself</v>
       </c>
       <c r="B97" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=9jMMOYr-VhE</v>
+        <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-24</v>
@@ -4064,10 +4064,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:15</v>
+        <v>4:04</v>
       </c>
       <c r="H97" t="str">
-        <v>RAYE</v>
+        <v>Emilia Tarrant</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall) - RAYE</v>
+        <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Madison Cunningham - My Full Name (Garden Session)</v>
+        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026)</v>
       </c>
       <c r="B98" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=o2F-QmqdNtI</v>
+        <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-24</v>
@@ -4102,10 +4102,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>4:07</v>
+        <v>3:09</v>
       </c>
       <c r="H98" t="str">
-        <v>Madison Cunningham</v>
+        <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Madison Cunningham - My Full Name (Garden Session) - Madison Cunningham</v>
+        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions)</v>
+        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer)</v>
       </c>
       <c r="B99" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=5-6cEVLqE90</v>
+        <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-24</v>
@@ -4140,10 +4140,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:10</v>
+        <v>2:27</v>
       </c>
       <c r="H99" t="str">
-        <v>Teddy Swims</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower)</v>
+        <v>Maggie Lindemann - fate</v>
       </c>
       <c r="B100" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=ivPSbcEMwCs</v>
+        <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-24</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:47</v>
+        <v>2:12</v>
       </c>
       <c r="H100" t="str">
-        <v>Christina Aguilera</v>
+        <v>Maggie Lindemann</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower) - Christina Aguilera</v>
+        <v>Maggie Lindemann - fate - Maggie Lindemann</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025)</v>
+        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023)</v>
       </c>
       <c r="B101" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=tYpOHbXFnm0</v>
+        <v>https://www.youtube.com/watch?v=wo9yPPCh75Q</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-24</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:58</v>
+        <v>4:44</v>
       </c>
       <c r="H101" t="str">
-        <v>RAYE</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025) - RAYE</v>
+        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023) - Cliff Richard</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>1 hour ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 hour ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:34</v>
@@ -477,7 +477,7 @@
         <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>8 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>8 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:01</v>
@@ -515,7 +515,7 @@
         <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B4" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:24</v>
@@ -553,7 +553,7 @@
         <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>9 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>9 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:52</v>
@@ -591,7 +591,7 @@
         <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B6" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>5:01</v>
@@ -626,10 +626,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B7" t="str">
-        <v>10 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>10 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:12</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">
@@ -667,7 +667,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:59</v>
@@ -705,7 +705,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B9" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>2:56</v>
@@ -743,7 +743,7 @@
         <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:46</v>
@@ -781,7 +781,7 @@
         <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B11" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G11" t="str">
         <v>2:47</v>
@@ -819,7 +819,7 @@
         <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B12" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v>4:37</v>
@@ -857,7 +857,7 @@
         <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:06</v>
@@ -895,7 +895,7 @@
         <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B14" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:54</v>
@@ -933,7 +933,7 @@
         <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G15" t="str">
         <v>4:10</v>
@@ -971,7 +971,7 @@
         <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G16" t="str">
         <v>3:26</v>
@@ -1047,7 +1047,7 @@
         <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G18" t="str">
         <v>2:56</v>
@@ -1085,7 +1085,7 @@
         <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G19" t="str">
         <v>4:01</v>
@@ -1123,7 +1123,7 @@
         <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G20" t="str">
         <v>3:05</v>
@@ -1161,7 +1161,7 @@
         <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G21" t="str">
         <v>2:27</v>
@@ -1199,7 +1199,7 @@
         <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G22" t="str">
         <v>2:34</v>
@@ -1237,7 +1237,7 @@
         <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G23" t="str">
         <v>3:13</v>
@@ -1275,7 +1275,7 @@
         <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B24" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G24" t="str">
         <v>3:13</v>
@@ -1313,7 +1313,7 @@
         <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G25" t="str">
         <v>3:08</v>
@@ -1503,7 +1503,7 @@
         <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>2:34</v>
@@ -2871,7 +2871,7 @@
         <v>Louie TheSinger "Texas Gold" Official Music Video</v>
       </c>
       <c r="B66" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G66" t="str">
         <v>4:09</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>2 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>2 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:34</v>
@@ -515,7 +515,7 @@
         <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B4" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:24</v>
@@ -591,7 +591,7 @@
         <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B6" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>5:01</v>
@@ -626,7 +626,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B7" t="str">
         <v>12 hours ago</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">
@@ -705,7 +705,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B9" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>2:56</v>
@@ -819,7 +819,7 @@
         <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B12" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v>4:37</v>
@@ -857,7 +857,7 @@
         <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:06</v>
@@ -895,7 +895,7 @@
         <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B14" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:54</v>
@@ -2643,7 +2643,7 @@
         <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
       </c>
       <c r="B60" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>4:11</v>
@@ -3935,7 +3935,7 @@
         <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v>3:57</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>3 hours ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>3 hours ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:34</v>
@@ -477,7 +477,7 @@
         <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:01</v>
@@ -515,7 +515,7 @@
         <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B4" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:24</v>
@@ -553,7 +553,7 @@
         <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:52</v>
@@ -591,7 +591,7 @@
         <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B6" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>5:01</v>
@@ -629,7 +629,7 @@
         <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B7" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:12</v>
@@ -667,7 +667,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:59</v>
@@ -705,7 +705,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B9" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>2:56</v>
@@ -743,7 +743,7 @@
         <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:46</v>
@@ -781,7 +781,7 @@
         <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B11" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G11" t="str">
         <v>2:47</v>
@@ -819,7 +819,7 @@
         <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B12" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
         <v>4:37</v>
@@ -857,7 +857,7 @@
         <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:06</v>
@@ -895,7 +895,7 @@
         <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B14" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:54</v>
@@ -933,7 +933,7 @@
         <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
         <v>4:10</v>
@@ -971,7 +971,7 @@
         <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G16" t="str">
         <v>3:26</v>
@@ -1047,7 +1047,7 @@
         <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G18" t="str">
         <v>2:56</v>
@@ -1085,7 +1085,7 @@
         <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G19" t="str">
         <v>4:01</v>
@@ -1123,7 +1123,7 @@
         <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G20" t="str">
         <v>3:05</v>
@@ -1161,7 +1161,7 @@
         <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G21" t="str">
         <v>2:27</v>
@@ -1199,7 +1199,7 @@
         <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G22" t="str">
         <v>2:34</v>
@@ -1237,7 +1237,7 @@
         <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G23" t="str">
         <v>3:13</v>
@@ -1275,7 +1275,7 @@
         <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B24" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G24" t="str">
         <v>3:13</v>
@@ -1313,7 +1313,7 @@
         <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G25" t="str">
         <v>3:08</v>
@@ -1617,7 +1617,7 @@
         <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>3:06</v>
@@ -1655,7 +1655,7 @@
         <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>3:21</v>
@@ -2073,7 +2073,7 @@
         <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B45" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>2:25</v>
@@ -2111,7 +2111,7 @@
         <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>1:14</v>
@@ -2149,7 +2149,7 @@
         <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B47" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>2:59</v>
@@ -2187,7 +2187,7 @@
         <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B48" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>2:29</v>
@@ -2225,7 +2225,7 @@
         <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B49" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>2:34</v>
@@ -2263,7 +2263,7 @@
         <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>3:48</v>
@@ -2301,7 +2301,7 @@
         <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B51" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>3:32</v>
@@ -2339,7 +2339,7 @@
         <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B52" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>3:49</v>
@@ -2377,7 +2377,7 @@
         <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
         <v>4:28</v>
@@ -2415,7 +2415,7 @@
         <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
         <v>3:37</v>
@@ -2453,7 +2453,7 @@
         <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>3:35</v>
@@ -2833,7 +2833,7 @@
         <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G65" t="str">
         <v>3:59</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>4 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>4 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:34</v>
@@ -477,7 +477,7 @@
         <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:01</v>
@@ -515,7 +515,7 @@
         <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B4" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:24</v>
@@ -553,7 +553,7 @@
         <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:52</v>
@@ -591,7 +591,7 @@
         <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B6" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>5:01</v>
@@ -626,10 +626,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B7" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:12</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">
@@ -667,7 +667,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:59</v>
@@ -705,7 +705,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B9" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>2:56</v>
@@ -743,7 +743,7 @@
         <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:46</v>
@@ -781,7 +781,7 @@
         <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B11" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G11" t="str">
         <v>2:47</v>
@@ -2605,7 +2605,7 @@
         <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B59" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
         <v>3:11</v>
@@ -3897,7 +3897,7 @@
         <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v>5:11</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:34</v>
@@ -477,7 +477,7 @@
         <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:01</v>
@@ -515,7 +515,7 @@
         <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B4" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:24</v>
@@ -553,7 +553,7 @@
         <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:52</v>
@@ -591,7 +591,7 @@
         <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B6" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>5:01</v>
@@ -626,10 +626,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B7" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:12</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">
@@ -667,7 +667,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:59</v>
@@ -705,7 +705,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B9" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>2:56</v>
@@ -743,7 +743,7 @@
         <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:46</v>
@@ -781,7 +781,7 @@
         <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B11" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G11" t="str">
         <v>2:47</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:34</v>
@@ -477,7 +477,7 @@
         <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:01</v>
@@ -515,7 +515,7 @@
         <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B4" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:24</v>
@@ -553,7 +553,7 @@
         <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:52</v>
@@ -591,7 +591,7 @@
         <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B6" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>5:01</v>
@@ -629,7 +629,7 @@
         <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B7" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:12</v>
@@ -667,7 +667,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:59</v>
@@ -705,7 +705,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B9" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>2:56</v>
@@ -743,7 +743,7 @@
         <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:46</v>
@@ -781,7 +781,7 @@
         <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B11" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
         <v>2:47</v>
@@ -2795,7 +2795,7 @@
         <v>Teo Glacier - Don't Mind (Music Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>2:47</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:34</v>
@@ -477,7 +477,7 @@
         <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:01</v>
@@ -515,7 +515,7 @@
         <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B4" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:24</v>
@@ -553,7 +553,7 @@
         <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:52</v>
@@ -591,7 +591,7 @@
         <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B6" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>5:01</v>
@@ -626,10 +626,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B7" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:12</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">
@@ -667,7 +667,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:59</v>
@@ -705,7 +705,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B9" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
         <v>2:56</v>
@@ -2757,7 +2757,7 @@
         <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B63" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G63" t="str">
         <v>4:42</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:34</v>
@@ -477,7 +477,7 @@
         <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:01</v>
@@ -515,7 +515,7 @@
         <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B4" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:24</v>
@@ -553,7 +553,7 @@
         <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:52</v>
@@ -591,7 +591,7 @@
         <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B6" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>5:01</v>
@@ -626,10 +626,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B7" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:12</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">
@@ -667,7 +667,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:59</v>
@@ -2035,7 +2035,7 @@
         <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>2:01</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -477,7 +477,7 @@
         <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:01</v>
@@ -515,7 +515,7 @@
         <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B4" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:24</v>
@@ -553,7 +553,7 @@
         <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:52</v>
@@ -591,7 +591,7 @@
         <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B6" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>5:01</v>
@@ -626,10 +626,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B7" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:12</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">
@@ -1427,7 +1427,7 @@
         <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>4:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>9 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>9 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:34</v>
@@ -477,7 +477,7 @@
         <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:01</v>
@@ -515,7 +515,7 @@
         <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B4" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:24</v>
@@ -553,7 +553,7 @@
         <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:52</v>
@@ -591,7 +591,7 @@
         <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B6" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>5:01</v>
@@ -629,7 +629,7 @@
         <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B7" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:12</v>
@@ -1579,7 +1579,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B32" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>3:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:34</v>
@@ -477,7 +477,7 @@
         <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:01</v>
@@ -515,7 +515,7 @@
         <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B4" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:24</v>
@@ -553,7 +553,7 @@
         <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:52</v>
@@ -591,7 +591,7 @@
         <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B6" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>5:01</v>
@@ -629,7 +629,7 @@
         <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B7" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:12</v>
@@ -1541,7 +1541,7 @@
         <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B31" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>3:10</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:34</v>
@@ -477,7 +477,7 @@
         <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:01</v>
@@ -515,7 +515,7 @@
         <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B4" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:24</v>
@@ -553,7 +553,7 @@
         <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:52</v>
@@ -591,7 +591,7 @@
         <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B6" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>5:01</v>
@@ -629,7 +629,7 @@
         <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B7" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:12</v>
@@ -1997,7 +1997,7 @@
         <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B43" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>3:25</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:34</v>
@@ -477,7 +477,7 @@
         <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:01</v>
@@ -515,7 +515,7 @@
         <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B4" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:24</v>
@@ -553,7 +553,7 @@
         <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:52</v>
@@ -591,7 +591,7 @@
         <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B6" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>5:01</v>
@@ -629,7 +629,7 @@
         <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B7" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:12</v>
@@ -1959,7 +1959,7 @@
         <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>2:54</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:34</v>
@@ -477,7 +477,7 @@
         <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:01</v>
@@ -515,7 +515,7 @@
         <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B4" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:24</v>
@@ -553,7 +553,7 @@
         <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:52</v>
@@ -591,7 +591,7 @@
         <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B6" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
         <v>5:01</v>
@@ -629,7 +629,7 @@
         <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B7" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:12</v>
@@ -1769,7 +1769,7 @@
         <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B37" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>3:45</v>
@@ -2567,7 +2567,7 @@
         <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B58" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
         <v>5:24</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -477,7 +477,7 @@
         <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:01</v>
@@ -515,7 +515,7 @@
         <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B4" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:24</v>
@@ -553,7 +553,7 @@
         <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:52</v>
@@ -626,7 +626,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">
@@ -1009,7 +1009,7 @@
         <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>2:56</v>
@@ -1389,7 +1389,7 @@
         <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>2:59</v>
@@ -1883,7 +1883,7 @@
         <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B40" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>4:27</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:34</v>
@@ -477,7 +477,7 @@
         <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:01</v>
@@ -1921,7 +1921,7 @@
         <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B41" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>4:34</v>
@@ -2529,7 +2529,7 @@
         <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B57" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>3:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -626,7 +626,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">
@@ -1465,7 +1465,7 @@
         <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>4:09</v>
@@ -1731,7 +1731,7 @@
         <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B36" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>3:17</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>17 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>17 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:34</v>
@@ -626,7 +626,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:34</v>
@@ -626,7 +626,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -626,7 +626,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">
@@ -1845,7 +1845,7 @@
         <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>3:03</v>
@@ -2719,7 +2719,7 @@
         <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
       </c>
       <c r="B62" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>4:16</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:34</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:34</v>
@@ -626,7 +626,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">
@@ -1693,7 +1693,7 @@
         <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B35" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>7:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,19 +439,19 @@
         <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:34</v>
@@ -483,7 +483,7 @@
         <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1351,19 +1351,19 @@
         <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B26" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>5:14</v>
@@ -1395,7 +1395,7 @@
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2491,19 +2491,19 @@
         <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
         <v>2:31</v>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2681,19 +2681,19 @@
         <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B61" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G61" t="str">
         <v>3:31</v>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=R2k_wPsAHKQ</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=wo9yPPCh75Q</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:34</v>
@@ -1503,7 +1503,7 @@
         <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>2:34</v>
@@ -1807,7 +1807,7 @@
         <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B38" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>3:57</v>
@@ -2643,7 +2643,7 @@
         <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
       </c>
       <c r="B60" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>4:11</v>
@@ -2871,7 +2871,7 @@
         <v>Louie TheSinger "Texas Gold" Official Music Video</v>
       </c>
       <c r="B66" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G66" t="str">
         <v>4:09</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -626,7 +626,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">
@@ -819,7 +819,7 @@
         <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>4:37</v>
@@ -857,7 +857,7 @@
         <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:06</v>
@@ -895,7 +895,7 @@
         <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B14" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:54</v>
@@ -933,7 +933,7 @@
         <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>4:10</v>
@@ -971,7 +971,7 @@
         <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>3:26</v>
@@ -1047,7 +1047,7 @@
         <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>2:56</v>
@@ -1085,7 +1085,7 @@
         <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>4:01</v>
@@ -1123,7 +1123,7 @@
         <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>3:05</v>
@@ -1161,7 +1161,7 @@
         <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>2:27</v>
@@ -1199,7 +1199,7 @@
         <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>2:34</v>
@@ -1237,7 +1237,7 @@
         <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>3:13</v>
@@ -1275,7 +1275,7 @@
         <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B24" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>3:13</v>
@@ -1313,7 +1313,7 @@
         <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>3:08</v>
@@ -1617,7 +1617,7 @@
         <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>3:06</v>
@@ -1655,7 +1655,7 @@
         <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>3:21</v>
@@ -2073,7 +2073,7 @@
         <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B45" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>2:25</v>
@@ -2111,7 +2111,7 @@
         <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B46" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>1:14</v>
@@ -2149,7 +2149,7 @@
         <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B47" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>2:59</v>
@@ -2187,7 +2187,7 @@
         <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B48" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>2:29</v>
@@ -2225,7 +2225,7 @@
         <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B49" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>2:34</v>
@@ -2263,7 +2263,7 @@
         <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>3:48</v>
@@ -2301,7 +2301,7 @@
         <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B51" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>3:32</v>
@@ -2339,7 +2339,7 @@
         <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B52" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>3:49</v>
@@ -2377,7 +2377,7 @@
         <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G53" t="str">
         <v>4:28</v>
@@ -2415,7 +2415,7 @@
         <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G54" t="str">
         <v>3:37</v>
@@ -2453,7 +2453,7 @@
         <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>3:35</v>
@@ -2833,7 +2833,7 @@
         <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G65" t="str">
         <v>3:59</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -2605,7 +2605,7 @@
         <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B59" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G59" t="str">
         <v>3:11</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -626,7 +626,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -626,7 +626,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">
@@ -743,7 +743,7 @@
         <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:46</v>
@@ -781,7 +781,7 @@
         <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>2:47</v>
@@ -2795,7 +2795,7 @@
         <v>Teo Glacier - Don't Mind (Music Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>2:47</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -626,7 +626,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">
@@ -705,7 +705,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>2:56</v>
@@ -2757,7 +2757,7 @@
         <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B63" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G63" t="str">
         <v>4:42</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -667,7 +667,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:59</v>
@@ -2035,7 +2035,7 @@
         <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>2:01</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -1427,7 +1427,7 @@
         <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>4:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -1579,7 +1579,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B32" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>3:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -1541,7 +1541,7 @@
         <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B31" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>3:10</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -626,7 +626,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">
@@ -1997,7 +1997,7 @@
         <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B43" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>3:25</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -1959,7 +1959,7 @@
         <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>2:54</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -591,7 +591,7 @@
         <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
         <v>5:01</v>
@@ -626,10 +626,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:12</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">
@@ -1769,7 +1769,7 @@
         <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B37" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>3:45</v>
@@ -2567,7 +2567,7 @@
         <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B58" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G58" t="str">
         <v>5:24</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -515,7 +515,7 @@
         <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:24</v>
@@ -553,7 +553,7 @@
         <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:52</v>
@@ -1009,7 +1009,7 @@
         <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>2:56</v>
@@ -1389,7 +1389,7 @@
         <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>2:59</v>
@@ -1883,7 +1883,7 @@
         <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B40" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>4:27</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -477,7 +477,7 @@
         <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:01</v>
@@ -626,7 +626,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B7" t="str">
         <v>2 days ago</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">
@@ -1921,7 +1921,7 @@
         <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B41" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>4:34</v>
@@ -2529,7 +2529,7 @@
         <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B57" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>3:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -626,7 +626,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B7" t="str">
         <v>2 days ago</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">
@@ -1465,7 +1465,7 @@
         <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>4:09</v>
@@ -1731,7 +1731,7 @@
         <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B36" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>3:17</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -626,7 +626,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B7" t="str">
         <v>2 days ago</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">
@@ -3859,7 +3859,7 @@
         <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v>3:42</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -626,7 +626,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B7" t="str">
         <v>2 days ago</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -1845,7 +1845,7 @@
         <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>3:03</v>
@@ -2719,7 +2719,7 @@
         <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
       </c>
       <c r="B62" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>4:16</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -626,7 +626,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B7" t="str">
         <v>2 days ago</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">
@@ -1693,7 +1693,7 @@
         <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B35" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>7:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -626,7 +626,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B7" t="str">
         <v>2 days ago</v>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1351,19 +1351,19 @@
         <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>5:14</v>
@@ -1395,7 +1395,7 @@
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2491,19 +2491,19 @@
         <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G56" t="str">
         <v>2:31</v>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2681,19 +2681,19 @@
         <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B61" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G61" t="str">
         <v>3:31</v>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=R2k_wPsAHKQ</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=wo9yPPCh75Q</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:34</v>
@@ -626,7 +626,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B7" t="str">
         <v>2 days ago</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">
@@ -1807,7 +1807,7 @@
         <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B38" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>3:57</v>
@@ -2871,7 +2871,7 @@
         <v>Louie TheSinger "Texas Gold" Official Music Video</v>
       </c>
       <c r="B66" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
         <v>4:09</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -626,7 +626,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B7" t="str">
         <v>2 days ago</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">
@@ -1503,7 +1503,7 @@
         <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>2:34</v>
@@ -2643,7 +2643,7 @@
         <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
       </c>
       <c r="B60" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>4:11</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -819,7 +819,7 @@
         <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B12" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>4:37</v>
@@ -857,7 +857,7 @@
         <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:06</v>
@@ -895,7 +895,7 @@
         <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:54</v>
@@ -933,7 +933,7 @@
         <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>4:10</v>
@@ -971,7 +971,7 @@
         <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>3:26</v>
@@ -1047,7 +1047,7 @@
         <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>2:56</v>
@@ -1085,7 +1085,7 @@
         <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>4:01</v>
@@ -1123,7 +1123,7 @@
         <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>3:05</v>
@@ -1161,7 +1161,7 @@
         <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>2:27</v>
@@ -1199,7 +1199,7 @@
         <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>2:34</v>
@@ -1237,7 +1237,7 @@
         <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>3:13</v>
@@ -1275,7 +1275,7 @@
         <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B24" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>3:13</v>
@@ -1313,7 +1313,7 @@
         <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>3:08</v>
@@ -1617,7 +1617,7 @@
         <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>3:06</v>
@@ -1655,7 +1655,7 @@
         <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>3:21</v>
@@ -2073,7 +2073,7 @@
         <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B45" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>2:25</v>
@@ -2111,7 +2111,7 @@
         <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B46" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>1:14</v>
@@ -2149,7 +2149,7 @@
         <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B47" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>2:59</v>
@@ -2187,7 +2187,7 @@
         <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B48" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>2:29</v>
@@ -2225,7 +2225,7 @@
         <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B49" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>2:34</v>
@@ -2263,7 +2263,7 @@
         <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>3:48</v>
@@ -2301,7 +2301,7 @@
         <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B51" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>3:32</v>
@@ -2339,7 +2339,7 @@
         <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B52" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>3:49</v>
@@ -2377,7 +2377,7 @@
         <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G53" t="str">
         <v>4:28</v>
@@ -2415,7 +2415,7 @@
         <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G54" t="str">
         <v>3:37</v>
@@ -2453,7 +2453,7 @@
         <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>3:35</v>
@@ -2605,7 +2605,7 @@
         <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B59" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G59" t="str">
         <v>3:11</v>
@@ -2833,7 +2833,7 @@
         <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G65" t="str">
         <v>3:59</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -743,7 +743,7 @@
         <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:46</v>
@@ -781,7 +781,7 @@
         <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>2:47</v>
@@ -2757,7 +2757,7 @@
         <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B63" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G63" t="str">
         <v>4:42</v>
@@ -2795,7 +2795,7 @@
         <v>Teo Glacier - Don't Mind (Music Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>2:47</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -626,7 +626,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B7" t="str">
         <v>2 days ago</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">
@@ -705,7 +705,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>2:56</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -667,7 +667,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:59</v>
@@ -2035,7 +2035,7 @@
         <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>2:01</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -626,7 +626,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B7" t="str">
         <v>2 days ago</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">
@@ -1427,7 +1427,7 @@
         <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>4:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -1579,7 +1579,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B32" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>3:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -1541,7 +1541,7 @@
         <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B31" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>3:10</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -1997,7 +1997,7 @@
         <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B43" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>3:25</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -1959,7 +1959,7 @@
         <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>2:54</v>
@@ -3687,7 +3687,7 @@
         <v>2:06</v>
       </c>
       <c r="H87" t="str">
-        <v>Estas Tonne</v>
+        <v>Estás Tonné</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,7 +3699,7 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estas Tonne</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estás Tonné</v>
       </c>
     </row>
     <row r="88">

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -591,7 +591,7 @@
         <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G6" t="str">
         <v>5:01</v>
@@ -629,7 +629,7 @@
         <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:12</v>
@@ -1769,7 +1769,7 @@
         <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B37" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>3:45</v>
@@ -2567,7 +2567,7 @@
         <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B58" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G58" t="str">
         <v>5:24</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -515,7 +515,7 @@
         <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B4" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:24</v>
@@ -553,7 +553,7 @@
         <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:52</v>
@@ -626,7 +626,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B7" t="str">
         <v>3 days ago</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">
@@ -1009,7 +1009,7 @@
         <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>2:56</v>
@@ -1389,7 +1389,7 @@
         <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>2:59</v>
@@ -1883,7 +1883,7 @@
         <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B40" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>4:27</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -477,7 +477,7 @@
         <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:01</v>
@@ -626,7 +626,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B7" t="str">
         <v>3 days ago</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">
@@ -1921,7 +1921,7 @@
         <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B41" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>4:34</v>
@@ -2529,7 +2529,7 @@
         <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B57" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>3:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -1465,7 +1465,7 @@
         <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>4:09</v>
@@ -1731,7 +1731,7 @@
         <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B36" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>3:17</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -3821,7 +3821,7 @@
         <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v>3:49</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -626,7 +626,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B7" t="str">
         <v>3 days ago</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -626,7 +626,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B7" t="str">
         <v>3 days ago</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">
@@ -1845,7 +1845,7 @@
         <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>3:03</v>
@@ -2719,7 +2719,7 @@
         <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
       </c>
       <c r="B62" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>4:16</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -626,7 +626,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B7" t="str">
         <v>3 days ago</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="8">
@@ -1693,7 +1693,7 @@
         <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B35" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>7:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -436,28 +436,28 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B2" t="str">
-        <v>2 days ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>2 days ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v>3:34</v>
+        <v>3:20</v>
       </c>
       <c r="H2" t="str">
-        <v>Clinton Kane</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,33 +469,33 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G3" t="str">
-        <v>4:01</v>
+        <v>3:34</v>
       </c>
       <c r="H3" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -530,10 +530,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G4" t="str">
-        <v>3:24</v>
+        <v>4:01</v>
       </c>
       <c r="H4" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B5" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -568,10 +568,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G5" t="str">
-        <v>5:52</v>
+        <v>3:24</v>
       </c>
       <c r="H5" t="str">
-        <v>Harry Styles</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B6" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -606,10 +606,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v>5:01</v>
+        <v>5:52</v>
       </c>
       <c r="H6" t="str">
-        <v>Neal Francis</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B7" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -644,10 +644,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>4:12</v>
+        <v>5:01</v>
       </c>
       <c r="H7" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B8" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -682,10 +682,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:59</v>
+        <v>4:12</v>
       </c>
       <c r="H8" t="str">
-        <v>Holly Humberstone</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B9" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -720,10 +720,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>2:56</v>
+        <v>3:59</v>
       </c>
       <c r="H9" t="str">
-        <v>Cliff Richard</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B10" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -758,10 +758,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:46</v>
+        <v>2:56</v>
       </c>
       <c r="H10" t="str">
-        <v>Jessie Ware</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,21 +773,21 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Dean Lewis - I Am Getting Well</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B11" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -796,10 +796,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>2:47</v>
+        <v>3:46</v>
       </c>
       <c r="H11" t="str">
-        <v>Dean Lewis</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,21 +811,21 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Dean Lewis - I Am Getting Well - Dean Lewis</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B12" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -834,10 +834,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>4:37</v>
+        <v>2:47</v>
       </c>
       <c r="H12" t="str">
-        <v>Bella White</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,21 +849,21 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Dean Lewis - I Am Getting Well - Dean Lewis</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B13" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -872,10 +872,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>4:06</v>
+        <v>4:37</v>
       </c>
       <c r="H13" t="str">
-        <v>Ryan Wright</v>
+        <v>Bella White</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,21 +887,21 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B14" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -910,10 +910,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:54</v>
+        <v>4:06</v>
       </c>
       <c r="H14" t="str">
-        <v>Dove Cameron</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,21 +925,21 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B15" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -948,10 +948,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>4:10</v>
+        <v>3:54</v>
       </c>
       <c r="H15" t="str">
-        <v>Parker McCollum</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,21 +963,21 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B16" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -986,10 +986,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:26</v>
+        <v>4:10</v>
       </c>
       <c r="H16" t="str">
-        <v>Matt Hansen</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,33 +1001,33 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>2:56</v>
+        <v>3:26</v>
       </c>
       <c r="H17" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,33 +1039,33 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>2:56</v>
       </c>
       <c r="H18" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,21 +1077,21 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B19" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1100,10 +1100,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>4:01</v>
+        <v>2:56</v>
       </c>
       <c r="H19" t="str">
-        <v>Tauren Wells</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,21 +1115,21 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1138,10 +1138,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:05</v>
+        <v>4:01</v>
       </c>
       <c r="H20" t="str">
-        <v>Maiah Manser</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,21 +1153,21 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B21" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1176,10 +1176,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>2:27</v>
+        <v>3:05</v>
       </c>
       <c r="H21" t="str">
-        <v>Taylor Austin Dye</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,21 +1191,21 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Chelsea Cutler - BAD (Official Video)</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B22" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1214,10 +1214,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>2:34</v>
+        <v>2:27</v>
       </c>
       <c r="H22" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,21 +1229,21 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B23" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1252,10 +1252,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:13</v>
+        <v>2:34</v>
       </c>
       <c r="H23" t="str">
-        <v>Ashley Kutcher</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,21 +1267,21 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
+        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1293,7 +1293,7 @@
         <v>3:13</v>
       </c>
       <c r="H24" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Ashley Kutcher</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,21 +1305,21 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B25" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
+        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1328,10 +1328,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:08</v>
+        <v>3:13</v>
       </c>
       <c r="H25" t="str">
-        <v>CAIN</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,21 +1343,21 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Harry Styles - Aperture (Official Audio)</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B26" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
+        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1366,10 +1366,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>5:14</v>
+        <v>3:08</v>
       </c>
       <c r="H26" t="str">
-        <v>Harry Styles</v>
+        <v>CAIN</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,21 +1381,21 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B27" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1404,10 +1404,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>2:59</v>
+        <v>5:14</v>
       </c>
       <c r="H27" t="str">
-        <v>Lana Lubany</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,21 +1419,21 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B28" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1442,10 +1442,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:21</v>
+        <v>2:59</v>
       </c>
       <c r="H28" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,33 +1457,33 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>4:09</v>
+        <v>4:21</v>
       </c>
       <c r="H29" t="str">
-        <v>Dermot Kennedy</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,21 +1495,21 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1518,10 +1518,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:34</v>
+        <v>4:09</v>
       </c>
       <c r="H30" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,33 +1533,33 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:10</v>
+        <v>2:34</v>
       </c>
       <c r="H31" t="str">
-        <v>Olivia Dean</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,21 +1571,21 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B32" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1594,10 +1594,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:21</v>
+        <v>3:10</v>
       </c>
       <c r="H32" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,21 +1609,21 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B33" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1632,10 +1632,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:06</v>
+        <v>3:21</v>
       </c>
       <c r="H33" t="str">
-        <v>The Avett Brothers</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,21 +1647,21 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B34" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1670,10 +1670,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:21</v>
+        <v>3:06</v>
       </c>
       <c r="H34" t="str">
-        <v>Jordana Bryant</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,33 +1685,33 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>7:21</v>
+        <v>3:21</v>
       </c>
       <c r="H35" t="str">
-        <v>Katy Perry</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,21 +1723,21 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B36" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1746,10 +1746,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:17</v>
+        <v>7:21</v>
       </c>
       <c r="H36" t="str">
-        <v>Lauren Watkins</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,33 +1761,33 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B37" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:45</v>
+        <v>3:17</v>
       </c>
       <c r="H37" t="str">
-        <v>Tones And I</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,21 +1799,21 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B38" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1822,10 +1822,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:57</v>
+        <v>3:45</v>
       </c>
       <c r="H38" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Tones And I</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,33 +1837,33 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B39" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:03</v>
+        <v>3:57</v>
       </c>
       <c r="H39" t="str">
-        <v>Charlie Puth</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,21 +1875,21 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B40" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1898,10 +1898,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>4:27</v>
+        <v>3:03</v>
       </c>
       <c r="H40" t="str">
-        <v>Chappell Roan</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,21 +1913,21 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B41" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1936,10 +1936,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>4:34</v>
+        <v>4:27</v>
       </c>
       <c r="H41" t="str">
-        <v>Armik</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,21 +1951,21 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B42" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -1974,10 +1974,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:54</v>
+        <v>4:34</v>
       </c>
       <c r="H42" t="str">
-        <v>LØLØ</v>
+        <v>Armik</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,21 +1989,21 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B43" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2012,10 +2012,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:25</v>
+        <v>2:54</v>
       </c>
       <c r="H43" t="str">
-        <v>Tenille Townes</v>
+        <v>LØLØ</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,21 +2027,21 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B44" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2050,10 +2050,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:01</v>
+        <v>3:25</v>
       </c>
       <c r="H44" t="str">
-        <v>Alan Walker</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,21 +2065,21 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B45" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2088,10 +2088,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>2:25</v>
+        <v>2:01</v>
       </c>
       <c r="H45" t="str">
-        <v>Charli xcx</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,21 +2103,21 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B46" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2126,10 +2126,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>1:14</v>
+        <v>2:25</v>
       </c>
       <c r="H46" t="str">
-        <v>Labrinth</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,21 +2141,21 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B47" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2164,10 +2164,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>2:59</v>
+        <v>1:14</v>
       </c>
       <c r="H47" t="str">
-        <v>Charlie Puth</v>
+        <v>Labrinth</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,21 +2179,21 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B48" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2202,10 +2202,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>2:29</v>
+        <v>2:59</v>
       </c>
       <c r="H48" t="str">
-        <v>Girl Tones</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,21 +2217,21 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B49" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2240,10 +2240,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>2:34</v>
+        <v>2:29</v>
       </c>
       <c r="H49" t="str">
-        <v>Jagwar Twin</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,21 +2255,21 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B50" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2278,10 +2278,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:48</v>
+        <v>2:34</v>
       </c>
       <c r="H50" t="str">
-        <v>Caroline Jones</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,21 +2293,21 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B51" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2316,10 +2316,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:32</v>
+        <v>3:48</v>
       </c>
       <c r="H51" t="str">
-        <v>The Beaches</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,21 +2331,21 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B52" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2354,10 +2354,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:49</v>
+        <v>3:32</v>
       </c>
       <c r="H52" t="str">
-        <v>Dolly Parton</v>
+        <v>The Beaches</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,21 +2369,21 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B53" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2392,10 +2392,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>4:28</v>
+        <v>3:49</v>
       </c>
       <c r="H53" t="str">
-        <v>Madison Beer</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,21 +2407,21 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2430,10 +2430,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:37</v>
+        <v>4:28</v>
       </c>
       <c r="H54" t="str">
-        <v>Ty Myers</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,21 +2445,21 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B55" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2468,10 +2468,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:35</v>
+        <v>3:37</v>
       </c>
       <c r="H55" t="str">
-        <v>Megan Moroney</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,21 +2483,21 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B56" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2506,10 +2506,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>2:31</v>
+        <v>3:35</v>
       </c>
       <c r="H56" t="str">
-        <v>Julia Cole Music</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,21 +2521,21 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B57" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2544,10 +2544,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:21</v>
+        <v>2:31</v>
       </c>
       <c r="H57" t="str">
-        <v>Lily Allen</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,21 +2559,21 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B58" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2582,10 +2582,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>5:24</v>
+        <v>3:21</v>
       </c>
       <c r="H58" t="str">
-        <v>Nickless</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,21 +2597,21 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B59" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2620,10 +2620,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:11</v>
+        <v>5:24</v>
       </c>
       <c r="H59" t="str">
-        <v>Peach PRC</v>
+        <v>Nickless</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,21 +2635,21 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
+        <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B60" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
+        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2658,10 +2658,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>4:11</v>
+        <v>3:11</v>
       </c>
       <c r="H60" t="str">
-        <v>Ocean Alley</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,21 +2673,21 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
+        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
       </c>
       <c r="B61" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
+        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2696,10 +2696,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:31</v>
+        <v>4:11</v>
       </c>
       <c r="H61" t="str">
-        <v>OneRepublic</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,21 +2711,21 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B62" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
+        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2734,10 +2734,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>4:16</v>
+        <v>3:31</v>
       </c>
       <c r="H62" t="str">
-        <v>Ty Myers</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,21 +2749,21 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
       </c>
       <c r="B63" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
+        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2772,10 +2772,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>4:42</v>
+        <v>4:16</v>
       </c>
       <c r="H63" t="str">
-        <v>JavaJazzFest</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,33 +2787,33 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video)</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B64" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
+        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:47</v>
+        <v>4:42</v>
       </c>
       <c r="H64" t="str">
-        <v>Teo Glacier</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,21 +2825,21 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
+        <v>Teo Glacier - Don't Mind (Music Video)</v>
       </c>
       <c r="B65" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
+        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2848,10 +2848,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:59</v>
+        <v>2:47</v>
       </c>
       <c r="H65" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>Teo Glacier</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,33 +2863,33 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
+        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>4:09</v>
+        <v>3:59</v>
       </c>
       <c r="H66" t="str">
-        <v>Louie TheSinger</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,21 +2901,21 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>ella jane - When I Was Beautiful (Live)</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
+        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:24</v>
+        <v>4:09</v>
       </c>
       <c r="H67" t="str">
-        <v>ella jane</v>
+        <v>Louie TheSinger</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,21 +2939,21 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Johnny Orlando - Emilia (Official Video)</v>
+        <v>ella jane - When I Was Beautiful (Live)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
+        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:14</v>
+        <v>3:24</v>
       </c>
       <c r="H68" t="str">
-        <v>Johnny Orlando</v>
+        <v>ella jane</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,21 +2977,21 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
+        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video)</v>
+        <v>Johnny Orlando - Emilia (Official Video)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
+        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:32</v>
+        <v>3:14</v>
       </c>
       <c r="H69" t="str">
-        <v>Kungs</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,21 +3015,21 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
+        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
+        <v>Kungs, Theophilus London - Galaxy (official video)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
+        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:15</v>
+        <v>3:32</v>
       </c>
       <c r="H70" t="str">
-        <v>Billy Raffoul</v>
+        <v>Kungs</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,21 +3053,21 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
+        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
+        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:03</v>
+        <v>3:15</v>
       </c>
       <c r="H71" t="str">
-        <v>NathanEvanss</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,21 +3091,21 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Stephen Sanchez - Sweet Love</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
+        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:04</v>
+        <v>3:03</v>
       </c>
       <c r="H72" t="str">
-        <v>Stephen Sanchez</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,21 +3129,21 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video]</v>
+        <v>Stephen Sanchez - Sweet Love</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
+        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:33</v>
+        <v>3:04</v>
       </c>
       <c r="H73" t="str">
-        <v>Bruno Mars</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,21 +3167,21 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
+        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
+        <v>Bruno Mars - I Just Might [Official Music Video]</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
+        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:53</v>
+        <v>3:33</v>
       </c>
       <c r="H74" t="str">
-        <v>MAX</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,21 +3205,21 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
+        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
+        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>4:11</v>
+        <v>2:53</v>
       </c>
       <c r="H75" t="str">
-        <v>Jessie J</v>
+        <v>MAX</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,21 +3243,21 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
+        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:45</v>
+        <v>4:11</v>
       </c>
       <c r="H76" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Jessie J</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,21 +3281,21 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
+        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>4:00</v>
+        <v>2:45</v>
       </c>
       <c r="H77" t="str">
-        <v>Brandon Lake and Cody Johnson</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,21 +3319,21 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
+        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:27</v>
+        <v>4:00</v>
       </c>
       <c r="H78" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Brandon Lake and Cody Johnson</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,21 +3357,21 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
+        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:25</v>
+        <v>3:27</v>
       </c>
       <c r="H79" t="str">
-        <v>Olivia Dean</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,21 +3395,21 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
+        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:34</v>
+        <v>3:25</v>
       </c>
       <c r="H80" t="str">
-        <v>Demi Lovato</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,21 +3433,21 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Train - Mittens (Live on TODAY)</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=R2k_wPsAHKQ</v>
+        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:17</v>
+        <v>3:34</v>
       </c>
       <c r="H81" t="str">
-        <v>Train</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,21 +3471,21 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Train - Mittens (Live on TODAY) - Train</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
+        <v>Train - Mittens (Live on TODAY)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
+        <v>https://www.youtube.com/watch?v=R2k_wPsAHKQ</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:25</v>
+        <v>3:17</v>
       </c>
       <c r="H82" t="str">
-        <v>Joseph</v>
+        <v>Train</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,21 +3509,21 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
+        <v>Train - Mittens (Live on TODAY) - Train</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
+        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:26</v>
+        <v>2:25</v>
       </c>
       <c r="H83" t="str">
-        <v>Demi Lovato</v>
+        <v>Joseph</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,21 +3547,21 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
+        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>4:46</v>
+        <v>3:26</v>
       </c>
       <c r="H84" t="str">
-        <v>Keith Urban</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,21 +3585,21 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
+        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3608,7 +3608,7 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:24</v>
+        <v>4:46</v>
       </c>
       <c r="H85" t="str">
         <v>Keith Urban</v>
@@ -3623,21 +3623,21 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
+        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:52</v>
+        <v>3:24</v>
       </c>
       <c r="H86" t="str">
-        <v>Madonna</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,21 +3661,21 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
+        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:06</v>
+        <v>2:52</v>
       </c>
       <c r="H87" t="str">
-        <v>Estás Tonné</v>
+        <v>Madonna</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,21 +3699,21 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estás Tonné</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Anna Graves - Burn On (Official Music Video)</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
+        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:09</v>
+        <v>2:06</v>
       </c>
       <c r="H88" t="str">
-        <v>Anna Graves</v>
+        <v>Estás Tonné</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,21 +3737,21 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estás Tonné</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
+        <v>Anna Graves - Burn On (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
+        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>5:11</v>
+        <v>3:09</v>
       </c>
       <c r="H89" t="str">
-        <v>Ocean Alley</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,21 +3775,21 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
+        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
+        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:40</v>
+        <v>5:11</v>
       </c>
       <c r="H90" t="str">
-        <v>Zara Larsson</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,33 +3813,33 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
       </c>
       <c r="B91" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
+        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:49</v>
+        <v>3:40</v>
       </c>
       <c r="H91" t="str">
-        <v>Lauren Watkins</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,21 +3851,21 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B92" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
+        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3874,10 +3874,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:42</v>
+        <v>3:49</v>
       </c>
       <c r="H92" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,21 +3889,21 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B93" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
+        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3912,10 +3912,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>5:11</v>
+        <v>3:42</v>
       </c>
       <c r="H93" t="str">
-        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,21 +3927,21 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B94" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
+        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3950,10 +3950,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:57</v>
+        <v>5:11</v>
       </c>
       <c r="H94" t="str">
-        <v>Lainey Wilson</v>
+        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,21 +3965,21 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video)</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
       </c>
       <c r="B95" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
+        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -3988,10 +3988,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:29</v>
+        <v>3:57</v>
       </c>
       <c r="H95" t="str">
-        <v>Grace Enger</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,21 +4003,21 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video)</v>
+        <v>Grace Enger - All My Songs (Official Lyric Video)</v>
       </c>
       <c r="B96" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
+        <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4026,10 +4026,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:10</v>
+        <v>3:29</v>
       </c>
       <c r="H96" t="str">
-        <v>Alan Walker and 2 more</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,21 +4041,21 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
+        <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Emilia Tarrant - Break Up With Myself</v>
+        <v>Alan Walker - Broken Strings (Official Music Video)</v>
       </c>
       <c r="B97" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
+        <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4064,10 +4064,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:04</v>
+        <v>3:10</v>
       </c>
       <c r="H97" t="str">
-        <v>Emilia Tarrant</v>
+        <v>Alan Walker and 2 more</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,21 +4079,21 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
+        <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026)</v>
+        <v>Emilia Tarrant - Break Up With Myself</v>
       </c>
       <c r="B98" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
+        <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4102,10 +4102,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:09</v>
+        <v>4:04</v>
       </c>
       <c r="H98" t="str">
-        <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Emilia Tarrant</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,21 +4117,21 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer)</v>
+        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026)</v>
       </c>
       <c r="B99" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
+        <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4140,10 +4140,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>2:27</v>
+        <v>3:09</v>
       </c>
       <c r="H99" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,21 +4155,21 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
+        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Maggie Lindemann - fate</v>
+        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer)</v>
       </c>
       <c r="B100" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
+        <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4178,10 +4178,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>2:12</v>
+        <v>2:27</v>
       </c>
       <c r="H100" t="str">
-        <v>Maggie Lindemann</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,21 +4193,21 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Maggie Lindemann - fate - Maggie Lindemann</v>
+        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023)</v>
+        <v>Maggie Lindemann - fate</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=wo9yPPCh75Q</v>
+        <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4216,10 +4216,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>4:44</v>
+        <v>2:12</v>
       </c>
       <c r="H101" t="str">
-        <v>Cliff Richard</v>
+        <v>Maggie Lindemann</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023) - Cliff Richard</v>
+        <v>Maggie Lindemann - fate - Maggie Lindemann</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B2" t="str">
-        <v>4 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>4 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:20</v>
@@ -477,7 +477,7 @@
         <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:34</v>
@@ -664,7 +664,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B8" t="str">
         <v>3 days ago</v>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="9">
@@ -1845,7 +1845,7 @@
         <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B39" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>3:57</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B2" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:20</v>
@@ -664,7 +664,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B8" t="str">
         <v>3 days ago</v>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="9">
@@ -1541,7 +1541,7 @@
         <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>2:34</v>
@@ -2681,7 +2681,7 @@
         <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
       </c>
       <c r="B61" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G61" t="str">
         <v>4:11</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B2" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:20</v>
@@ -857,7 +857,7 @@
         <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B13" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:37</v>
@@ -895,7 +895,7 @@
         <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>4:06</v>
@@ -933,7 +933,7 @@
         <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B15" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>3:54</v>
@@ -971,7 +971,7 @@
         <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>4:10</v>
@@ -1009,7 +1009,7 @@
         <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:26</v>
@@ -1085,7 +1085,7 @@
         <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>2:56</v>
@@ -1123,7 +1123,7 @@
         <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>4:01</v>
@@ -1161,7 +1161,7 @@
         <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>3:05</v>
@@ -1199,7 +1199,7 @@
         <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>2:27</v>
@@ -1237,7 +1237,7 @@
         <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>2:34</v>
@@ -1275,7 +1275,7 @@
         <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>3:13</v>
@@ -1313,7 +1313,7 @@
         <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B25" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>3:13</v>
@@ -1351,7 +1351,7 @@
         <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>3:08</v>
@@ -1655,7 +1655,7 @@
         <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>3:06</v>
@@ -1693,7 +1693,7 @@
         <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>3:21</v>
@@ -2111,7 +2111,7 @@
         <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B46" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>2:25</v>
@@ -2149,7 +2149,7 @@
         <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B47" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>1:14</v>
@@ -2187,7 +2187,7 @@
         <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B48" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>2:59</v>
@@ -2225,7 +2225,7 @@
         <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B49" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>2:29</v>
@@ -2263,7 +2263,7 @@
         <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B50" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>2:34</v>
@@ -2301,7 +2301,7 @@
         <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>3:48</v>
@@ -2339,7 +2339,7 @@
         <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B52" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>3:32</v>
@@ -2377,7 +2377,7 @@
         <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B53" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G53" t="str">
         <v>3:49</v>
@@ -2415,7 +2415,7 @@
         <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G54" t="str">
         <v>4:28</v>
@@ -2453,7 +2453,7 @@
         <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>3:37</v>
@@ -2491,7 +2491,7 @@
         <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G56" t="str">
         <v>3:35</v>
@@ -2871,7 +2871,7 @@
         <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
         <v>3:59</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B2" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:20</v>
@@ -664,7 +664,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B8" t="str">
         <v>3 days ago</v>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="9">
@@ -2643,7 +2643,7 @@
         <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B60" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>3:11</v>
@@ -3476,13 +3476,13 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Train - Mittens (Live on TODAY)</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=R2k_wPsAHKQ</v>
+        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-27</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:17</v>
+        <v>2:25</v>
       </c>
       <c r="H82" t="str">
-        <v>Train</v>
+        <v>Joseph</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Train - Mittens (Live on TODAY) - Train</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
+        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-27</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:25</v>
+        <v>3:26</v>
       </c>
       <c r="H83" t="str">
-        <v>Joseph</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
+        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-27</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:26</v>
+        <v>4:46</v>
       </c>
       <c r="H84" t="str">
-        <v>Demi Lovato</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
+        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-27</v>
@@ -3608,7 +3608,7 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>4:46</v>
+        <v>3:24</v>
       </c>
       <c r="H85" t="str">
         <v>Keith Urban</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
+        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-27</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:24</v>
+        <v>2:52</v>
       </c>
       <c r="H86" t="str">
-        <v>Keith Urban</v>
+        <v>Madonna</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
+        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-27</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:52</v>
+        <v>2:06</v>
       </c>
       <c r="H87" t="str">
-        <v>Madonna</v>
+        <v>Estás Tonné</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estás Tonné</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
+        <v>Anna Graves - Burn On (Official Music Video)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
+        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-27</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:06</v>
+        <v>3:09</v>
       </c>
       <c r="H88" t="str">
-        <v>Estás Tonné</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estás Tonné</v>
+        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Anna Graves - Burn On (Official Music Video)</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
+        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-27</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:09</v>
+        <v>5:11</v>
       </c>
       <c r="H89" t="str">
-        <v>Anna Graves</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
+        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-27</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>5:11</v>
+        <v>3:40</v>
       </c>
       <c r="H90" t="str">
-        <v>Ocean Alley</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
+        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-27</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:40</v>
+        <v>3:49</v>
       </c>
       <c r="H91" t="str">
-        <v>Zara Larsson</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B92" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
+        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-27</v>
@@ -3874,10 +3874,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:49</v>
+        <v>3:42</v>
       </c>
       <c r="H92" t="str">
-        <v>Lauren Watkins</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B93" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
+        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-27</v>
@@ -3912,10 +3912,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:42</v>
+        <v>5:11</v>
       </c>
       <c r="H93" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
       </c>
       <c r="B94" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
+        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-27</v>
@@ -3950,10 +3950,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>5:11</v>
+        <v>3:57</v>
       </c>
       <c r="H94" t="str">
-        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
+        <v>Grace Enger - All My Songs (Official Lyric Video)</v>
       </c>
       <c r="B95" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
+        <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-27</v>
@@ -3988,10 +3988,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:57</v>
+        <v>3:29</v>
       </c>
       <c r="H95" t="str">
-        <v>Lainey Wilson</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
+        <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video)</v>
+        <v>Alan Walker - Broken Strings (Official Music Video)</v>
       </c>
       <c r="B96" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
+        <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-27</v>
@@ -4026,10 +4026,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:29</v>
+        <v>3:10</v>
       </c>
       <c r="H96" t="str">
-        <v>Grace Enger</v>
+        <v>Alan Walker and 2 more</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
+        <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video)</v>
+        <v>Emilia Tarrant - Break Up With Myself</v>
       </c>
       <c r="B97" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
+        <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-27</v>
@@ -4064,10 +4064,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:10</v>
+        <v>4:04</v>
       </c>
       <c r="H97" t="str">
-        <v>Alan Walker and 2 more</v>
+        <v>Emilia Tarrant</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
+        <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Emilia Tarrant - Break Up With Myself</v>
+        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026)</v>
       </c>
       <c r="B98" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
+        <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-27</v>
@@ -4102,10 +4102,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>4:04</v>
+        <v>3:09</v>
       </c>
       <c r="H98" t="str">
-        <v>Emilia Tarrant</v>
+        <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
+        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026)</v>
+        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer)</v>
       </c>
       <c r="B99" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
+        <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-27</v>
@@ -4140,10 +4140,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:09</v>
+        <v>2:27</v>
       </c>
       <c r="H99" t="str">
-        <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer)</v>
+        <v>Maggie Lindemann - fate</v>
       </c>
       <c r="B100" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
+        <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-27</v>
@@ -4178,10 +4178,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>2:27</v>
+        <v>2:12</v>
       </c>
       <c r="H100" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Maggie Lindemann</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
+        <v>Maggie Lindemann - fate - Maggie Lindemann</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Maggie Lindemann - fate</v>
+        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023)</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
+        <v>https://www.youtube.com/watch?v=wo9yPPCh75Q</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-27</v>
@@ -4216,10 +4216,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>2:12</v>
+        <v>4:44</v>
       </c>
       <c r="H101" t="str">
-        <v>Maggie Lindemann</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Maggie Lindemann - fate - Maggie Lindemann</v>
+        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023) - Cliff Richard</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B2" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:20</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B2" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:20</v>
@@ -664,7 +664,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B8" t="str">
         <v>3 days ago</v>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="9">
@@ -781,7 +781,7 @@
         <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>3:46</v>
@@ -819,7 +819,7 @@
         <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B12" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>2:47</v>
@@ -2833,7 +2833,7 @@
         <v>Teo Glacier - Don't Mind (Music Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
         <v>2:47</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:20</v>
@@ -743,7 +743,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B10" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>2:56</v>
@@ -2795,7 +2795,7 @@
         <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B64" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>4:42</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B2" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:20</v>
@@ -664,7 +664,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B8" t="str">
         <v>3 days ago</v>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="9">
@@ -705,7 +705,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>3:59</v>
@@ -2073,7 +2073,7 @@
         <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>2:01</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B2" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:20</v>
@@ -664,7 +664,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B8" t="str">
         <v>3 days ago</v>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="9">
@@ -1465,7 +1465,7 @@
         <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>4:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B2" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:20</v>
@@ -664,7 +664,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B8" t="str">
         <v>3 days ago</v>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="9">
@@ -1617,7 +1617,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B33" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>3:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B2" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:20</v>
@@ -664,7 +664,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B8" t="str">
         <v>3 days ago</v>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="9">
@@ -1579,7 +1579,7 @@
         <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B32" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>3:10</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B2" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:20</v>
@@ -664,7 +664,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B8" t="str">
         <v>3 days ago</v>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="9">
@@ -2035,7 +2035,7 @@
         <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B44" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>3:25</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>17 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-27</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>17 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v>3:20</v>
+        <v>3:01</v>
       </c>
       <c r="H2" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B3" t="str">
-        <v>3 days ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-27</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>3 days ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>3:34</v>
+        <v>3:20</v>
       </c>
       <c r="H3" t="str">
-        <v>Clinton Kane</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B4" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-27</v>
@@ -530,10 +530,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G4" t="str">
-        <v>4:01</v>
+        <v>3:34</v>
       </c>
       <c r="H4" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B5" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-27</v>
@@ -568,10 +568,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G5" t="str">
-        <v>3:24</v>
+        <v>4:01</v>
       </c>
       <c r="H5" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B6" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-27</v>
@@ -606,10 +606,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v>5:52</v>
+        <v>3:24</v>
       </c>
       <c r="H6" t="str">
-        <v>Harry Styles</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B7" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-27</v>
@@ -644,10 +644,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>5:01</v>
+        <v>5:52</v>
       </c>
       <c r="H7" t="str">
-        <v>Neal Francis</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B8" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-27</v>
@@ -682,10 +682,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>4:12</v>
+        <v>5:01</v>
       </c>
       <c r="H8" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B9" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-27</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:59</v>
+        <v>4:12</v>
       </c>
       <c r="H9" t="str">
-        <v>Holly Humberstone</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B10" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-27</v>
@@ -758,10 +758,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>2:56</v>
+        <v>3:59</v>
       </c>
       <c r="H10" t="str">
-        <v>Cliff Richard</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B11" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-27</v>
@@ -796,10 +796,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:46</v>
+        <v>2:56</v>
       </c>
       <c r="H11" t="str">
-        <v>Jessie Ware</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Dean Lewis - I Am Getting Well</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B12" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-27</v>
@@ -834,10 +834,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>2:47</v>
+        <v>3:46</v>
       </c>
       <c r="H12" t="str">
-        <v>Dean Lewis</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Dean Lewis - I Am Getting Well - Dean Lewis</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B13" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-27</v>
@@ -872,10 +872,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>4:37</v>
+        <v>2:47</v>
       </c>
       <c r="H13" t="str">
-        <v>Bella White</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Dean Lewis - I Am Getting Well - Dean Lewis</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B14" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-27</v>
@@ -910,10 +910,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>4:06</v>
+        <v>4:37</v>
       </c>
       <c r="H14" t="str">
-        <v>Ryan Wright</v>
+        <v>Bella White</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B15" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-27</v>
@@ -948,10 +948,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:54</v>
+        <v>4:06</v>
       </c>
       <c r="H15" t="str">
-        <v>Dove Cameron</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B16" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-27</v>
@@ -986,10 +986,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:10</v>
+        <v>3:54</v>
       </c>
       <c r="H16" t="str">
-        <v>Parker McCollum</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B17" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-27</v>
@@ -1024,10 +1024,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:26</v>
+        <v>4:10</v>
       </c>
       <c r="H17" t="str">
-        <v>Matt Hansen</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-27</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>2:56</v>
+        <v>3:26</v>
       </c>
       <c r="H18" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-27</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>2:56</v>
       </c>
       <c r="H19" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B20" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-27</v>
@@ -1138,10 +1138,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>4:01</v>
+        <v>2:56</v>
       </c>
       <c r="H20" t="str">
-        <v>Tauren Wells</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-27</v>
@@ -1176,10 +1176,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:05</v>
+        <v>4:01</v>
       </c>
       <c r="H21" t="str">
-        <v>Maiah Manser</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B22" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-27</v>
@@ -1214,10 +1214,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>2:27</v>
+        <v>3:05</v>
       </c>
       <c r="H22" t="str">
-        <v>Taylor Austin Dye</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Chelsea Cutler - BAD (Official Video)</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B23" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-27</v>
@@ -1252,10 +1252,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>2:34</v>
+        <v>2:27</v>
       </c>
       <c r="H23" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B24" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-27</v>
@@ -1290,10 +1290,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:13</v>
+        <v>2:34</v>
       </c>
       <c r="H24" t="str">
-        <v>Ashley Kutcher</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B25" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
+        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-27</v>
@@ -1331,7 +1331,7 @@
         <v>3:13</v>
       </c>
       <c r="H25" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Ashley Kutcher</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B26" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
+        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-27</v>
@@ -1366,10 +1366,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:08</v>
+        <v>3:13</v>
       </c>
       <c r="H26" t="str">
-        <v>CAIN</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Harry Styles - Aperture (Official Audio)</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B27" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
+        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-27</v>
@@ -1404,10 +1404,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>5:14</v>
+        <v>3:08</v>
       </c>
       <c r="H27" t="str">
-        <v>Harry Styles</v>
+        <v>CAIN</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B28" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-27</v>
@@ -1442,10 +1442,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>2:59</v>
+        <v>5:14</v>
       </c>
       <c r="H28" t="str">
-        <v>Lana Lubany</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-27</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>4:21</v>
+        <v>2:59</v>
       </c>
       <c r="H29" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B30" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-27</v>
@@ -1518,10 +1518,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>4:09</v>
+        <v>4:21</v>
       </c>
       <c r="H30" t="str">
-        <v>Dermot Kennedy</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-27</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:34</v>
+        <v>4:09</v>
       </c>
       <c r="H31" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-27</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:10</v>
+        <v>2:34</v>
       </c>
       <c r="H32" t="str">
-        <v>Olivia Dean</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B33" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-27</v>
@@ -1632,10 +1632,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:21</v>
+        <v>3:10</v>
       </c>
       <c r="H33" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B34" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-27</v>
@@ -1670,10 +1670,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:06</v>
+        <v>3:21</v>
       </c>
       <c r="H34" t="str">
-        <v>The Avett Brothers</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B35" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-27</v>
@@ -1708,10 +1708,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:21</v>
+        <v>3:06</v>
       </c>
       <c r="H35" t="str">
-        <v>Jordana Bryant</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B36" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-27</v>
@@ -1746,10 +1746,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>7:21</v>
+        <v>3:21</v>
       </c>
       <c r="H36" t="str">
-        <v>Katy Perry</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B37" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-27</v>
@@ -1784,10 +1784,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:17</v>
+        <v>7:21</v>
       </c>
       <c r="H37" t="str">
-        <v>Lauren Watkins</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B38" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-27</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:45</v>
+        <v>3:17</v>
       </c>
       <c r="H38" t="str">
-        <v>Tones And I</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B39" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-27</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:57</v>
+        <v>3:45</v>
       </c>
       <c r="H39" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Tones And I</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B40" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-27</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:03</v>
+        <v>3:57</v>
       </c>
       <c r="H40" t="str">
-        <v>Charlie Puth</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B41" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-27</v>
@@ -1936,10 +1936,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>4:27</v>
+        <v>3:03</v>
       </c>
       <c r="H41" t="str">
-        <v>Chappell Roan</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B42" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-27</v>
@@ -1974,10 +1974,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>4:34</v>
+        <v>4:27</v>
       </c>
       <c r="H42" t="str">
-        <v>Armik</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B43" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-27</v>
@@ -2012,10 +2012,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:54</v>
+        <v>4:34</v>
       </c>
       <c r="H43" t="str">
-        <v>LØLØ</v>
+        <v>Armik</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B44" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-27</v>
@@ -2050,10 +2050,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:25</v>
+        <v>2:54</v>
       </c>
       <c r="H44" t="str">
-        <v>Tenille Townes</v>
+        <v>LØLØ</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B45" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-27</v>
@@ -2088,10 +2088,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>2:01</v>
+        <v>3:25</v>
       </c>
       <c r="H45" t="str">
-        <v>Alan Walker</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B46" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-27</v>
@@ -2126,10 +2126,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>2:25</v>
+        <v>2:01</v>
       </c>
       <c r="H46" t="str">
-        <v>Charli xcx</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B47" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-27</v>
@@ -2164,10 +2164,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>1:14</v>
+        <v>2:25</v>
       </c>
       <c r="H47" t="str">
-        <v>Labrinth</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B48" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-27</v>
@@ -2202,10 +2202,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>2:59</v>
+        <v>1:14</v>
       </c>
       <c r="H48" t="str">
-        <v>Charlie Puth</v>
+        <v>Labrinth</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B49" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-27</v>
@@ -2240,10 +2240,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>2:29</v>
+        <v>2:59</v>
       </c>
       <c r="H49" t="str">
-        <v>Girl Tones</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B50" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-27</v>
@@ -2278,10 +2278,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>2:34</v>
+        <v>2:29</v>
       </c>
       <c r="H50" t="str">
-        <v>Jagwar Twin</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B51" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-27</v>
@@ -2316,10 +2316,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:48</v>
+        <v>2:34</v>
       </c>
       <c r="H51" t="str">
-        <v>Caroline Jones</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B52" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-27</v>
@@ -2354,10 +2354,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:32</v>
+        <v>3:48</v>
       </c>
       <c r="H52" t="str">
-        <v>The Beaches</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B53" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-27</v>
@@ -2392,10 +2392,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:49</v>
+        <v>3:32</v>
       </c>
       <c r="H53" t="str">
-        <v>Dolly Parton</v>
+        <v>The Beaches</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B54" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-27</v>
@@ -2430,10 +2430,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>4:28</v>
+        <v>3:49</v>
       </c>
       <c r="H54" t="str">
-        <v>Madison Beer</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B55" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-27</v>
@@ -2468,10 +2468,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:37</v>
+        <v>4:28</v>
       </c>
       <c r="H55" t="str">
-        <v>Ty Myers</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B56" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-27</v>
@@ -2506,10 +2506,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:35</v>
+        <v>3:37</v>
       </c>
       <c r="H56" t="str">
-        <v>Megan Moroney</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B57" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-27</v>
@@ -2544,10 +2544,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>2:31</v>
+        <v>3:35</v>
       </c>
       <c r="H57" t="str">
-        <v>Julia Cole Music</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B58" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-27</v>
@@ -2582,10 +2582,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:21</v>
+        <v>2:31</v>
       </c>
       <c r="H58" t="str">
-        <v>Lily Allen</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B59" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-27</v>
@@ -2620,10 +2620,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>5:24</v>
+        <v>3:21</v>
       </c>
       <c r="H59" t="str">
-        <v>Nickless</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B60" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-27</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:11</v>
+        <v>5:24</v>
       </c>
       <c r="H60" t="str">
-        <v>Peach PRC</v>
+        <v>Nickless</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
+        <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B61" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
+        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-27</v>
@@ -2696,10 +2696,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>4:11</v>
+        <v>3:11</v>
       </c>
       <c r="H61" t="str">
-        <v>Ocean Alley</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
+        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
       </c>
       <c r="B62" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
+        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-27</v>
@@ -2734,10 +2734,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:31</v>
+        <v>4:11</v>
       </c>
       <c r="H62" t="str">
-        <v>OneRepublic</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B63" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
+        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-27</v>
@@ -2772,10 +2772,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>4:16</v>
+        <v>3:31</v>
       </c>
       <c r="H63" t="str">
-        <v>Ty Myers</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
       </c>
       <c r="B64" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
+        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-27</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>4:42</v>
+        <v>4:16</v>
       </c>
       <c r="H64" t="str">
-        <v>JavaJazzFest</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video)</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B65" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
+        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-27</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:47</v>
+        <v>4:42</v>
       </c>
       <c r="H65" t="str">
-        <v>Teo Glacier</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
+        <v>Teo Glacier - Don't Mind (Music Video)</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
+        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-27</v>
@@ -2886,10 +2886,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:59</v>
+        <v>2:47</v>
       </c>
       <c r="H66" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>Teo Glacier</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
+        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-27</v>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>4:09</v>
+        <v>3:59</v>
       </c>
       <c r="H67" t="str">
-        <v>Louie TheSinger</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>ella jane - When I Was Beautiful (Live)</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
+        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-27</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:24</v>
+        <v>4:09</v>
       </c>
       <c r="H68" t="str">
-        <v>ella jane</v>
+        <v>Louie TheSinger</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Johnny Orlando - Emilia (Official Video)</v>
+        <v>ella jane - When I Was Beautiful (Live)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
+        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-27</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:14</v>
+        <v>3:24</v>
       </c>
       <c r="H69" t="str">
-        <v>Johnny Orlando</v>
+        <v>ella jane</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
+        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video)</v>
+        <v>Johnny Orlando - Emilia (Official Video)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
+        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-27</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:32</v>
+        <v>3:14</v>
       </c>
       <c r="H70" t="str">
-        <v>Kungs</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
+        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
+        <v>Kungs, Theophilus London - Galaxy (official video)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
+        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-27</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:15</v>
+        <v>3:32</v>
       </c>
       <c r="H71" t="str">
-        <v>Billy Raffoul</v>
+        <v>Kungs</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
+        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
+        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-27</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:03</v>
+        <v>3:15</v>
       </c>
       <c r="H72" t="str">
-        <v>NathanEvanss</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Stephen Sanchez - Sweet Love</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
+        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-27</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:04</v>
+        <v>3:03</v>
       </c>
       <c r="H73" t="str">
-        <v>Stephen Sanchez</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video]</v>
+        <v>Stephen Sanchez - Sweet Love</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
+        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-27</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:33</v>
+        <v>3:04</v>
       </c>
       <c r="H74" t="str">
-        <v>Bruno Mars</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
+        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
+        <v>Bruno Mars - I Just Might [Official Music Video]</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
+        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-27</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:53</v>
+        <v>3:33</v>
       </c>
       <c r="H75" t="str">
-        <v>MAX</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
+        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
+        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-27</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>4:11</v>
+        <v>2:53</v>
       </c>
       <c r="H76" t="str">
-        <v>Jessie J</v>
+        <v>MAX</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
+        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-27</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>2:45</v>
+        <v>4:11</v>
       </c>
       <c r="H77" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Jessie J</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
+        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-27</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>4:00</v>
+        <v>2:45</v>
       </c>
       <c r="H78" t="str">
-        <v>Brandon Lake and Cody Johnson</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
+        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-27</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:27</v>
+        <v>4:00</v>
       </c>
       <c r="H79" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Brandon Lake and Cody Johnson</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
+        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-27</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:25</v>
+        <v>3:27</v>
       </c>
       <c r="H80" t="str">
-        <v>Olivia Dean</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
+        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-27</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:34</v>
+        <v>3:25</v>
       </c>
       <c r="H81" t="str">
-        <v>Demi Lovato</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
+        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-27</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:25</v>
+        <v>3:34</v>
       </c>
       <c r="H82" t="str">
-        <v>Joseph</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
+        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-27</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:26</v>
+        <v>2:25</v>
       </c>
       <c r="H83" t="str">
-        <v>Demi Lovato</v>
+        <v>Joseph</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
+        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-27</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>4:46</v>
+        <v>3:26</v>
       </c>
       <c r="H84" t="str">
-        <v>Keith Urban</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
+        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-27</v>
@@ -3608,7 +3608,7 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:24</v>
+        <v>4:46</v>
       </c>
       <c r="H85" t="str">
         <v>Keith Urban</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
+        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-27</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:52</v>
+        <v>3:24</v>
       </c>
       <c r="H86" t="str">
-        <v>Madonna</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
+        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-27</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:06</v>
+        <v>2:52</v>
       </c>
       <c r="H87" t="str">
-        <v>Estás Tonné</v>
+        <v>Madonna</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estás Tonné</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Anna Graves - Burn On (Official Music Video)</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
+        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-27</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:09</v>
+        <v>2:06</v>
       </c>
       <c r="H88" t="str">
-        <v>Anna Graves</v>
+        <v>Estás Tonné</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estás Tonné</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
+        <v>Anna Graves - Burn On (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
+        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-27</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>5:11</v>
+        <v>3:09</v>
       </c>
       <c r="H89" t="str">
-        <v>Ocean Alley</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
+        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
+        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-27</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:40</v>
+        <v>5:11</v>
       </c>
       <c r="H90" t="str">
-        <v>Zara Larsson</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
       </c>
       <c r="B91" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
+        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-27</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:49</v>
+        <v>3:40</v>
       </c>
       <c r="H91" t="str">
-        <v>Lauren Watkins</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B92" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
+        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-27</v>
@@ -3874,10 +3874,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:42</v>
+        <v>3:49</v>
       </c>
       <c r="H92" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B93" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
+        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-27</v>
@@ -3912,10 +3912,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>5:11</v>
+        <v>3:42</v>
       </c>
       <c r="H93" t="str">
-        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B94" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
+        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-27</v>
@@ -3950,10 +3950,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:57</v>
+        <v>5:11</v>
       </c>
       <c r="H94" t="str">
-        <v>Lainey Wilson</v>
+        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video)</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
       </c>
       <c r="B95" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
+        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-27</v>
@@ -3988,10 +3988,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:29</v>
+        <v>3:57</v>
       </c>
       <c r="H95" t="str">
-        <v>Grace Enger</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video)</v>
+        <v>Grace Enger - All My Songs (Official Lyric Video)</v>
       </c>
       <c r="B96" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
+        <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-27</v>
@@ -4026,10 +4026,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:10</v>
+        <v>3:29</v>
       </c>
       <c r="H96" t="str">
-        <v>Alan Walker and 2 more</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
+        <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Emilia Tarrant - Break Up With Myself</v>
+        <v>Alan Walker - Broken Strings (Official Music Video)</v>
       </c>
       <c r="B97" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
+        <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-27</v>
@@ -4064,10 +4064,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:04</v>
+        <v>3:10</v>
       </c>
       <c r="H97" t="str">
-        <v>Emilia Tarrant</v>
+        <v>Alan Walker and 2 more</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
+        <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026)</v>
+        <v>Emilia Tarrant - Break Up With Myself</v>
       </c>
       <c r="B98" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
+        <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-27</v>
@@ -4102,10 +4102,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:09</v>
+        <v>4:04</v>
       </c>
       <c r="H98" t="str">
-        <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Emilia Tarrant</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer)</v>
+        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026)</v>
       </c>
       <c r="B99" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
+        <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-27</v>
@@ -4140,10 +4140,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>2:27</v>
+        <v>3:09</v>
       </c>
       <c r="H99" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
+        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Maggie Lindemann - fate</v>
+        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer)</v>
       </c>
       <c r="B100" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
+        <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-27</v>
@@ -4178,10 +4178,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>2:12</v>
+        <v>2:27</v>
       </c>
       <c r="H100" t="str">
-        <v>Maggie Lindemann</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Maggie Lindemann - fate - Maggie Lindemann</v>
+        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023)</v>
+        <v>Maggie Lindemann - fate</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=wo9yPPCh75Q</v>
+        <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-27</v>
@@ -4216,10 +4216,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>4:44</v>
+        <v>2:12</v>
       </c>
       <c r="H101" t="str">
-        <v>Cliff Richard</v>
+        <v>Maggie Lindemann</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023) - Cliff Richard</v>
+        <v>Maggie Lindemann - fate - Maggie Lindemann</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>3 hours ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>3 hours ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -477,7 +477,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B3" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:20</v>
@@ -667,7 +667,7 @@
         <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B8" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G8" t="str">
         <v>5:01</v>
@@ -702,10 +702,10 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B9" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>4:12</v>
@@ -735,7 +735,7 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B39" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>3:45</v>
@@ -2643,7 +2643,7 @@
         <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B60" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>5:24</v>
@@ -3821,7 +3821,7 @@
         <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v>3:40</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>4 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>4 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -477,7 +477,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B3" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:20</v>
@@ -591,7 +591,7 @@
         <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B6" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:24</v>
@@ -629,7 +629,7 @@
         <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G7" t="str">
         <v>5:52</v>
@@ -702,7 +702,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B9" t="str">
         <v>4 days ago</v>
@@ -735,7 +735,7 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="10">
@@ -1085,7 +1085,7 @@
         <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>2:56</v>
@@ -1465,7 +1465,7 @@
         <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>2:59</v>
@@ -1959,7 +1959,7 @@
         <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B42" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>4:27</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -477,7 +477,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B3" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:20</v>
@@ -553,7 +553,7 @@
         <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G5" t="str">
         <v>4:01</v>
@@ -702,7 +702,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B9" t="str">
         <v>4 days ago</v>
@@ -735,7 +735,7 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="10">
@@ -1997,7 +1997,7 @@
         <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B43" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>4:34</v>
@@ -2605,7 +2605,7 @@
         <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B59" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G59" t="str">
         <v>3:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -477,7 +477,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B3" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:20</v>
@@ -702,7 +702,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B9" t="str">
         <v>4 days ago</v>
@@ -735,7 +735,7 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="10">
@@ -1541,7 +1541,7 @@
         <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>4:09</v>
@@ -1807,7 +1807,7 @@
         <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B38" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>3:17</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -477,7 +477,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B3" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:20</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -477,7 +477,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:20</v>
@@ -702,7 +702,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B9" t="str">
         <v>4 days ago</v>
@@ -735,7 +735,7 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="10">

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -1921,7 +1921,7 @@
         <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>3:03</v>
@@ -2795,7 +2795,7 @@
         <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
       </c>
       <c r="B64" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>4:16</v>
@@ -3783,7 +3783,7 @@
         <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v>5:11</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -1769,7 +1769,7 @@
         <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B37" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>7:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,19 +439,19 @@
         <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>11 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>11 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -483,7 +483,7 @@
         <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -515,19 +515,19 @@
         <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:34</v>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1427,19 +1427,19 @@
         <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B28" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>5:14</v>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1883,19 +1883,19 @@
         <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B40" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>3:57</v>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2567,19 +2567,19 @@
         <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G58" t="str">
         <v>2:31</v>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2757,19 +2757,19 @@
         <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B63" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G63" t="str">
         <v>3:31</v>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -702,7 +702,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B9" t="str">
         <v>4 days ago</v>
@@ -735,7 +735,7 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="10">
@@ -1579,7 +1579,7 @@
         <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>2:34</v>
@@ -2719,7 +2719,7 @@
         <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
       </c>
       <c r="B62" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>4:11</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -702,7 +702,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B9" t="str">
         <v>4 days ago</v>
@@ -735,7 +735,7 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="10">
@@ -895,7 +895,7 @@
         <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B14" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>4:37</v>
@@ -933,7 +933,7 @@
         <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>4:06</v>
@@ -971,7 +971,7 @@
         <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B16" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>3:54</v>
@@ -1009,7 +1009,7 @@
         <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>4:10</v>
@@ -1047,7 +1047,7 @@
         <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:26</v>
@@ -1123,7 +1123,7 @@
         <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>2:56</v>
@@ -1161,7 +1161,7 @@
         <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>4:01</v>
@@ -1199,7 +1199,7 @@
         <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>3:05</v>
@@ -1237,7 +1237,7 @@
         <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>2:27</v>
@@ -1275,7 +1275,7 @@
         <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>2:34</v>
@@ -1313,7 +1313,7 @@
         <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>3:13</v>
@@ -1351,7 +1351,7 @@
         <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B26" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>3:13</v>
@@ -1389,7 +1389,7 @@
         <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>3:08</v>
@@ -1693,7 +1693,7 @@
         <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>3:06</v>
@@ -1731,7 +1731,7 @@
         <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>3:21</v>
@@ -2149,7 +2149,7 @@
         <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B47" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>2:25</v>
@@ -2187,7 +2187,7 @@
         <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B48" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>1:14</v>
@@ -2225,7 +2225,7 @@
         <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B49" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>2:59</v>
@@ -2263,7 +2263,7 @@
         <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B50" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>2:29</v>
@@ -2301,7 +2301,7 @@
         <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B51" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>2:34</v>
@@ -2339,7 +2339,7 @@
         <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>3:48</v>
@@ -2377,7 +2377,7 @@
         <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B53" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G53" t="str">
         <v>3:32</v>
@@ -2415,7 +2415,7 @@
         <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B54" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G54" t="str">
         <v>3:49</v>
@@ -2453,7 +2453,7 @@
         <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>4:28</v>
@@ -2491,7 +2491,7 @@
         <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G56" t="str">
         <v>3:37</v>
@@ -2529,7 +2529,7 @@
         <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>3:35</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -702,7 +702,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B9" t="str">
         <v>4 days ago</v>
@@ -735,7 +735,7 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="10">
@@ -2681,7 +2681,7 @@
         <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B61" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G61" t="str">
         <v>3:11</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -702,7 +702,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B9" t="str">
         <v>4 days ago</v>
@@ -735,7 +735,7 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="10">

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -819,7 +819,7 @@
         <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>3:46</v>
@@ -857,7 +857,7 @@
         <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B13" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>2:47</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -781,7 +781,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B11" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>2:56</v>
@@ -2833,7 +2833,7 @@
         <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B65" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
         <v>4:42</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -702,7 +702,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B9" t="str">
         <v>4 days ago</v>
@@ -735,7 +735,7 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="10">
@@ -743,7 +743,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:59</v>
@@ -2111,7 +2111,7 @@
         <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>2:01</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -702,7 +702,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B9" t="str">
         <v>4 days ago</v>
@@ -735,7 +735,7 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="10">
@@ -1503,7 +1503,7 @@
         <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>4:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -1655,7 +1655,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B34" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>3:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-28</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v>3:01</v>
+        <v>4:27</v>
       </c>
       <c r="H2" t="str">
-        <v>Timebelle Official</v>
+        <v>We Three</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B3" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-28</v>
@@ -492,10 +492,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
-        <v>3:20</v>
+        <v>3:01</v>
       </c>
       <c r="H3" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B4" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-28</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
-        <v>3:34</v>
+        <v>3:20</v>
       </c>
       <c r="H4" t="str">
-        <v>Clinton Kane</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B5" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-28</v>
@@ -568,10 +568,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G5" t="str">
-        <v>4:01</v>
+        <v>3:34</v>
       </c>
       <c r="H5" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-28</v>
@@ -606,10 +606,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:24</v>
+        <v>4:01</v>
       </c>
       <c r="H6" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B7" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-28</v>
@@ -644,10 +644,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>5:52</v>
+        <v>3:24</v>
       </c>
       <c r="H7" t="str">
-        <v>Harry Styles</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B8" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-28</v>
@@ -682,10 +682,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>5:01</v>
+        <v>5:52</v>
       </c>
       <c r="H8" t="str">
-        <v>Neal Francis</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B9" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-28</v>
@@ -720,10 +720,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>4:12</v>
+        <v>5:01</v>
       </c>
       <c r="H9" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B10" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-28</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:59</v>
+        <v>4:12</v>
       </c>
       <c r="H10" t="str">
-        <v>Holly Humberstone</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B11" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-28</v>
@@ -796,10 +796,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>2:56</v>
+        <v>3:59</v>
       </c>
       <c r="H11" t="str">
-        <v>Cliff Richard</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B12" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-28</v>
@@ -834,10 +834,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:46</v>
+        <v>2:56</v>
       </c>
       <c r="H12" t="str">
-        <v>Jessie Ware</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Dean Lewis - I Am Getting Well</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B13" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-28</v>
@@ -872,10 +872,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>2:47</v>
+        <v>3:46</v>
       </c>
       <c r="H13" t="str">
-        <v>Dean Lewis</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Dean Lewis - I Am Getting Well - Dean Lewis</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B14" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-28</v>
@@ -910,10 +910,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>4:37</v>
+        <v>2:47</v>
       </c>
       <c r="H14" t="str">
-        <v>Bella White</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Dean Lewis - I Am Getting Well - Dean Lewis</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B15" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-28</v>
@@ -948,10 +948,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>4:06</v>
+        <v>4:37</v>
       </c>
       <c r="H15" t="str">
-        <v>Ryan Wright</v>
+        <v>Bella White</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B16" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-28</v>
@@ -986,10 +986,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:54</v>
+        <v>4:06</v>
       </c>
       <c r="H16" t="str">
-        <v>Dove Cameron</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B17" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-28</v>
@@ -1024,10 +1024,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:10</v>
+        <v>3:54</v>
       </c>
       <c r="H17" t="str">
-        <v>Parker McCollum</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B18" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-28</v>
@@ -1062,10 +1062,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:26</v>
+        <v>4:10</v>
       </c>
       <c r="H18" t="str">
-        <v>Matt Hansen</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-28</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:56</v>
+        <v>3:26</v>
       </c>
       <c r="H19" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-28</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>2:56</v>
       </c>
       <c r="H20" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B21" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-28</v>
@@ -1176,10 +1176,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>4:01</v>
+        <v>2:56</v>
       </c>
       <c r="H21" t="str">
-        <v>Tauren Wells</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-28</v>
@@ -1214,10 +1214,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:05</v>
+        <v>4:01</v>
       </c>
       <c r="H22" t="str">
-        <v>Maiah Manser</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B23" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-28</v>
@@ -1252,10 +1252,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>2:27</v>
+        <v>3:05</v>
       </c>
       <c r="H23" t="str">
-        <v>Taylor Austin Dye</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Chelsea Cutler - BAD (Official Video)</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-28</v>
@@ -1290,10 +1290,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>2:34</v>
+        <v>2:27</v>
       </c>
       <c r="H24" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B25" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-28</v>
@@ -1328,10 +1328,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:13</v>
+        <v>2:34</v>
       </c>
       <c r="H25" t="str">
-        <v>Ashley Kutcher</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B26" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
+        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-28</v>
@@ -1369,7 +1369,7 @@
         <v>3:13</v>
       </c>
       <c r="H26" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Ashley Kutcher</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B27" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
+        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-28</v>
@@ -1404,10 +1404,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:08</v>
+        <v>3:13</v>
       </c>
       <c r="H27" t="str">
-        <v>CAIN</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Harry Styles - Aperture (Official Audio)</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B28" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
+        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-28</v>
@@ -1442,10 +1442,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>5:14</v>
+        <v>3:08</v>
       </c>
       <c r="H28" t="str">
-        <v>Harry Styles</v>
+        <v>CAIN</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B29" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-28</v>
@@ -1480,10 +1480,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:59</v>
+        <v>5:14</v>
       </c>
       <c r="H29" t="str">
-        <v>Lana Lubany</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-28</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>4:21</v>
+        <v>2:59</v>
       </c>
       <c r="H30" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-28</v>
@@ -1556,10 +1556,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>4:09</v>
+        <v>4:21</v>
       </c>
       <c r="H31" t="str">
-        <v>Dermot Kennedy</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-28</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:34</v>
+        <v>4:09</v>
       </c>
       <c r="H32" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-28</v>
@@ -1632,10 +1632,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:10</v>
+        <v>2:34</v>
       </c>
       <c r="H33" t="str">
-        <v>Olivia Dean</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B34" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-28</v>
@@ -1670,10 +1670,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:21</v>
+        <v>3:10</v>
       </c>
       <c r="H34" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B35" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-28</v>
@@ -1708,10 +1708,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:06</v>
+        <v>3:21</v>
       </c>
       <c r="H35" t="str">
-        <v>The Avett Brothers</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B36" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-28</v>
@@ -1746,10 +1746,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:21</v>
+        <v>3:06</v>
       </c>
       <c r="H36" t="str">
-        <v>Jordana Bryant</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B37" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-28</v>
@@ -1784,10 +1784,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>7:21</v>
+        <v>3:21</v>
       </c>
       <c r="H37" t="str">
-        <v>Katy Perry</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B38" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-28</v>
@@ -1822,10 +1822,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:17</v>
+        <v>7:21</v>
       </c>
       <c r="H38" t="str">
-        <v>Lauren Watkins</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B39" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-28</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:45</v>
+        <v>3:17</v>
       </c>
       <c r="H39" t="str">
-        <v>Tones And I</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B40" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-28</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:57</v>
+        <v>3:45</v>
       </c>
       <c r="H40" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Tones And I</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B41" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-28</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:03</v>
+        <v>3:57</v>
       </c>
       <c r="H41" t="str">
-        <v>Charlie Puth</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B42" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-28</v>
@@ -1974,10 +1974,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>4:27</v>
+        <v>3:03</v>
       </c>
       <c r="H42" t="str">
-        <v>Chappell Roan</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B43" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-28</v>
@@ -2012,10 +2012,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>4:34</v>
+        <v>4:27</v>
       </c>
       <c r="H43" t="str">
-        <v>Armik</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B44" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-28</v>
@@ -2050,10 +2050,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:54</v>
+        <v>4:34</v>
       </c>
       <c r="H44" t="str">
-        <v>LØLØ</v>
+        <v>Armik</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-28</v>
@@ -2088,10 +2088,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:25</v>
+        <v>2:54</v>
       </c>
       <c r="H45" t="str">
-        <v>Tenille Townes</v>
+        <v>LØLØ</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B46" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-28</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>2:01</v>
+        <v>3:25</v>
       </c>
       <c r="H46" t="str">
-        <v>Alan Walker</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-28</v>
@@ -2164,10 +2164,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>2:25</v>
+        <v>2:01</v>
       </c>
       <c r="H47" t="str">
-        <v>Charli xcx</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B48" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-28</v>
@@ -2202,10 +2202,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>1:14</v>
+        <v>2:25</v>
       </c>
       <c r="H48" t="str">
-        <v>Labrinth</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B49" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-28</v>
@@ -2240,10 +2240,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>2:59</v>
+        <v>1:14</v>
       </c>
       <c r="H49" t="str">
-        <v>Charlie Puth</v>
+        <v>Labrinth</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B50" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-28</v>
@@ -2278,10 +2278,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>2:29</v>
+        <v>2:59</v>
       </c>
       <c r="H50" t="str">
-        <v>Girl Tones</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B51" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-28</v>
@@ -2316,10 +2316,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:34</v>
+        <v>2:29</v>
       </c>
       <c r="H51" t="str">
-        <v>Jagwar Twin</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B52" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-28</v>
@@ -2354,10 +2354,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:48</v>
+        <v>2:34</v>
       </c>
       <c r="H52" t="str">
-        <v>Caroline Jones</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B53" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-28</v>
@@ -2392,10 +2392,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:32</v>
+        <v>3:48</v>
       </c>
       <c r="H53" t="str">
-        <v>The Beaches</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B54" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-28</v>
@@ -2430,10 +2430,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:49</v>
+        <v>3:32</v>
       </c>
       <c r="H54" t="str">
-        <v>Dolly Parton</v>
+        <v>The Beaches</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B55" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-28</v>
@@ -2468,10 +2468,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>4:28</v>
+        <v>3:49</v>
       </c>
       <c r="H55" t="str">
-        <v>Madison Beer</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B56" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-28</v>
@@ -2506,10 +2506,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:37</v>
+        <v>4:28</v>
       </c>
       <c r="H56" t="str">
-        <v>Ty Myers</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B57" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-28</v>
@@ -2544,10 +2544,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:35</v>
+        <v>3:37</v>
       </c>
       <c r="H57" t="str">
-        <v>Megan Moroney</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B58" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-28</v>
@@ -2582,10 +2582,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>2:31</v>
+        <v>3:35</v>
       </c>
       <c r="H58" t="str">
-        <v>Julia Cole Music</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-28</v>
@@ -2620,10 +2620,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:21</v>
+        <v>2:31</v>
       </c>
       <c r="H59" t="str">
-        <v>Lily Allen</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B60" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-28</v>
@@ -2658,10 +2658,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>5:24</v>
+        <v>3:21</v>
       </c>
       <c r="H60" t="str">
-        <v>Nickless</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B61" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-28</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:11</v>
+        <v>5:24</v>
       </c>
       <c r="H61" t="str">
-        <v>Peach PRC</v>
+        <v>Nickless</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
+        <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B62" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
+        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-28</v>
@@ -2734,10 +2734,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>4:11</v>
+        <v>3:11</v>
       </c>
       <c r="H62" t="str">
-        <v>Ocean Alley</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
+        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
       </c>
       <c r="B63" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
+        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-28</v>
@@ -2772,10 +2772,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:31</v>
+        <v>4:11</v>
       </c>
       <c r="H63" t="str">
-        <v>OneRepublic</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B64" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
+        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-28</v>
@@ -2810,10 +2810,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>4:16</v>
+        <v>3:31</v>
       </c>
       <c r="H64" t="str">
-        <v>Ty Myers</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
       </c>
       <c r="B65" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
+        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-28</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>4:42</v>
+        <v>4:16</v>
       </c>
       <c r="H65" t="str">
-        <v>JavaJazzFest</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video)</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
+        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-28</v>
@@ -2886,10 +2886,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>2:47</v>
+        <v>4:42</v>
       </c>
       <c r="H66" t="str">
-        <v>Teo Glacier</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
+        <v>Teo Glacier - Don't Mind (Music Video)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
+        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-28</v>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:59</v>
+        <v>2:47</v>
       </c>
       <c r="H67" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>Teo Glacier</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
+        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-28</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:09</v>
+        <v>3:59</v>
       </c>
       <c r="H68" t="str">
-        <v>Louie TheSinger</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>ella jane - When I Was Beautiful (Live)</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
+        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-28</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:24</v>
+        <v>4:09</v>
       </c>
       <c r="H69" t="str">
-        <v>ella jane</v>
+        <v>Louie TheSinger</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Johnny Orlando - Emilia (Official Video)</v>
+        <v>ella jane - When I Was Beautiful (Live)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
+        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-28</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:14</v>
+        <v>3:24</v>
       </c>
       <c r="H70" t="str">
-        <v>Johnny Orlando</v>
+        <v>ella jane</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
+        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video)</v>
+        <v>Johnny Orlando - Emilia (Official Video)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
+        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-28</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:32</v>
+        <v>3:14</v>
       </c>
       <c r="H71" t="str">
-        <v>Kungs</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
+        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
+        <v>Kungs, Theophilus London - Galaxy (official video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
+        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-28</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:15</v>
+        <v>3:32</v>
       </c>
       <c r="H72" t="str">
-        <v>Billy Raffoul</v>
+        <v>Kungs</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
+        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
+        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-28</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:03</v>
+        <v>3:15</v>
       </c>
       <c r="H73" t="str">
-        <v>NathanEvanss</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Stephen Sanchez - Sweet Love</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
+        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-28</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:04</v>
+        <v>3:03</v>
       </c>
       <c r="H74" t="str">
-        <v>Stephen Sanchez</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video]</v>
+        <v>Stephen Sanchez - Sweet Love</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
+        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-28</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:33</v>
+        <v>3:04</v>
       </c>
       <c r="H75" t="str">
-        <v>Bruno Mars</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
+        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
+        <v>Bruno Mars - I Just Might [Official Music Video]</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
+        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-28</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:53</v>
+        <v>3:33</v>
       </c>
       <c r="H76" t="str">
-        <v>MAX</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
+        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
+        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-28</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>4:11</v>
+        <v>2:53</v>
       </c>
       <c r="H77" t="str">
-        <v>Jessie J</v>
+        <v>MAX</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
+        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-28</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>2:45</v>
+        <v>4:11</v>
       </c>
       <c r="H78" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Jessie J</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
+        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-28</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>4:00</v>
+        <v>2:45</v>
       </c>
       <c r="H79" t="str">
-        <v>Brandon Lake and Cody Johnson</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
+        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-28</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:27</v>
+        <v>4:00</v>
       </c>
       <c r="H80" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Brandon Lake and Cody Johnson</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
+        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-28</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:25</v>
+        <v>3:27</v>
       </c>
       <c r="H81" t="str">
-        <v>Olivia Dean</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
+        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-28</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:34</v>
+        <v>3:25</v>
       </c>
       <c r="H82" t="str">
-        <v>Demi Lovato</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
+        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-28</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:25</v>
+        <v>3:34</v>
       </c>
       <c r="H83" t="str">
-        <v>Joseph</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
+        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-28</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:26</v>
+        <v>2:25</v>
       </c>
       <c r="H84" t="str">
-        <v>Demi Lovato</v>
+        <v>Joseph</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
+        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-28</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>4:46</v>
+        <v>3:26</v>
       </c>
       <c r="H85" t="str">
-        <v>Keith Urban</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
+        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-28</v>
@@ -3646,7 +3646,7 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:24</v>
+        <v>4:46</v>
       </c>
       <c r="H86" t="str">
         <v>Keith Urban</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
+        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-28</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:52</v>
+        <v>3:24</v>
       </c>
       <c r="H87" t="str">
-        <v>Madonna</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
+        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-28</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:06</v>
+        <v>2:52</v>
       </c>
       <c r="H88" t="str">
-        <v>Estás Tonné</v>
+        <v>Madonna</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estás Tonné</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Anna Graves - Burn On (Official Music Video)</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
+        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-28</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:09</v>
+        <v>2:06</v>
       </c>
       <c r="H89" t="str">
-        <v>Anna Graves</v>
+        <v>Estás Tonné</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estás Tonné</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
+        <v>Anna Graves - Burn On (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
+        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-28</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>5:11</v>
+        <v>3:09</v>
       </c>
       <c r="H90" t="str">
-        <v>Ocean Alley</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
+        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
       </c>
       <c r="B91" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
+        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-28</v>
@@ -3836,10 +3836,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:40</v>
+        <v>5:11</v>
       </c>
       <c r="H91" t="str">
-        <v>Zara Larsson</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
       </c>
       <c r="B92" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
+        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-28</v>
@@ -3874,10 +3874,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:49</v>
+        <v>3:40</v>
       </c>
       <c r="H92" t="str">
-        <v>Lauren Watkins</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B93" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
+        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-28</v>
@@ -3912,10 +3912,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:42</v>
+        <v>3:49</v>
       </c>
       <c r="H93" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B94" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
+        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-28</v>
@@ -3950,10 +3950,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>5:11</v>
+        <v>3:42</v>
       </c>
       <c r="H94" t="str">
-        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B95" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
+        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-28</v>
@@ -3988,10 +3988,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:57</v>
+        <v>5:11</v>
       </c>
       <c r="H95" t="str">
-        <v>Lainey Wilson</v>
+        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video)</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
       </c>
       <c r="B96" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
+        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-28</v>
@@ -4026,10 +4026,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:29</v>
+        <v>3:57</v>
       </c>
       <c r="H96" t="str">
-        <v>Grace Enger</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video)</v>
+        <v>Grace Enger - All My Songs (Official Lyric Video)</v>
       </c>
       <c r="B97" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
+        <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-28</v>
@@ -4064,10 +4064,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:10</v>
+        <v>3:29</v>
       </c>
       <c r="H97" t="str">
-        <v>Alan Walker and 2 more</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
+        <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Emilia Tarrant - Break Up With Myself</v>
+        <v>Alan Walker - Broken Strings (Official Music Video)</v>
       </c>
       <c r="B98" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
+        <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-28</v>
@@ -4102,10 +4102,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>4:04</v>
+        <v>3:10</v>
       </c>
       <c r="H98" t="str">
-        <v>Emilia Tarrant</v>
+        <v>Alan Walker and 2 more</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
+        <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026)</v>
+        <v>Emilia Tarrant - Break Up With Myself</v>
       </c>
       <c r="B99" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
+        <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-28</v>
@@ -4140,10 +4140,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:09</v>
+        <v>4:04</v>
       </c>
       <c r="H99" t="str">
-        <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Emilia Tarrant</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer)</v>
+        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026)</v>
       </c>
       <c r="B100" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
+        <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-28</v>
@@ -4178,10 +4178,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>2:27</v>
+        <v>3:09</v>
       </c>
       <c r="H100" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
+        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Maggie Lindemann - fate</v>
+        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer)</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
+        <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-28</v>
@@ -4216,10 +4216,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>2:12</v>
+        <v>2:27</v>
       </c>
       <c r="H101" t="str">
-        <v>Maggie Lindemann</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Maggie Lindemann - fate - Maggie Lindemann</v>
+        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:27</v>
@@ -2111,7 +2111,7 @@
         <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B46" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>3:25</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:27</v>
@@ -2073,7 +2073,7 @@
         <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>2:54</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:27</v>
@@ -705,7 +705,7 @@
         <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B9" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>5:01</v>
@@ -740,10 +740,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B10" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>4:12</v>
@@ -773,7 +773,7 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="11">
@@ -1883,7 +1883,7 @@
         <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B40" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>3:45</v>
@@ -2681,7 +2681,7 @@
         <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B61" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G61" t="str">
         <v>5:24</v>
@@ -3745,7 +3745,7 @@
         <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G89" t="str">
         <v>2:06</v>
@@ -3783,7 +3783,7 @@
         <v>Anna Graves - Burn On (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v>3:09</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:27</v>
@@ -629,7 +629,7 @@
         <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B7" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:24</v>
@@ -667,7 +667,7 @@
         <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G8" t="str">
         <v>5:52</v>
@@ -740,7 +740,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B10" t="str">
         <v>5 days ago</v>
@@ -773,7 +773,7 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="11">
@@ -892,13 +892,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Dean Lewis - I Am Getting Well</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B14" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-28</v>
@@ -910,10 +910,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:47</v>
+        <v>4:37</v>
       </c>
       <c r="H14" t="str">
-        <v>Dean Lewis</v>
+        <v>Bella White</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Dean Lewis - I Am Getting Well - Dean Lewis</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B15" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-28</v>
@@ -948,10 +948,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>4:37</v>
+        <v>4:06</v>
       </c>
       <c r="H15" t="str">
-        <v>Bella White</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B16" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-28</v>
@@ -986,10 +986,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:06</v>
+        <v>3:54</v>
       </c>
       <c r="H16" t="str">
-        <v>Ryan Wright</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B17" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-28</v>
@@ -1024,10 +1024,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:54</v>
+        <v>4:10</v>
       </c>
       <c r="H17" t="str">
-        <v>Dove Cameron</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B18" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-28</v>
@@ -1062,10 +1062,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>4:10</v>
+        <v>3:26</v>
       </c>
       <c r="H18" t="str">
-        <v>Parker McCollum</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-28</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:26</v>
+        <v>2:56</v>
       </c>
       <c r="H19" t="str">
-        <v>Matt Hansen</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-28</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>2:56</v>
       </c>
       <c r="H20" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-28</v>
@@ -1176,10 +1176,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>2:56</v>
+        <v>4:01</v>
       </c>
       <c r="H21" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B22" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-28</v>
@@ -1214,10 +1214,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>4:01</v>
+        <v>3:05</v>
       </c>
       <c r="H22" t="str">
-        <v>Tauren Wells</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B23" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-28</v>
@@ -1252,10 +1252,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:05</v>
+        <v>2:27</v>
       </c>
       <c r="H23" t="str">
-        <v>Maiah Manser</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B24" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-28</v>
@@ -1290,10 +1290,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>2:27</v>
+        <v>2:34</v>
       </c>
       <c r="H24" t="str">
-        <v>Taylor Austin Dye</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Chelsea Cutler - BAD (Official Video)</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B25" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
+        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-28</v>
@@ -1328,10 +1328,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:34</v>
+        <v>3:13</v>
       </c>
       <c r="H25" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Ashley Kutcher</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B26" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
+        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-28</v>
@@ -1369,7 +1369,7 @@
         <v>3:13</v>
       </c>
       <c r="H26" t="str">
-        <v>Ashley Kutcher</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B27" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
+        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-28</v>
@@ -1404,10 +1404,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:13</v>
+        <v>3:08</v>
       </c>
       <c r="H27" t="str">
-        <v>Louis Tomlinson</v>
+        <v>CAIN</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
+        <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B28" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
+        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-28</v>
@@ -1442,10 +1442,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:08</v>
+        <v>5:14</v>
       </c>
       <c r="H28" t="str">
-        <v>CAIN</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
+        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Harry Styles - Aperture (Official Audio)</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-28</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>5:14</v>
+        <v>2:59</v>
       </c>
       <c r="H29" t="str">
-        <v>Harry Styles</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-28</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:59</v>
+        <v>4:21</v>
       </c>
       <c r="H30" t="str">
-        <v>Lana Lubany</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B31" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-28</v>
@@ -1556,10 +1556,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>4:21</v>
+        <v>4:09</v>
       </c>
       <c r="H31" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-28</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>4:09</v>
+        <v>2:34</v>
       </c>
       <c r="H32" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B33" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-28</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>2:34</v>
+        <v>3:10</v>
       </c>
       <c r="H33" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B34" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-28</v>
@@ -1670,10 +1670,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:10</v>
+        <v>3:21</v>
       </c>
       <c r="H34" t="str">
-        <v>Olivia Dean</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B35" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-28</v>
@@ -1708,10 +1708,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:21</v>
+        <v>3:06</v>
       </c>
       <c r="H35" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B36" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-28</v>
@@ -1746,10 +1746,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:06</v>
+        <v>3:21</v>
       </c>
       <c r="H36" t="str">
-        <v>The Avett Brothers</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B37" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-28</v>
@@ -1784,10 +1784,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:21</v>
+        <v>7:21</v>
       </c>
       <c r="H37" t="str">
-        <v>Jordana Bryant</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B38" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-28</v>
@@ -1822,10 +1822,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>7:21</v>
+        <v>3:17</v>
       </c>
       <c r="H38" t="str">
-        <v>Katy Perry</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B39" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-28</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:17</v>
+        <v>3:45</v>
       </c>
       <c r="H39" t="str">
-        <v>Lauren Watkins</v>
+        <v>Tones And I</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B40" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-28</v>
@@ -1898,10 +1898,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:45</v>
+        <v>3:57</v>
       </c>
       <c r="H40" t="str">
-        <v>Tones And I</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-28</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:57</v>
+        <v>3:03</v>
       </c>
       <c r="H41" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B42" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-28</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:03</v>
+        <v>4:27</v>
       </c>
       <c r="H42" t="str">
-        <v>Charlie Puth</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B43" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-28</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>4:27</v>
+        <v>4:34</v>
       </c>
       <c r="H43" t="str">
-        <v>Chappell Roan</v>
+        <v>Armik</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-28</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>4:34</v>
+        <v>2:54</v>
       </c>
       <c r="H44" t="str">
-        <v>Armik</v>
+        <v>LØLØ</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B45" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-28</v>
@@ -2088,10 +2088,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>2:54</v>
+        <v>3:25</v>
       </c>
       <c r="H45" t="str">
-        <v>LØLØ</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B46" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-28</v>
@@ -2126,10 +2126,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:25</v>
+        <v>2:01</v>
       </c>
       <c r="H46" t="str">
-        <v>Tenille Townes</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B47" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-28</v>
@@ -2164,10 +2164,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>2:01</v>
+        <v>2:25</v>
       </c>
       <c r="H47" t="str">
-        <v>Alan Walker</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B48" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-28</v>
@@ -2202,10 +2202,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>2:25</v>
+        <v>1:14</v>
       </c>
       <c r="H48" t="str">
-        <v>Charli xcx</v>
+        <v>Labrinth</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B49" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-28</v>
@@ -2240,10 +2240,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>1:14</v>
+        <v>2:59</v>
       </c>
       <c r="H49" t="str">
-        <v>Labrinth</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B50" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-28</v>
@@ -2278,10 +2278,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>2:59</v>
+        <v>2:29</v>
       </c>
       <c r="H50" t="str">
-        <v>Charlie Puth</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B51" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-28</v>
@@ -2316,10 +2316,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:29</v>
+        <v>2:34</v>
       </c>
       <c r="H51" t="str">
-        <v>Girl Tones</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B52" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-28</v>
@@ -2354,10 +2354,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>2:34</v>
+        <v>3:48</v>
       </c>
       <c r="H52" t="str">
-        <v>Jagwar Twin</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B53" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-28</v>
@@ -2392,10 +2392,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:48</v>
+        <v>3:32</v>
       </c>
       <c r="H53" t="str">
-        <v>Caroline Jones</v>
+        <v>The Beaches</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B54" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-28</v>
@@ -2430,10 +2430,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:32</v>
+        <v>3:49</v>
       </c>
       <c r="H54" t="str">
-        <v>The Beaches</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B55" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-28</v>
@@ -2468,10 +2468,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:49</v>
+        <v>4:28</v>
       </c>
       <c r="H55" t="str">
-        <v>Dolly Parton</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B56" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-28</v>
@@ -2506,10 +2506,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>4:28</v>
+        <v>3:37</v>
       </c>
       <c r="H56" t="str">
-        <v>Madison Beer</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B57" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-28</v>
@@ -2544,10 +2544,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:37</v>
+        <v>3:35</v>
       </c>
       <c r="H57" t="str">
-        <v>Ty Myers</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B58" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-28</v>
@@ -2582,10 +2582,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:35</v>
+        <v>2:31</v>
       </c>
       <c r="H58" t="str">
-        <v>Megan Moroney</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B59" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-28</v>
@@ -2620,10 +2620,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:31</v>
+        <v>3:21</v>
       </c>
       <c r="H59" t="str">
-        <v>Julia Cole Music</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B60" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-28</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:21</v>
+        <v>5:24</v>
       </c>
       <c r="H60" t="str">
-        <v>Lily Allen</v>
+        <v>Nickless</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B61" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-28</v>
@@ -2696,10 +2696,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>5:24</v>
+        <v>3:11</v>
       </c>
       <c r="H61" t="str">
-        <v>Nickless</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
       </c>
       <c r="B62" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-28</v>
@@ -2734,10 +2734,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:11</v>
+        <v>4:11</v>
       </c>
       <c r="H62" t="str">
-        <v>Peach PRC</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B63" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
+        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-28</v>
@@ -2772,10 +2772,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>4:11</v>
+        <v>3:31</v>
       </c>
       <c r="H63" t="str">
-        <v>Ocean Alley</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
       </c>
       <c r="B64" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
+        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-28</v>
@@ -2810,10 +2810,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:31</v>
+        <v>4:16</v>
       </c>
       <c r="H64" t="str">
-        <v>OneRepublic</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B65" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
+        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-28</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>4:16</v>
+        <v>4:42</v>
       </c>
       <c r="H65" t="str">
-        <v>Ty Myers</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
+        <v>Teo Glacier - Don't Mind (Music Video)</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
+        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-28</v>
@@ -2886,10 +2886,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>4:42</v>
+        <v>2:47</v>
       </c>
       <c r="H66" t="str">
-        <v>JavaJazzFest</v>
+        <v>Teo Glacier</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video)</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
+        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-28</v>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>2:47</v>
+        <v>3:59</v>
       </c>
       <c r="H67" t="str">
-        <v>Teo Glacier</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
+        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-28</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:59</v>
+        <v>4:09</v>
       </c>
       <c r="H68" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>Louie TheSinger</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
+        <v>ella jane - When I Was Beautiful (Live)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
+        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-28</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>4:09</v>
+        <v>3:24</v>
       </c>
       <c r="H69" t="str">
-        <v>Louie TheSinger</v>
+        <v>ella jane</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
+        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>ella jane - When I Was Beautiful (Live)</v>
+        <v>Johnny Orlando - Emilia (Official Video)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
+        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-28</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:24</v>
+        <v>3:14</v>
       </c>
       <c r="H70" t="str">
-        <v>ella jane</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
+        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Johnny Orlando - Emilia (Official Video)</v>
+        <v>Kungs, Theophilus London - Galaxy (official video)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
+        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-28</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:14</v>
+        <v>3:32</v>
       </c>
       <c r="H71" t="str">
-        <v>Johnny Orlando</v>
+        <v>Kungs</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
+        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video)</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
+        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-28</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:32</v>
+        <v>3:15</v>
       </c>
       <c r="H72" t="str">
-        <v>Kungs</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
+        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-28</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:15</v>
+        <v>3:03</v>
       </c>
       <c r="H73" t="str">
-        <v>Billy Raffoul</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
+        <v>Stephen Sanchez - Sweet Love</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
+        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-28</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:03</v>
+        <v>3:04</v>
       </c>
       <c r="H74" t="str">
-        <v>NathanEvanss</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
+        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Stephen Sanchez - Sweet Love</v>
+        <v>Bruno Mars - I Just Might [Official Music Video]</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
+        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-28</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:04</v>
+        <v>3:33</v>
       </c>
       <c r="H75" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
+        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video]</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
+        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-28</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:33</v>
+        <v>2:53</v>
       </c>
       <c r="H76" t="str">
-        <v>Bruno Mars</v>
+        <v>MAX</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
+        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-28</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>2:53</v>
+        <v>4:11</v>
       </c>
       <c r="H77" t="str">
-        <v>MAX</v>
+        <v>Jessie J</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
+        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-28</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>4:11</v>
+        <v>2:45</v>
       </c>
       <c r="H78" t="str">
-        <v>Jessie J</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
+        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-28</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>2:45</v>
+        <v>4:00</v>
       </c>
       <c r="H79" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Brandon Lake and Cody Johnson</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
+        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-28</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:00</v>
+        <v>3:27</v>
       </c>
       <c r="H80" t="str">
-        <v>Brandon Lake and Cody Johnson</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
+        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-28</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:27</v>
+        <v>3:25</v>
       </c>
       <c r="H81" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
+        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-28</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:25</v>
+        <v>3:34</v>
       </c>
       <c r="H82" t="str">
-        <v>Olivia Dean</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
+        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-28</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:34</v>
+        <v>2:25</v>
       </c>
       <c r="H83" t="str">
-        <v>Demi Lovato</v>
+        <v>Joseph</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
+        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-28</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:25</v>
+        <v>3:26</v>
       </c>
       <c r="H84" t="str">
-        <v>Joseph</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
+        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-28</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:26</v>
+        <v>4:46</v>
       </c>
       <c r="H85" t="str">
-        <v>Demi Lovato</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
+        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-28</v>
@@ -3643,10 +3643,10 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>4:46</v>
+        <v>3:24</v>
       </c>
       <c r="H86" t="str">
         <v>Keith Urban</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
+        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-28</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:24</v>
+        <v>2:52</v>
       </c>
       <c r="H87" t="str">
-        <v>Keith Urban</v>
+        <v>Madonna</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
+        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-28</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:52</v>
+        <v>2:06</v>
       </c>
       <c r="H88" t="str">
-        <v>Madonna</v>
+        <v>Estás Tonné</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estás Tonné</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
+        <v>Anna Graves - Burn On (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
+        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-28</v>
@@ -3760,10 +3760,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>2:06</v>
+        <v>3:09</v>
       </c>
       <c r="H89" t="str">
-        <v>Estás Tonné</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estás Tonné</v>
+        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Anna Graves - Burn On (Official Music Video)</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
       </c>
       <c r="B90" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
+        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-28</v>
@@ -3798,10 +3798,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:09</v>
+        <v>5:11</v>
       </c>
       <c r="H90" t="str">
-        <v>Anna Graves</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
       </c>
       <c r="B91" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
+        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-28</v>
@@ -3836,10 +3836,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>5:11</v>
+        <v>3:40</v>
       </c>
       <c r="H91" t="str">
-        <v>Ocean Alley</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B92" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
+        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-28</v>
@@ -3874,10 +3874,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:40</v>
+        <v>3:49</v>
       </c>
       <c r="H92" t="str">
-        <v>Zara Larsson</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B93" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
+        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-28</v>
@@ -3912,10 +3912,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:49</v>
+        <v>3:42</v>
       </c>
       <c r="H93" t="str">
-        <v>Lauren Watkins</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B94" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
+        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-28</v>
@@ -3950,10 +3950,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:42</v>
+        <v>5:11</v>
       </c>
       <c r="H94" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
       </c>
       <c r="B95" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
+        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-28</v>
@@ -3988,10 +3988,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>5:11</v>
+        <v>3:57</v>
       </c>
       <c r="H95" t="str">
-        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
+        <v>Grace Enger - All My Songs (Official Lyric Video)</v>
       </c>
       <c r="B96" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
+        <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-28</v>
@@ -4026,10 +4026,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:57</v>
+        <v>3:29</v>
       </c>
       <c r="H96" t="str">
-        <v>Lainey Wilson</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
+        <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video)</v>
+        <v>Alan Walker - Broken Strings (Official Music Video)</v>
       </c>
       <c r="B97" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
+        <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-28</v>
@@ -4064,10 +4064,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:29</v>
+        <v>3:10</v>
       </c>
       <c r="H97" t="str">
-        <v>Grace Enger</v>
+        <v>Alan Walker and 2 more</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
+        <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video)</v>
+        <v>Emilia Tarrant - Break Up With Myself</v>
       </c>
       <c r="B98" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
+        <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-28</v>
@@ -4102,10 +4102,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:10</v>
+        <v>4:04</v>
       </c>
       <c r="H98" t="str">
-        <v>Alan Walker and 2 more</v>
+        <v>Emilia Tarrant</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
+        <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Emilia Tarrant - Break Up With Myself</v>
+        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026)</v>
       </c>
       <c r="B99" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
+        <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-28</v>
@@ -4140,10 +4140,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:04</v>
+        <v>3:09</v>
       </c>
       <c r="H99" t="str">
-        <v>Emilia Tarrant</v>
+        <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
+        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026)</v>
+        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer)</v>
       </c>
       <c r="B100" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
+        <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-28</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:09</v>
+        <v>2:27</v>
       </c>
       <c r="H100" t="str">
-        <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer)</v>
+        <v>Maggie Lindemann - fate</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
+        <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-28</v>
@@ -4216,10 +4216,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>2:27</v>
+        <v>2:12</v>
       </c>
       <c r="H101" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Maggie Lindemann</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
+        <v>Maggie Lindemann - fate - Maggie Lindemann</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:27</v>
@@ -591,7 +591,7 @@
         <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:01</v>
@@ -2605,7 +2605,7 @@
         <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B59" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G59" t="str">
         <v>3:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:27</v>
@@ -1541,7 +1541,7 @@
         <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>4:09</v>
@@ -1807,7 +1807,7 @@
         <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B38" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>3:17</v>
@@ -3669,7 +3669,7 @@
         <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G87" t="str">
         <v>2:52</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:27</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:27</v>
@@ -515,7 +515,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:20</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:27</v>
@@ -1921,7 +1921,7 @@
         <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>3:03</v>
@@ -2795,7 +2795,7 @@
         <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
       </c>
       <c r="B64" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
         <v>4:16</v>
@@ -3479,7 +3479,7 @@
         <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G82" t="str">
         <v>3:34</v>
@@ -3517,7 +3517,7 @@
         <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G83" t="str">
         <v>2:25</v>
@@ -3555,7 +3555,7 @@
         <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G84" t="str">
         <v>3:26</v>
@@ -3593,7 +3593,7 @@
         <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G85" t="str">
         <v>4:46</v>
@@ -4201,7 +4201,7 @@
         <v>Maggie Lindemann - fate</v>
       </c>
       <c r="B101" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v>2:12</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-01-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
       </c>
       <c r="B2" t="str">
-        <v>14 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-28</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>14 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v>4:27</v>
+        <v>2:57</v>
       </c>
       <c r="H2" t="str">
-        <v>We Three</v>
+        <v>The Offspring</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-28</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>3:01</v>
+        <v>4:10</v>
       </c>
       <c r="H3" t="str">
-        <v>Timebelle Official</v>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B4" t="str">
-        <v>2 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-28</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>3:20</v>
+        <v>2:10</v>
       </c>
       <c r="H4" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B5" t="str">
-        <v>4 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-28</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>4 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G5" t="str">
-        <v>3:34</v>
+        <v>3:52</v>
       </c>
       <c r="H5" t="str">
-        <v>Clinton Kane</v>
+        <v>lights</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>5 days ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-28</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>5 days ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G6" t="str">
-        <v>4:01</v>
+        <v>3:50</v>
       </c>
       <c r="H6" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Telenova</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>I Did "HOW MUSIC WORKS" Live To 1500 People</v>
       </c>
       <c r="B7" t="str">
-        <v>5 days ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-28</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>5 days ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:24</v>
+        <v>5:32</v>
       </c>
       <c r="H7" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Marcin</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>I Did "HOW MUSIC WORKS" Live To 1500 People - Marcin</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>5 days ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-28</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>5 days ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G8" t="str">
-        <v>5:52</v>
+        <v>4:27</v>
       </c>
       <c r="H8" t="str">
-        <v>Harry Styles</v>
+        <v>We Three</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-28</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
-        <v>5:01</v>
+        <v>3:01</v>
       </c>
       <c r="H9" t="str">
-        <v>Neal Francis</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B10" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-28</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>4:12</v>
+        <v>3:20</v>
       </c>
       <c r="H10" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-28</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:59</v>
+        <v>3:34</v>
       </c>
       <c r="H11" t="str">
-        <v>Holly Humberstone</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-28</v>
@@ -834,10 +834,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>2:56</v>
+        <v>4:01</v>
       </c>
       <c r="H12" t="str">
-        <v>Cliff Richard</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B13" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-28</v>
@@ -872,10 +872,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:46</v>
+        <v>3:24</v>
       </c>
       <c r="H13" t="str">
-        <v>Jessie Ware</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B14" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-28</v>
@@ -910,10 +910,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>4:37</v>
+        <v>5:52</v>
       </c>
       <c r="H14" t="str">
-        <v>Bella White</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B15" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-28</v>
@@ -948,10 +948,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>4:06</v>
+        <v>5:01</v>
       </c>
       <c r="H15" t="str">
-        <v>Ryan Wright</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B16" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-28</v>
@@ -986,10 +986,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:54</v>
+        <v>4:12</v>
       </c>
       <c r="H16" t="str">
-        <v>Dove Cameron</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B17" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-28</v>
@@ -1024,10 +1024,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:10</v>
+        <v>3:59</v>
       </c>
       <c r="H17" t="str">
-        <v>Parker McCollum</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B18" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-28</v>
@@ -1062,10 +1062,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:26</v>
+        <v>2:56</v>
       </c>
       <c r="H18" t="str">
-        <v>Matt Hansen</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-28</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:56</v>
+        <v>3:46</v>
       </c>
       <c r="H19" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B20" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-28</v>
@@ -1138,10 +1138,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>2:56</v>
+        <v>4:37</v>
       </c>
       <c r="H20" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Bella White</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B21" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-28</v>
@@ -1176,10 +1176,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>4:01</v>
+        <v>4:06</v>
       </c>
       <c r="H21" t="str">
-        <v>Tauren Wells</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B22" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-28</v>
@@ -1214,10 +1214,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:05</v>
+        <v>3:54</v>
       </c>
       <c r="H22" t="str">
-        <v>Maiah Manser</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B23" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-28</v>
@@ -1252,10 +1252,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>2:27</v>
+        <v>4:10</v>
       </c>
       <c r="H23" t="str">
-        <v>Taylor Austin Dye</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Chelsea Cutler - BAD (Official Video)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-28</v>
@@ -1290,10 +1290,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>2:34</v>
+        <v>3:26</v>
       </c>
       <c r="H24" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-28</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:13</v>
+        <v>2:56</v>
       </c>
       <c r="H25" t="str">
-        <v>Ashley Kutcher</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-28</v>
@@ -1366,10 +1366,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:13</v>
+        <v>2:56</v>
       </c>
       <c r="H26" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B27" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-28</v>
@@ -1404,10 +1404,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:08</v>
+        <v>4:01</v>
       </c>
       <c r="H27" t="str">
-        <v>CAIN</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Harry Styles - Aperture (Official Audio)</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-28</v>
@@ -1442,10 +1442,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>5:14</v>
+        <v>3:05</v>
       </c>
       <c r="H28" t="str">
-        <v>Harry Styles</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-28</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:59</v>
+        <v>2:27</v>
       </c>
       <c r="H29" t="str">
-        <v>Lana Lubany</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-28</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>4:21</v>
+        <v>2:34</v>
       </c>
       <c r="H30" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-28</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>4:09</v>
+        <v>3:13</v>
       </c>
       <c r="H31" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Ashley Kutcher</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B32" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-28</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:34</v>
+        <v>3:13</v>
       </c>
       <c r="H32" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-28</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:10</v>
+        <v>3:08</v>
       </c>
       <c r="H33" t="str">
-        <v>Olivia Dean</v>
+        <v>CAIN</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B34" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-28</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:21</v>
+        <v>5:14</v>
       </c>
       <c r="H34" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-28</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:06</v>
+        <v>2:59</v>
       </c>
       <c r="H35" t="str">
-        <v>The Avett Brothers</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-28</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:21</v>
+        <v>4:21</v>
       </c>
       <c r="H36" t="str">
-        <v>Jordana Bryant</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-28</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>7:21</v>
+        <v>4:09</v>
       </c>
       <c r="H37" t="str">
-        <v>Katy Perry</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-28</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:17</v>
+        <v>2:34</v>
       </c>
       <c r="H38" t="str">
-        <v>Lauren Watkins</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B39" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-28</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:45</v>
+        <v>3:10</v>
       </c>
       <c r="H39" t="str">
-        <v>Tones And I</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B40" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-28</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:57</v>
+        <v>3:21</v>
       </c>
       <c r="H40" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-28</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:03</v>
+        <v>3:06</v>
       </c>
       <c r="H41" t="str">
-        <v>Charlie Puth</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-28</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>4:27</v>
+        <v>3:21</v>
       </c>
       <c r="H42" t="str">
-        <v>Chappell Roan</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B43" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-28</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>4:34</v>
+        <v>7:21</v>
       </c>
       <c r="H43" t="str">
-        <v>Armik</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B44" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-28</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:54</v>
+        <v>3:17</v>
       </c>
       <c r="H44" t="str">
-        <v>LØLØ</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B45" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-28</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:25</v>
+        <v>3:45</v>
       </c>
       <c r="H45" t="str">
-        <v>Tenille Townes</v>
+        <v>Tones And I</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B46" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-28</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>2:01</v>
+        <v>3:57</v>
       </c>
       <c r="H46" t="str">
-        <v>Alan Walker</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B47" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-28</v>
@@ -2164,10 +2164,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>2:25</v>
+        <v>3:03</v>
       </c>
       <c r="H47" t="str">
-        <v>Charli xcx</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B48" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-28</v>
@@ -2202,10 +2202,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>1:14</v>
+        <v>4:27</v>
       </c>
       <c r="H48" t="str">
-        <v>Labrinth</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B49" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-28</v>
@@ -2240,10 +2240,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>2:59</v>
+        <v>4:34</v>
       </c>
       <c r="H49" t="str">
-        <v>Charlie Puth</v>
+        <v>Armik</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-28</v>
@@ -2278,10 +2278,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>2:29</v>
+        <v>2:54</v>
       </c>
       <c r="H50" t="str">
-        <v>Girl Tones</v>
+        <v>LØLØ</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B51" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-28</v>
@@ -2316,10 +2316,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:34</v>
+        <v>3:25</v>
       </c>
       <c r="H51" t="str">
-        <v>Jagwar Twin</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B52" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-28</v>
@@ -2354,10 +2354,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:48</v>
+        <v>2:01</v>
       </c>
       <c r="H52" t="str">
-        <v>Caroline Jones</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B53" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-28</v>
@@ -2392,10 +2392,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:32</v>
+        <v>2:25</v>
       </c>
       <c r="H53" t="str">
-        <v>The Beaches</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B54" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-28</v>
@@ -2430,10 +2430,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:49</v>
+        <v>1:14</v>
       </c>
       <c r="H54" t="str">
-        <v>Dolly Parton</v>
+        <v>Labrinth</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B55" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-28</v>
@@ -2468,10 +2468,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>4:28</v>
+        <v>2:59</v>
       </c>
       <c r="H55" t="str">
-        <v>Madison Beer</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B56" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-28</v>
@@ -2506,10 +2506,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:37</v>
+        <v>2:29</v>
       </c>
       <c r="H56" t="str">
-        <v>Ty Myers</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B57" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-28</v>
@@ -2544,10 +2544,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:35</v>
+        <v>2:34</v>
       </c>
       <c r="H57" t="str">
-        <v>Megan Moroney</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B58" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-28</v>
@@ -2582,10 +2582,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>2:31</v>
+        <v>3:48</v>
       </c>
       <c r="H58" t="str">
-        <v>Julia Cole Music</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B59" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-28</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:21</v>
+        <v>3:32</v>
       </c>
       <c r="H59" t="str">
-        <v>Lily Allen</v>
+        <v>The Beaches</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B60" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-28</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>5:24</v>
+        <v>3:49</v>
       </c>
       <c r="H60" t="str">
-        <v>Nickless</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-28</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:11</v>
+        <v>4:28</v>
       </c>
       <c r="H61" t="str">
-        <v>Peach PRC</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-28</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>4:11</v>
+        <v>3:37</v>
       </c>
       <c r="H62" t="str">
-        <v>Ocean Alley</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-28</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:31</v>
+        <v>3:35</v>
       </c>
       <c r="H63" t="str">
-        <v>OneRepublic</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-28</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>4:16</v>
+        <v>2:31</v>
       </c>
       <c r="H64" t="str">
-        <v>Ty Myers</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B65" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-28</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>4:42</v>
+        <v>3:21</v>
       </c>
       <c r="H65" t="str">
-        <v>JavaJazzFest</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video)</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B66" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-28</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>2:47</v>
+        <v>5:24</v>
       </c>
       <c r="H66" t="str">
-        <v>Teo Glacier</v>
+        <v>Nickless</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
+        <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B67" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
+        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-28</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:59</v>
+        <v>3:11</v>
       </c>
       <c r="H67" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
       </c>
       <c r="B68" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
+        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-28</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:09</v>
+        <v>4:11</v>
       </c>
       <c r="H68" t="str">
-        <v>Louie TheSinger</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>ella jane - When I Was Beautiful (Live)</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B69" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
+        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-28</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:24</v>
+        <v>3:31</v>
       </c>
       <c r="H69" t="str">
-        <v>ella jane</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Johnny Orlando - Emilia (Official Video)</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
+        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-28</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:14</v>
+        <v>4:16</v>
       </c>
       <c r="H70" t="str">
-        <v>Johnny Orlando</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video)</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
+        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-28</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:32</v>
+        <v>4:42</v>
       </c>
       <c r="H71" t="str">
-        <v>Kungs</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
+        <v>Teo Glacier - Don't Mind (Music Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
+        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-28</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:15</v>
+        <v>2:47</v>
       </c>
       <c r="H72" t="str">
-        <v>Billy Raffoul</v>
+        <v>Teo Glacier</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
+        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
+        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-28</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:03</v>
+        <v>3:59</v>
       </c>
       <c r="H73" t="str">
-        <v>NathanEvanss</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Stephen Sanchez - Sweet Love</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
+        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-28</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:04</v>
+        <v>4:09</v>
       </c>
       <c r="H74" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Louie TheSinger</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video]</v>
+        <v>ella jane - When I Was Beautiful (Live)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
+        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-28</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:33</v>
+        <v>3:24</v>
       </c>
       <c r="H75" t="str">
-        <v>Bruno Mars</v>
+        <v>ella jane</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
+        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
+        <v>Johnny Orlando - Emilia (Official Video)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
+        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-28</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:53</v>
+        <v>3:14</v>
       </c>
       <c r="H76" t="str">
-        <v>MAX</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
+        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
+        <v>Kungs, Theophilus London - Galaxy (official video)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
+        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-28</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>4:11</v>
+        <v>3:32</v>
       </c>
       <c r="H77" t="str">
-        <v>Jessie J</v>
+        <v>Kungs</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
+        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
+        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-28</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>2:45</v>
+        <v>3:15</v>
       </c>
       <c r="H78" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
+        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-28</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>4:00</v>
+        <v>3:03</v>
       </c>
       <c r="H79" t="str">
-        <v>Brandon Lake and Cody Johnson</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
+        <v>Stephen Sanchez - Sweet Love</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
+        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-28</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:27</v>
+        <v>3:04</v>
       </c>
       <c r="H80" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
+        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
+        <v>Bruno Mars - I Just Might [Official Music Video]</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
+        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-28</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:25</v>
+        <v>3:33</v>
       </c>
       <c r="H81" t="str">
-        <v>Olivia Dean</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
+        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
       </c>
       <c r="B82" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
+        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-28</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:34</v>
+        <v>2:53</v>
       </c>
       <c r="H82" t="str">
-        <v>Demi Lovato</v>
+        <v>MAX</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
+        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-28</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:25</v>
+        <v>4:11</v>
       </c>
       <c r="H83" t="str">
-        <v>Joseph</v>
+        <v>Jessie J</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
+        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-28</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:26</v>
+        <v>2:45</v>
       </c>
       <c r="H84" t="str">
-        <v>Demi Lovato</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
+        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-28</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>4:46</v>
+        <v>4:00</v>
       </c>
       <c r="H85" t="str">
-        <v>Keith Urban</v>
+        <v>Brandon Lake and Cody Johnson</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
       </c>
       <c r="B86" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
+        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-28</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:24</v>
+        <v>3:27</v>
       </c>
       <c r="H86" t="str">
-        <v>Keith Urban</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
       </c>
       <c r="B87" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
+        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-28</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:52</v>
+        <v>3:25</v>
       </c>
       <c r="H87" t="str">
-        <v>Madonna</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B88" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
+        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-28</v>
@@ -3722,10 +3722,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:06</v>
+        <v>3:34</v>
       </c>
       <c r="H88" t="str">
-        <v>Estás Tonné</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estás Tonné</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Anna Graves - Burn On (Official Music Video)</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
       </c>
       <c r="B89" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
+        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-28</v>
@@ -3760,10 +3760,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:09</v>
+        <v>2:25</v>
       </c>
       <c r="H89" t="str">
-        <v>Anna Graves</v>
+        <v>Joseph</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B90" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
+        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-28</v>
@@ -3798,10 +3798,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>5:11</v>
+        <v>3:26</v>
       </c>
       <c r="H90" t="str">
-        <v>Ocean Alley</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B91" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
+        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-28</v>
@@ -3836,10 +3836,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:40</v>
+        <v>4:46</v>
       </c>
       <c r="H91" t="str">
-        <v>Zara Larsson</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B92" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
+        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-28</v>
@@ -3874,10 +3874,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:49</v>
+        <v>3:24</v>
       </c>
       <c r="H92" t="str">
-        <v>Lauren Watkins</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
       </c>
       <c r="B93" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
+        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-28</v>
@@ -3912,10 +3912,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:42</v>
+        <v>2:52</v>
       </c>
       <c r="H93" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Madonna</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
       </c>
       <c r="B94" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
+        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-28</v>
@@ -3950,10 +3950,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>5:11</v>
+        <v>2:06</v>
       </c>
       <c r="H94" t="str">
-        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Estás Tonné</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estás Tonné</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
+        <v>Anna Graves - Burn On (Official Music Video)</v>
       </c>
       <c r="B95" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
+        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-28</v>
@@ -3988,10 +3988,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:57</v>
+        <v>3:09</v>
       </c>
       <c r="H95" t="str">
-        <v>Lainey Wilson</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
+        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video)</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
       </c>
       <c r="B96" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
+        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-28</v>
@@ -4026,10 +4026,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:29</v>
+        <v>5:11</v>
       </c>
       <c r="H96" t="str">
-        <v>Grace Enger</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video)</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
       </c>
       <c r="B97" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
+        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-28</v>
@@ -4064,10 +4064,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:10</v>
+        <v>3:40</v>
       </c>
       <c r="H97" t="str">
-        <v>Alan Walker and 2 more</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Emilia Tarrant - Break Up With Myself</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B98" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
+        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-28</v>
@@ -4102,10 +4102,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>4:04</v>
+        <v>3:49</v>
       </c>
       <c r="H98" t="str">
-        <v>Emilia Tarrant</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026)</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B99" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
+        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-28</v>
@@ -4140,10 +4140,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:09</v>
+        <v>3:42</v>
       </c>
       <c r="H99" t="str">
-        <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer)</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B100" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
+        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-28</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>2:27</v>
+        <v>5:11</v>
       </c>
       <c r="H100" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Maggie Lindemann - fate</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
       </c>
       <c r="B101" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
+        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-28</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>2:12</v>
+        <v>3:57</v>
       </c>
       <c r="H101" t="str">
-        <v>Maggie Lindemann</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Maggie Lindemann - fate - Maggie Lindemann</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
       </c>
     </row>
   </sheetData>
